--- a/labeled_dataset.xlsx
+++ b/labeled_dataset.xlsx
@@ -639,23 +639,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>http://www.wqqdjddjjddd.weebly.com/</t>
+          <t>https://wordpress-203685-icloudjp.cloudclusters.net/wp-content/accptw/index.php</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
       <c r="F5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="b">
         <v>0</v>
@@ -664,7 +664,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>1.73</v>
+        <v>4.16</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -676,10 +676,10 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>7472</v>
+        <v>2843</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -688,17 +688,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>http://lktvr057nhw-ghfcyfyn-1w8v9g-pz611a.pages.dev/</t>
+          <t>http://www.wqqdjddjjddd.weebly.com/</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>4.4</v>
+        <v>1.73</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -724,9 +724,11 @@
       <c r="L6" t="b">
         <v>0</v>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>7472</v>
+      </c>
       <c r="N6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -735,14 +737,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://wordpress-203685-icloudjp.cloudclusters.net/wp-content/accptw/index.php</t>
+          <t>http://lktvr057nhw-ghfcyfyn-1w8v9g-pz611a.pages.dev/</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>3</v>
@@ -751,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="b">
         <v>0</v>
@@ -760,7 +762,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>4.16</v>
+        <v>4.4</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -771,11 +773,9 @@
       <c r="L7" t="b">
         <v>0</v>
       </c>
-      <c r="M7" t="n">
-        <v>2843</v>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -784,11 +784,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://m3tamsklogen.gitbook.io/us</t>
+          <t>http://m3tamsklogen.gitbook.io/</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C8" t="n">
         <v>2</v>
@@ -800,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="b">
         <v>0</v>
@@ -824,7 +824,7 @@
         <v>4549</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -833,11 +833,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>http://m3tamsklogen.gitbook.io/</t>
+          <t>https://m3tamsklogen.gitbook.io/us</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C9" t="n">
         <v>2</v>
@@ -849,7 +849,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="b">
         <v>0</v>
@@ -873,7 +873,7 @@
         <v>4549</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -882,32 +882,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://netflix-two-mu.vercel.app/signin</t>
+          <t>http://counter-offer-access-letter.authorizationsso.help/</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
       </c>
       <c r="F10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="b">
         <v>0</v>
       </c>
       <c r="H10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -918,9 +918,11 @@
       <c r="L10" t="b">
         <v>0</v>
       </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>8</v>
+      </c>
       <c r="N10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -929,32 +931,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>http://counter-offer-access-letter.authorizationsso.help/</t>
+          <t>https://netflix-two-mu.vercel.app/signin</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
       </c>
       <c r="F11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="b">
         <v>0</v>
       </c>
       <c r="H11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -965,11 +967,9 @@
       <c r="L11" t="b">
         <v>0</v>
       </c>
-      <c r="M11" t="n">
-        <v>8</v>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1317,14 +1317,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>http://shopeeid220.blogspot.com/?m=1</t>
+          <t>http://tiny.cc/g3ba101</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1339,10 +1339,10 @@
         <v>0</v>
       </c>
       <c r="H19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1353,9 +1353,11 @@
       <c r="L19" t="b">
         <v>0</v>
       </c>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>7489</v>
+      </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
         <v>1</v>
@@ -1364,11 +1366,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://shopeetbk7272.blogspot.com/</t>
+          <t>http://shopeeid220.blogspot.com/?m=1</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C20" t="n">
         <v>2</v>
@@ -1380,7 +1382,7 @@
         <v>0</v>
       </c>
       <c r="F20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="b">
         <v>0</v>
@@ -1389,7 +1391,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1402,7 +1404,7 @@
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O20" t="n">
         <v>1</v>
@@ -1411,14 +1413,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>http://tiny.cc/g3ba101</t>
+          <t>https://shopeetbk7272.blogspot.com/</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -1427,16 +1429,16 @@
         <v>0</v>
       </c>
       <c r="F21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="b">
         <v>0</v>
       </c>
       <c r="H21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>3.24</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1447,11 +1449,9 @@
       <c r="L21" t="b">
         <v>0</v>
       </c>
-      <c r="M21" t="n">
-        <v>7489</v>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
@@ -1742,23 +1742,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://danakagetrsm.vercel.app/</t>
+          <t>http://hadiah-shopee246.blogspot.com/</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C28" t="n">
         <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
       </c>
       <c r="F28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" t="b">
         <v>0</v>
@@ -1767,10 +1767,10 @@
         <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>3.19</v>
+        <v>3.45</v>
       </c>
       <c r="J28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K28" t="b">
         <v>0</v>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
@@ -1789,23 +1789,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>http://hadiah-shopee246.blogspot.com/</t>
+          <t>https://danakagetrsm.vercel.app/</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C29" t="n">
         <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
       </c>
       <c r="F29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="b">
         <v>0</v>
@@ -1814,10 +1814,10 @@
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>3.45</v>
+        <v>3.19</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O29" t="n">
         <v>1</v>
@@ -1836,23 +1836,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>http://www.danakagetrsm.vercel.app/</t>
+          <t>https://androshchuknastya.github.io/right-phone-sms/</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
       </c>
       <c r="F30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="b">
         <v>0</v>
@@ -1861,7 +1861,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>3.19</v>
+        <v>3.45</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O30" t="n">
         <v>1</v>
@@ -1883,23 +1883,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://androshchuknastya.github.io/right-phone-sms/</t>
+          <t>http://www.danakagetrsm.vercel.app/</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
       </c>
       <c r="F31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="b">
         <v>0</v>
@@ -1908,7 +1908,7 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>3.45</v>
+        <v>3.19</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O31" t="n">
         <v>1</v>
@@ -1979,17 +1979,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://bridge-docs-trezar-auth.webflow.io/</t>
+          <t>https://www.roblox.ly/communities/3109493600/LYchurchill</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="C33" t="n">
         <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>3.76</v>
+        <v>-0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2015,9 +2015,11 @@
       <c r="L33" t="b">
         <v>0</v>
       </c>
-      <c r="M33" t="inlineStr"/>
+      <c r="M33" t="n">
+        <v>60</v>
+      </c>
       <c r="N33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>1</v>
@@ -2026,17 +2028,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.roblox.ly/communities/3109493600/LYchurchill</t>
+          <t>https://bridge-docs-trezar-auth.webflow.io/</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C34" t="n">
         <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
@@ -2051,7 +2053,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>-0</v>
+        <v>3.76</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2062,11 +2064,9 @@
       <c r="L34" t="b">
         <v>0</v>
       </c>
-      <c r="M34" t="n">
-        <v>60</v>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O34" t="n">
         <v>1</v>
@@ -2075,17 +2075,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://alto-norte-comercial.onrender.com/</t>
+          <t>https://tinyurl.com/2banr4fn</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E35" t="b">
         <v>0</v>
@@ -2100,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>3.38</v>
+        <v>2.81</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2111,7 +2111,9 @@
       <c r="L35" t="b">
         <v>0</v>
       </c>
-      <c r="M35" t="inlineStr"/>
+      <c r="M35" t="n">
+        <v>8994</v>
+      </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
@@ -2169,17 +2171,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2banr4fn</t>
+          <t>https://alto-norte-comercial.onrender.com/</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E37" t="b">
         <v>0</v>
@@ -2194,7 +2196,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>2.81</v>
+        <v>3.38</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2205,9 +2207,7 @@
       <c r="L37" t="b">
         <v>0</v>
       </c>
-      <c r="M37" t="n">
-        <v>8994</v>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="n">
         <v>0</v>
       </c>
@@ -2265,11 +2265,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://lntermaticopacifico.online/</t>
+          <t>https://tlknan.net/</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C39" t="n">
         <v>1</v>
@@ -2290,7 +2290,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>3.43</v>
+        <v>2.25</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2301,9 +2301,11 @@
       <c r="L39" t="b">
         <v>0</v>
       </c>
-      <c r="M39" t="inlineStr"/>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O39" t="n">
         <v>1</v>
@@ -2312,14 +2314,14 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://cancelsecurealfa.vercel.app/</t>
+          <t>https://lntermaticopacifico.online/</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -2334,10 +2336,10 @@
         <v>0</v>
       </c>
       <c r="H40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>2.98</v>
+        <v>3.43</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2350,7 +2352,7 @@
       </c>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>1</v>
@@ -2359,17 +2361,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://aw3749333-coder.github.io/express-dhl</t>
+          <t>https://cancelsecurealfa.vercel.app/</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C41" t="n">
         <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
@@ -2384,7 +2386,7 @@
         <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>3.37</v>
+        <v>2.98</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2502,11 +2504,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://aerditee-hub.github.io/Netflix-Clone</t>
+          <t>https://aw3749333-coder.github.io/express-dhl</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C44" t="n">
         <v>2</v>
@@ -2527,7 +2529,7 @@
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>3.19</v>
+        <v>3.37</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2596,17 +2598,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://companypolicy.com.au/?r=ae7fc135-43ca-46ba-83a1-d0c556b0e4ae&amp;rg=us</t>
+          <t>https://aerditee-hub.github.io/Netflix-Clone</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="C46" t="n">
         <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
@@ -2618,10 +2620,10 @@
         <v>0</v>
       </c>
       <c r="H46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>3.09</v>
+        <v>3.19</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2634,7 +2636,7 @@
       </c>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O46" t="n">
         <v>1</v>
@@ -2643,17 +2645,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://tlknan.net/</t>
+          <t>https://companypolicy.com.au/?r=ae7fc135-43ca-46ba-83a1-d0c556b0e4ae&amp;rg=us</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
@@ -2668,7 +2670,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>2.25</v>
+        <v>3.09</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2679,11 +2681,9 @@
       <c r="L47" t="b">
         <v>0</v>
       </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>1</v>
@@ -2980,17 +2980,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://gift-community.beer/id=5947221648</t>
+          <t>https://394532.xyz/</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="C54" t="n">
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" t="b">
         <v>0</v>
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>3.38</v>
+        <v>2.25</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -3029,14 +3029,14 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://394532.xyz/</t>
+          <t>https://www.fyshur.com/</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>2.25</v>
+        <v>-0</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -3066,10 +3066,10 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="N55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>1</v>
@@ -3078,14 +3078,14 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.fyshur.com/</t>
+          <t>http://tiny.cc/uoaa101</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
         <v>0</v>
       </c>
       <c r="F56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56" t="b">
         <v>0</v>
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>-0</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>43</v>
+        <v>7489</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O56" t="n">
         <v>1</v>
@@ -3127,11 +3127,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>http://tiny.cc/uoaa101</t>
+          <t>https://lkntansr.net/</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C57" t="n">
         <v>1</v>
@@ -3143,7 +3143,7 @@
         <v>0</v>
       </c>
       <c r="F57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" t="b">
         <v>0</v>
@@ -3152,7 +3152,7 @@
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3164,10 +3164,10 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>7489</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O57" t="n">
         <v>1</v>
@@ -3176,23 +3176,23 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>http://pay.emag.ro/pay/v2/</t>
+          <t>https://gift-community.beer/id=5947221648</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58" t="b">
         <v>0</v>
       </c>
       <c r="F58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G58" t="b">
         <v>0</v>
@@ -3201,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>1.58</v>
+        <v>3.38</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3213,10 +3213,10 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>9385</v>
+        <v>3</v>
       </c>
       <c r="N58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O58" t="n">
         <v>1</v>
@@ -3225,11 +3225,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.google.com</t>
+          <t>http://pay.emag.ro/pay/v2/</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C59" t="n">
         <v>2</v>
@@ -3241,7 +3241,7 @@
         <v>0</v>
       </c>
       <c r="F59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59" t="b">
         <v>0</v>
@@ -3250,10 +3250,10 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>-0</v>
+        <v>1.58</v>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K59" t="b">
         <v>0</v>
@@ -3262,13 +3262,13 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>10589</v>
+        <v>9385</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3323,7 +3323,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.python.org</t>
+          <t>https://www.google.com</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3360,7 +3360,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>11492</v>
+        <v>10589</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
@@ -3372,14 +3372,14 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://lkntansr.net/</t>
+          <t>https://www.python.org</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>2.75</v>
+        <v>-0</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" t="b">
         <v>0</v>
@@ -3409,23 +3409,23 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>11492</v>
       </c>
       <c r="N62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.wikipedia.org</t>
+          <t>https://www.github.com</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C63" t="n">
         <v>2</v>
@@ -3449,7 +3449,7 @@
         <v>-0</v>
       </c>
       <c r="J63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K63" t="b">
         <v>0</v>
@@ -3458,7 +3458,7 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>9373</v>
+        <v>6912</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
@@ -3470,11 +3470,11 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.apple.com</t>
+          <t>https://www.wikipedia.org</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C64" t="n">
         <v>2</v>
@@ -3507,7 +3507,7 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>14450</v>
+        <v>9373</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
@@ -3519,11 +3519,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.github.com</t>
+          <t>https://www.apple.com</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C65" t="n">
         <v>2</v>
@@ -3547,7 +3547,7 @@
         <v>-0</v>
       </c>
       <c r="J65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K65" t="b">
         <v>0</v>
@@ -3556,7 +3556,7 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>6912</v>
+        <v>14450</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
@@ -3617,17 +3617,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.netflix.com</t>
+          <t>https://apple-verify.us/help?fGK</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" t="b">
         <v>0</v>
@@ -3642,7 +3642,7 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>-0</v>
+        <v>3.25</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -3654,35 +3654,35 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>10532</v>
+        <v>211</v>
       </c>
       <c r="N67" t="n">
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com</t>
+          <t>http://apple-verify.us/fGK</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" t="b">
         <v>0</v>
       </c>
       <c r="F68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68" t="b">
         <v>0</v>
@@ -3691,10 +3691,10 @@
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>-0</v>
+        <v>3.25</v>
       </c>
       <c r="J68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K68" t="b">
         <v>0</v>
@@ -3703,23 +3703,23 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>8714</v>
+        <v>211</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.paypal.com</t>
+          <t>https://www.netflix.com</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C69" t="n">
         <v>2</v>
@@ -3752,7 +3752,7 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>9921</v>
+        <v>10532</v>
       </c>
       <c r="N69" t="n">
         <v>0</v>
@@ -3764,11 +3764,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.reddit.com</t>
+          <t>https://www.linkedin.com</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C70" t="n">
         <v>2</v>
@@ -3792,7 +3792,7 @@
         <v>-0</v>
       </c>
       <c r="J70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K70" t="b">
         <v>0</v>
@@ -3801,7 +3801,7 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>7805</v>
+        <v>8714</v>
       </c>
       <c r="N70" t="n">
         <v>0</v>
@@ -3813,11 +3813,11 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.spotify.com</t>
+          <t>https://www.reddit.com</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C71" t="n">
         <v>2</v>
@@ -3841,7 +3841,7 @@
         <v>-0</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K71" t="b">
         <v>0</v>
@@ -3850,7 +3850,7 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>7447</v>
+        <v>7805</v>
       </c>
       <c r="N71" t="n">
         <v>0</v>
@@ -3862,17 +3862,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://apple-verify.us/help?fGK</t>
+          <t>https://www.paypal.com</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E72" t="b">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>3.25</v>
+        <v>-0</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -3899,35 +3899,35 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>211</v>
+        <v>9921</v>
       </c>
       <c r="N72" t="n">
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>http://apple-verify.us/fGK</t>
+          <t>https://www.spotify.com</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E73" t="b">
         <v>0</v>
       </c>
       <c r="F73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73" t="b">
         <v>0</v>
@@ -3936,7 +3936,7 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>3.25</v>
+        <v>-0</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -3948,19 +3948,19 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>211</v>
+        <v>7447</v>
       </c>
       <c r="N73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.dropbox.com</t>
+          <t>https://www.nytimes.com</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -3988,7 +3988,7 @@
         <v>-0</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K74" t="b">
         <v>0</v>
@@ -3997,7 +3997,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>11399</v>
+        <v>11925</v>
       </c>
       <c r="N74" t="n">
         <v>0</v>
@@ -4009,11 +4009,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com</t>
+          <t>https://www.bbc.com</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C75" t="n">
         <v>2</v>
@@ -4037,7 +4037,7 @@
         <v>-0</v>
       </c>
       <c r="J75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K75" t="b">
         <v>0</v>
@@ -4046,7 +4046,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>11925</v>
+        <v>13573</v>
       </c>
       <c r="N75" t="n">
         <v>0</v>
@@ -4058,11 +4058,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.cloudflare.com</t>
+          <t>https://www.dropbox.com</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C76" t="n">
         <v>2</v>
@@ -4095,7 +4095,7 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>6415</v>
+        <v>11399</v>
       </c>
       <c r="N76" t="n">
         <v>0</v>
@@ -4107,11 +4107,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.bbc.com</t>
+          <t>https://www.cloudflare.com</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C77" t="n">
         <v>2</v>
@@ -4144,7 +4144,7 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>13573</v>
+        <v>6415</v>
       </c>
       <c r="N77" t="n">
         <v>0</v>
@@ -4450,11 +4450,11 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.adobe.com</t>
+          <t>https://www.ebay.com</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C84" t="n">
         <v>2</v>
@@ -4487,7 +4487,7 @@
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>14544</v>
+        <v>11362</v>
       </c>
       <c r="N84" t="n">
         <v>0</v>
@@ -4499,11 +4499,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.ebay.com</t>
+          <t>https://www.adobe.com</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C85" t="n">
         <v>2</v>
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>11362</v>
+        <v>14544</v>
       </c>
       <c r="N85" t="n">
         <v>0</v>
@@ -4597,11 +4597,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.uber.com</t>
+          <t>https://www.airbnb.com</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C87" t="n">
         <v>2</v>
@@ -4625,19 +4625,19 @@
         <v>-0</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K87" t="b">
         <v>0</v>
       </c>
       <c r="L87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>11383</v>
+        <v>6612</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -4646,11 +4646,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.airbnb.com</t>
+          <t>https://www.uber.com</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C88" t="n">
         <v>2</v>
@@ -4674,19 +4674,19 @@
         <v>-0</v>
       </c>
       <c r="J88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K88" t="b">
         <v>0</v>
       </c>
       <c r="L88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>6612</v>
+        <v>11383</v>
       </c>
       <c r="N88" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>

--- a/labeled_dataset.xlsx
+++ b/labeled_dataset.xlsx
@@ -496,23 +496,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://3ib64a1sok-k9t7f7se-evaygbgad7dueuhq.z02.azurefd.net/</t>
+          <t>http://sp32ct-dalrex-biz-vornik-cesla.pages.dev/</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
       </c>
       <c r="F2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="b">
         <v>0</v>
@@ -521,7 +521,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>4.62</v>
+        <v>4.17</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -534,7 +534,7 @@
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -543,17 +543,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>http://staging.dtbf2az168uk3.amplifyapp.com/</t>
+          <t>http://intrepid-amused-analysts--vdsbwa.replit.app/</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -565,23 +565,23 @@
         <v>0</v>
       </c>
       <c r="H3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>4.11</v>
+        <v>3.85</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="b">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -590,18 +590,18 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.metuamssk-logiye.godaddysites.com/</t>
+          <t>https://xernqavi-mpt-borvexo-r8d2me61.pages.dev/</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
       <c r="E4" t="b">
         <v>0</v>
       </c>
@@ -615,7 +615,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>3.62</v>
+        <v>4.09</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -626,9 +626,7 @@
       <c r="L4" t="b">
         <v>0</v>
       </c>
-      <c r="M4" t="n">
-        <v>4680</v>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
         <v>6</v>
       </c>
@@ -639,17 +637,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://wordpress-203685-icloudjp.cloudclusters.net/wp-content/accptw/index.php</t>
+          <t>https://www.account-verification-method.vercel.app/</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -664,7 +662,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>4.16</v>
+        <v>3.75</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -675,9 +673,7 @@
       <c r="L5" t="b">
         <v>0</v>
       </c>
-      <c r="M5" t="n">
-        <v>2843</v>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
         <v>6</v>
       </c>
@@ -688,17 +684,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>http://www.wqqdjddjjddd.weebly.com/</t>
+          <t>http://www.your-order-logistics-global-tracking.vercel.app/</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="C6" t="n">
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -713,7 +709,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1.73</v>
+        <v>3.88</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -724,11 +720,9 @@
       <c r="L6" t="b">
         <v>0</v>
       </c>
-      <c r="M6" t="n">
-        <v>7472</v>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -737,23 +731,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>http://lktvr057nhw-ghfcyfyn-1w8v9g-pz611a.pages.dev/</t>
+          <t>https://navzuri-mpt-qelfavo-c3h8me57.pages.dev/thn-yjm-uio-lkh?welcome=1235735009619786&amp;stt=1235735009619786&amp;name_stt=E-%20Commerce%20With%20Shoaib</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>52</v>
+        <v>147</v>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
       </c>
       <c r="F7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="b">
         <v>0</v>
@@ -762,7 +756,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -775,7 +769,7 @@
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -784,11 +778,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>http://m3tamsklogen.gitbook.io/</t>
+          <t>https://roblox.com.bo/communities/488688266/</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C8" t="n">
         <v>2</v>
@@ -800,16 +794,16 @@
         <v>0</v>
       </c>
       <c r="F8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="b">
         <v>0</v>
       </c>
       <c r="H8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3.42</v>
+        <v>2.25</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -820,11 +814,9 @@
       <c r="L8" t="b">
         <v>0</v>
       </c>
-      <c r="M8" t="n">
-        <v>4549</v>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -833,17 +825,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://m3tamsklogen.gitbook.io/us</t>
+          <t>https://www.roblox.ly/games/920587237/Adopt-Me?privateServerLinkCode=25143865265762886900763909739476</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -855,10 +847,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>3.42</v>
+        <v>-0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -870,10 +862,10 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4549</v>
+        <v>60</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -882,17 +874,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>http://counter-offer-access-letter.authorizationsso.help/</t>
+          <t>http://wp.pl-krajowyrejestdlugow.info.vh13647.vh.net.pl/</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -907,7 +899,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -919,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>8</v>
+        <v>2661</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -931,17 +923,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://netflix-two-mu.vercel.app/signin</t>
+          <t>https://vwwv-roblox.co/users/1515798849/profile</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -953,13 +945,13 @@
         <v>0</v>
       </c>
       <c r="H11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>3.52</v>
+        <v>2.91</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
@@ -967,9 +959,11 @@
       <c r="L11" t="b">
         <v>0</v>
       </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>4</v>
+      </c>
       <c r="N11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -978,32 +972,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>http://www.17vip07.com/</t>
+          <t>https://hadiah-shopee242.blogspot.com/</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
       </c>
       <c r="F12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="b">
         <v>0</v>
       </c>
       <c r="H12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>3.33</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1014,11 +1008,9 @@
       <c r="L12" t="b">
         <v>0</v>
       </c>
-      <c r="M12" t="n">
-        <v>1634</v>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -1027,45 +1019,45 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>http://security-server-landing-page--manostelee.replit.app/</t>
+          <t>https://www.shopeeid414.blogspot.com/</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
       </c>
       <c r="F13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="b">
         <v>0</v>
       </c>
       <c r="H13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>3.86</v>
+        <v>3.1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="b">
         <v>0</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -1074,17 +1066,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://inicio-2026aunthentication365.yzz.me/</t>
+          <t>https://shopeeid077.blogspot.com/</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
@@ -1096,10 +1088,10 @@
         <v>0</v>
       </c>
       <c r="H14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>3.67</v>
+        <v>3.1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1110,9 +1102,7 @@
       <c r="L14" t="b">
         <v>0</v>
       </c>
-      <c r="M14" t="n">
-        <v>1496</v>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
         <v>3</v>
       </c>
@@ -1123,17 +1113,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://phantom1-wallet.godaddysites.com/</t>
+          <t>https://irsrefundservice.us/</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
@@ -1145,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>3.51</v>
+        <v>3.16</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
@@ -1160,10 +1150,10 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4680</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
@@ -1172,17 +1162,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://s4w.in/roblox-com-user-382073395-profile</t>
+          <t>https://www.robiox.com.gr/users/8880414661/profile</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
@@ -1197,7 +1187,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1.58</v>
+        <v>-0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1208,9 +1198,7 @@
       <c r="L16" t="b">
         <v>0</v>
       </c>
-      <c r="M16" t="n">
-        <v>6876</v>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
         <v>0</v>
       </c>
@@ -1221,23 +1209,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.phantom1-wallet.godaddysites.com/</t>
+          <t>http://www.shopeeid077.blogspot.com/</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
         <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
       </c>
       <c r="F17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="b">
         <v>0</v>
@@ -1246,7 +1234,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>3.51</v>
+        <v>3.1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1257,11 +1245,9 @@
       <c r="L17" t="b">
         <v>0</v>
       </c>
-      <c r="M17" t="n">
-        <v>4680</v>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O17" t="n">
         <v>1</v>
@@ -1270,32 +1256,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>http://fast-report-968025.framer.app/</t>
+          <t>https://shopeeid414.blogspot.com/</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C18" t="n">
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
       </c>
       <c r="F18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="b">
         <v>0</v>
       </c>
       <c r="H18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>3.84</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1308,7 +1294,7 @@
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
         <v>1</v>
@@ -1317,14 +1303,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>http://tiny.cc/g3ba101</t>
+          <t>http://www.robloxc.com.es/users/1539346212/profile/</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1342,7 +1328,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>-0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1353,9 +1339,7 @@
       <c r="L19" t="b">
         <v>0</v>
       </c>
-      <c r="M19" t="n">
-        <v>7489</v>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
         <v>1</v>
       </c>
@@ -1366,11 +1350,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>http://shopeeid220.blogspot.com/?m=1</t>
+          <t>https://3x4x43x.pages.dev/</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C20" t="n">
         <v>2</v>
@@ -1382,7 +1366,7 @@
         <v>0</v>
       </c>
       <c r="F20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="b">
         <v>0</v>
@@ -1391,7 +1375,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>3.1</v>
+        <v>1.56</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1404,7 +1388,7 @@
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
         <v>1</v>
@@ -1413,17 +1397,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://shopeetbk7272.blogspot.com/</t>
+          <t>https://highpoint-02.pages.dev/?app_vl=ZYFwlWpnbWKEmLqxy5qmnnx0YsC2wa-TpaiVYsBxj2phmqOgnLFwrYw&amp;dd=USE1NzEhKCczOiAyZSUjKCA&amp;e=tomtom%2540tomorrow.com&amp;sui=%257Bsui%257D&amp;fn=Tom&amp;ln=Wiltshire%252Bbooth&amp;p=&amp;z=CHNAMER...</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>35</v>
+        <v>211</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
@@ -1438,7 +1422,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1460,14 +1444,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>http://undianshopee151.blogspot.com/</t>
+          <t>https://vmi3567924.contaboserver.net/fix/sen/rena/msg.php</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -1476,16 +1460,16 @@
         <v>0</v>
       </c>
       <c r="F22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="b">
         <v>0</v>
       </c>
       <c r="H22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>3.51</v>
+        <v>3.32</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1496,9 +1480,11 @@
       <c r="L22" t="b">
         <v>0</v>
       </c>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>3478</v>
+      </c>
       <c r="N22" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>1</v>
@@ -1507,23 +1493,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>http://shopeeid209.blogspot.com/</t>
+          <t>https://ledger--livedesktop--welcome.pages.dev/</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C23" t="n">
         <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
       </c>
       <c r="F23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="b">
         <v>0</v>
@@ -1532,7 +1518,7 @@
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>3.28</v>
+        <v>3.66</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1545,7 +1531,7 @@
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O23" t="n">
         <v>1</v>
@@ -1554,17 +1540,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://hadiahshopee512.blogspot.com/?m=1</t>
+          <t>https://site-tjaobqglc.godaddysites.com/</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C24" t="n">
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
@@ -1579,10 +1565,10 @@
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>3.32</v>
+        <v>3.66</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="b">
         <v>0</v>
@@ -1590,9 +1576,11 @@
       <c r="L24" t="b">
         <v>0</v>
       </c>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="n">
+        <v>4680</v>
+      </c>
       <c r="N24" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O24" t="n">
         <v>1</v>
@@ -1601,11 +1589,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>http://hadiah-shopee116.blogspot.com/</t>
+          <t>https://vht-sk.sk/Benachrichtigung/htm.html</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C25" t="n">
         <v>2</v>
@@ -1617,19 +1605,19 @@
         <v>0</v>
       </c>
       <c r="F25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="b">
         <v>0</v>
       </c>
       <c r="H25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>3.33</v>
+        <v>2.58</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
@@ -1637,9 +1625,11 @@
       <c r="L25" t="b">
         <v>0</v>
       </c>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>1264</v>
+      </c>
       <c r="N25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>1</v>
@@ -1648,11 +1638,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>http://hadiah-shopee823.blogspot.com/</t>
+          <t>https://aiman54321.github.io/netflix-clone</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C26" t="n">
         <v>2</v>
@@ -1664,7 +1654,7 @@
         <v>0</v>
       </c>
       <c r="F26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="b">
         <v>0</v>
@@ -1673,7 +1663,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>3.45</v>
+        <v>3.12</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1686,7 +1676,7 @@
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
         <v>1</v>
@@ -1695,23 +1685,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>http://ondp.finance/</t>
+          <t>https://www.roblox.com.mu/games/139410450104051/Chat-with-AI-Emiko?privateServerLinkCode=79442235214644471569831337955340</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>20</v>
+        <v>121</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
       </c>
       <c r="F27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="b">
         <v>0</v>
@@ -1720,7 +1710,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>-0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1731,9 +1721,11 @@
       <c r="L27" t="b">
         <v>0</v>
       </c>
-      <c r="M27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>97</v>
+      </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>1</v>
@@ -1742,14 +1734,14 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>http://hadiah-shopee246.blogspot.com/</t>
+          <t>http://www.mclarencar.ebaymclaren-austin.eventshouse.app/</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
         <v>1</v>
@@ -1764,10 +1756,10 @@
         <v>0</v>
       </c>
       <c r="H28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>3.45</v>
+        <v>-0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1780,7 +1772,7 @@
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
@@ -1789,14 +1781,14 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://danakagetrsm.vercel.app/</t>
+          <t>https://lnk.ink/HTv47</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1811,13 +1803,13 @@
         <v>0</v>
       </c>
       <c r="H29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>3.19</v>
+        <v>1.58</v>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
@@ -1825,9 +1817,11 @@
       <c r="L29" t="b">
         <v>0</v>
       </c>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="n">
+        <v>496</v>
+      </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>1</v>
@@ -1836,17 +1830,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://androshchuknastya.github.io/right-phone-sms/</t>
+          <t>https://d2cx10dsi4ptcz.cloudfront.net/</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="C30" t="n">
         <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
@@ -1858,10 +1852,10 @@
         <v>0</v>
       </c>
       <c r="H30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1883,17 +1877,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>http://www.danakagetrsm.vercel.app/</t>
+          <t>http://www.mclarenf1car.ebaymclaren-austin.eventshouse.app/</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
@@ -1905,10 +1899,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>3.19</v>
+        <v>-0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1921,7 +1915,7 @@
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O31" t="n">
         <v>1</v>
@@ -1930,23 +1924,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.financesantanderm.tu.lahmtm.com/</t>
+          <t>http://www.hofmemorabilia.ebaymclaren-austin.eventshouse.app/</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="C32" t="n">
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
       </c>
       <c r="F32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="b">
         <v>0</v>
@@ -1966,11 +1960,9 @@
       <c r="L32" t="b">
         <v>0</v>
       </c>
-      <c r="M32" t="n">
-        <v>90</v>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" t="n">
         <v>1</v>
@@ -1979,14 +1971,14 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.roblox.ly/communities/3109493600/LYchurchill</t>
+          <t>http://www.drainit.vercel.app/</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -1995,16 +1987,16 @@
         <v>0</v>
       </c>
       <c r="F33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" t="b">
         <v>0</v>
       </c>
       <c r="H33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>-0</v>
+        <v>2.52</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2015,11 +2007,9 @@
       <c r="L33" t="b">
         <v>0</v>
       </c>
-      <c r="M33" t="n">
-        <v>60</v>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O33" t="n">
         <v>1</v>
@@ -2028,17 +2018,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://bridge-docs-trezar-auth.webflow.io/</t>
+          <t>https://verif-mail.cloud/</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
@@ -2053,7 +2043,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>3.76</v>
+        <v>3.12</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2064,7 +2054,9 @@
       <c r="L34" t="b">
         <v>0</v>
       </c>
-      <c r="M34" t="inlineStr"/>
+      <c r="M34" t="n">
+        <v>2</v>
+      </c>
       <c r="N34" t="n">
         <v>3</v>
       </c>
@@ -2075,35 +2067,35 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2banr4fn</t>
+          <t>http://site-yzcbrf6j0.godaddysites.com/</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" t="b">
         <v>0</v>
       </c>
       <c r="F35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" t="b">
         <v>0</v>
       </c>
       <c r="H35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>2.81</v>
+        <v>3.81</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="b">
         <v>0</v>
@@ -2112,10 +2104,10 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>8994</v>
+        <v>4680</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O35" t="n">
         <v>1</v>
@@ -2124,17 +2116,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>http://lively-field-d81c.rudofopelomi.workers.dev/</t>
+          <t>http://staging.d2vcbrxbzugw3i.amplifyapp.com/</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C36" t="n">
         <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
@@ -2146,10 +2138,10 @@
         <v>0</v>
       </c>
       <c r="H36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>3.34</v>
+        <v>4.06</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2162,7 +2154,7 @@
       </c>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O36" t="n">
         <v>1</v>
@@ -2171,17 +2163,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://alto-norte-comercial.onrender.com/</t>
+          <t>https://www.roblox.com.hr/users/3904040857/profile</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E37" t="b">
         <v>0</v>
@@ -2196,7 +2188,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>3.38</v>
+        <v>-0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2207,9 +2199,11 @@
       <c r="L37" t="b">
         <v>0</v>
       </c>
-      <c r="M37" t="inlineStr"/>
+      <c r="M37" t="n">
+        <v>21</v>
+      </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O37" t="n">
         <v>1</v>
@@ -2218,17 +2212,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://trustwallet-neon.vercel.app/</t>
+          <t>https://www.roblox.com.hr/users/1671344922/profile</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" t="b">
         <v>0</v>
@@ -2240,10 +2234,10 @@
         <v>0</v>
       </c>
       <c r="H38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>3.33</v>
+        <v>-0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2254,7 +2248,9 @@
       <c r="L38" t="b">
         <v>0</v>
       </c>
-      <c r="M38" t="inlineStr"/>
+      <c r="M38" t="n">
+        <v>21</v>
+      </c>
       <c r="N38" t="n">
         <v>3</v>
       </c>
@@ -2265,14 +2261,14 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://tlknan.net/</t>
+          <t>https://www.roblox.com.bi/users/748717893250/profile</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -2290,7 +2286,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>2.25</v>
+        <v>-0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2302,10 +2298,10 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="N39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>1</v>
@@ -2314,11 +2310,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://lntermaticopacifico.online/</t>
+          <t>https://goo.su/UItgh</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
@@ -2339,7 +2335,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>3.43</v>
+        <v>0.92</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2350,7 +2346,9 @@
       <c r="L40" t="b">
         <v>0</v>
       </c>
-      <c r="M40" t="inlineStr"/>
+      <c r="M40" t="n">
+        <v>2646</v>
+      </c>
       <c r="N40" t="n">
         <v>0</v>
       </c>
@@ -2361,17 +2359,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://cancelsecurealfa.vercel.app/</t>
+          <t>https://www.collectableswall.ebaymclaren-austin.eventshouse.app/</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
@@ -2383,10 +2381,10 @@
         <v>0</v>
       </c>
       <c r="H41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>2.98</v>
+        <v>-0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2399,7 +2397,7 @@
       </c>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>1</v>
@@ -2408,17 +2406,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>http://sp15ct-munex-biz-zorak-qavel.pages.dev/</t>
+          <t>http://7t60y-ix3-chlx-vi11r-11-09-2026-hh.pages.dev/</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C42" t="n">
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E42" t="b">
         <v>0</v>
@@ -2433,7 +2431,7 @@
         <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>4.31</v>
+        <v>3.76</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2455,14 +2453,14 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://bgtgdtferu.lat/</t>
+          <t>https://www.metamsk_loogii.godaddysites.com/</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -2477,10 +2475,10 @@
         <v>0</v>
       </c>
       <c r="H43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>2.92</v>
+        <v>3.38</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2492,7 +2490,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>2</v>
+        <v>4680</v>
       </c>
       <c r="N43" t="n">
         <v>3</v>
@@ -2504,17 +2502,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://aw3749333-coder.github.io/express-dhl</t>
+          <t>https://www.uupholed-logiinus.godaddysites.com/</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" t="b">
         <v>0</v>
@@ -2529,7 +2527,7 @@
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>3.37</v>
+        <v>3.45</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2540,7 +2538,9 @@
       <c r="L44" t="b">
         <v>0</v>
       </c>
-      <c r="M44" t="inlineStr"/>
+      <c r="M44" t="n">
+        <v>4680</v>
+      </c>
       <c r="N44" t="n">
         <v>3</v>
       </c>
@@ -2551,17 +2551,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://ledger-live-get-desktop-coz.pages.dev/</t>
+          <t>https://1xbet-c.com/en/block</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E45" t="b">
         <v>0</v>
@@ -2573,10 +2573,10 @@
         <v>0</v>
       </c>
       <c r="H45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>3.66</v>
+        <v>2.81</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2587,9 +2587,11 @@
       <c r="L45" t="b">
         <v>0</v>
       </c>
-      <c r="M45" t="inlineStr"/>
+      <c r="M45" t="n">
+        <v>64</v>
+      </c>
       <c r="N45" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>1</v>
@@ -2598,17 +2600,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://aerditee-hub.github.io/Netflix-Clone</t>
+          <t>https://1xbet-c.com/*</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
@@ -2620,10 +2622,10 @@
         <v>0</v>
       </c>
       <c r="H46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>3.19</v>
+        <v>2.81</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2634,9 +2636,11 @@
       <c r="L46" t="b">
         <v>0</v>
       </c>
-      <c r="M46" t="inlineStr"/>
+      <c r="M46" t="n">
+        <v>64</v>
+      </c>
       <c r="N46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>1</v>
@@ -2645,17 +2649,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://companypolicy.com.au/?r=ae7fc135-43ca-46ba-83a1-d0c556b0e4ae&amp;rg=us</t>
+          <t>https://cssm.66ghz.com/</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="C47" t="n">
         <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
@@ -2670,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>3.09</v>
+        <v>1.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2681,7 +2685,9 @@
       <c r="L47" t="b">
         <v>0</v>
       </c>
-      <c r="M47" t="inlineStr"/>
+      <c r="M47" t="n">
+        <v>7236</v>
+      </c>
       <c r="N47" t="n">
         <v>0</v>
       </c>
@@ -2692,17 +2698,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://creditscolombia.com/</t>
+          <t>https://psss13.noloco.co/join/?invitationToken=1b31daf4-a815-42f6-9189-ba0ed3f67c6f</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E48" t="b">
         <v>0</v>
@@ -2717,7 +2723,7 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>3.51</v>
+        <v>1.79</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2729,10 +2735,10 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>9</v>
+        <v>1892</v>
       </c>
       <c r="N48" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>1</v>
@@ -2741,23 +2747,23 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>http://palm-night.pages.dev/</t>
+          <t>https://account-verification-method.vercel.app/</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="C49" t="n">
         <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" t="b">
         <v>0</v>
       </c>
       <c r="F49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" t="b">
         <v>0</v>
@@ -2766,7 +2772,7 @@
         <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>3.32</v>
+        <v>3.75</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2779,7 +2785,7 @@
       </c>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O49" t="n">
         <v>1</v>
@@ -2788,17 +2794,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://illimited.updatemybilling.app/YUBpCClmwZER/?redirection=login</t>
+          <t>https://start-linkedin.com/</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" t="b">
         <v>0</v>
@@ -2813,7 +2819,7 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>2.42</v>
+        <v>3.38</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2824,9 +2830,11 @@
       <c r="L50" t="b">
         <v>0</v>
       </c>
-      <c r="M50" t="inlineStr"/>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O50" t="n">
         <v>1</v>
@@ -2835,11 +2843,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://illimited.updatemybilling.app/</t>
+          <t>https://servicemaster.sviluppo.host/sclli/?LOG=24f3a45ae6194eee07570f78868ff973f93a228024c00b23a6c603f16f44550d</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="C51" t="n">
         <v>2</v>
@@ -2860,18 +2868,20 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>2.42</v>
+        <v>3.03</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" t="b">
         <v>0</v>
       </c>
-      <c r="M51" t="inlineStr"/>
+      <c r="M51" t="n">
+        <v>3410</v>
+      </c>
       <c r="N51" t="n">
         <v>0</v>
       </c>
@@ -2882,47 +2892,45 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>http://booking.jh-print.com/1102053484/</t>
+          <t>https://vijwiki.github.io/newhope</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C52" t="n">
         <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" t="b">
         <v>0</v>
       </c>
       <c r="F52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" t="b">
         <v>0</v>
       </c>
       <c r="H52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>2.52</v>
+        <v>2.13</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52" t="b">
         <v>0</v>
       </c>
       <c r="L52" t="b">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
-        <v>5806</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O52" t="n">
         <v>1</v>
@@ -2931,32 +2939,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>http://roblox.com.mu/communities/3442332532/MLCloths</t>
+          <t>https://xernqavi-mpt-borvexo-r8d2me61.pages.dev/thn-yjm-uio-lkh?welcome=164156410116085&amp;stt=164156410116085&amp;name_stt=Centro%20Legal</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>52</v>
+        <v>131</v>
       </c>
       <c r="C53" t="n">
         <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E53" t="b">
         <v>0</v>
       </c>
       <c r="F53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" t="b">
         <v>0</v>
       </c>
       <c r="H53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>2.25</v>
+        <v>4.09</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2967,11 +2975,9 @@
       <c r="L53" t="b">
         <v>0</v>
       </c>
-      <c r="M53" t="n">
-        <v>97</v>
-      </c>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O53" t="n">
         <v>1</v>
@@ -2980,17 +2986,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://394532.xyz/</t>
+          <t>https://iahnp-g5p-0jym-r1nwm-11-09-2026-hh.pages.dev/</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E54" t="b">
         <v>0</v>
@@ -3002,10 +3008,10 @@
         <v>0</v>
       </c>
       <c r="H54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>2.25</v>
+        <v>3.85</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -3016,11 +3022,9 @@
       <c r="L54" t="b">
         <v>0</v>
       </c>
-      <c r="M54" t="n">
-        <v>3</v>
-      </c>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O54" t="n">
         <v>1</v>
@@ -3029,17 +3033,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.fyshur.com/</t>
+          <t>https://your-order-logistics-global-tracking.vercel.app/</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="C55" t="n">
         <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
@@ -3051,10 +3055,10 @@
         <v>0</v>
       </c>
       <c r="H55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>-0</v>
+        <v>3.88</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -3065,11 +3069,9 @@
       <c r="L55" t="b">
         <v>0</v>
       </c>
-      <c r="M55" t="n">
-        <v>43</v>
-      </c>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O55" t="n">
         <v>1</v>
@@ -3078,14 +3080,14 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>http://tiny.cc/uoaa101</t>
+          <t>http://ligjerccobstartt.webflow.io/</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -3103,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>3.45</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3114,9 +3116,7 @@
       <c r="L56" t="b">
         <v>0</v>
       </c>
-      <c r="M56" t="n">
-        <v>7489</v>
-      </c>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="n">
         <v>1</v>
       </c>
@@ -3127,14 +3127,14 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://lkntansr.net/</t>
+          <t>https://cerexedwardsteamword2136.myclickfunnels.com/kjjjjkjklkkljljkjkkkl</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>21</v>
+        <v>73</v>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -3152,19 +3152,19 @@
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>2.75</v>
+        <v>3.69</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" t="b">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3614</v>
       </c>
       <c r="N57" t="n">
         <v>3</v>
@@ -3176,17 +3176,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://gift-community.beer/id=5947221648</t>
+          <t>https://roblox.com.bo/games/80576062127494/HOT-Catgirl-Obby-Surprise-at-the-end?privateServerLinkCode=72838528769061477230979315901569</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>41</v>
+        <v>134</v>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E58" t="b">
         <v>0</v>
@@ -3201,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>3.38</v>
+        <v>2.25</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3212,11 +3212,9 @@
       <c r="L58" t="b">
         <v>0</v>
       </c>
-      <c r="M58" t="n">
-        <v>3</v>
-      </c>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>1</v>
@@ -3225,11 +3223,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>http://pay.emag.ro/pay/v2/</t>
+          <t>https://www.google.com</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C59" t="n">
         <v>2</v>
@@ -3241,7 +3239,7 @@
         <v>0</v>
       </c>
       <c r="F59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" t="b">
         <v>0</v>
@@ -3250,10 +3248,10 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>1.58</v>
+        <v>-0</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K59" t="b">
         <v>0</v>
@@ -3262,23 +3260,23 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>9385</v>
+        <v>10589</v>
       </c>
       <c r="N59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.microsoft.com</t>
+          <t>http://www.officialseller.vip/m/register/</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="C60" t="n">
         <v>2</v>
@@ -3290,7 +3288,7 @@
         <v>0</v>
       </c>
       <c r="F60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G60" t="b">
         <v>0</v>
@@ -3302,7 +3300,7 @@
         <v>-0</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K60" t="b">
         <v>0</v>
@@ -3311,23 +3309,23 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>12917</v>
+        <v>11</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.google.com</t>
+          <t>https://www.microsoft.com</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C61" t="n">
         <v>2</v>
@@ -3360,7 +3358,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>10589</v>
+        <v>12917</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
@@ -3421,14 +3419,14 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.github.com</t>
+          <t>https://shpeeaffilator.com/m/register?codeNumber=399158</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -3446,10 +3444,10 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>-0</v>
+        <v>3.38</v>
       </c>
       <c r="J63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K63" t="b">
         <v>0</v>
@@ -3458,13 +3456,13 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>6912</v>
+        <v>2</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -3519,11 +3517,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.apple.com</t>
+          <t>https://www.github.com</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C65" t="n">
         <v>2</v>
@@ -3547,7 +3545,7 @@
         <v>-0</v>
       </c>
       <c r="J65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K65" t="b">
         <v>0</v>
@@ -3556,7 +3554,7 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>14450</v>
+        <v>6912</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
@@ -3568,14 +3566,14 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.amazon.com</t>
+          <t>https://www.roblox.com.ml/users/246777368635/profile</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
@@ -3604,30 +3602,28 @@
       <c r="L66" t="b">
         <v>0</v>
       </c>
-      <c r="M66" t="n">
-        <v>11638</v>
-      </c>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" t="n">
         <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://apple-verify.us/help?fGK</t>
+          <t>https://www.apple.com</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67" t="b">
         <v>0</v>
@@ -3642,10 +3638,10 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>3.25</v>
+        <v>-0</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K67" t="b">
         <v>0</v>
@@ -3654,35 +3650,35 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>211</v>
+        <v>14450</v>
       </c>
       <c r="N67" t="n">
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>http://apple-verify.us/fGK</t>
+          <t>https://www.amazon.com</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68" t="b">
         <v>0</v>
       </c>
       <c r="F68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" t="b">
         <v>0</v>
@@ -3691,7 +3687,7 @@
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>3.25</v>
+        <v>-0</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -3703,23 +3699,23 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>211</v>
+        <v>11638</v>
       </c>
       <c r="N68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.netflix.com</t>
+          <t>https://www.paypal.com</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C69" t="n">
         <v>2</v>
@@ -3752,7 +3748,7 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>10532</v>
+        <v>9921</v>
       </c>
       <c r="N69" t="n">
         <v>0</v>
@@ -3813,11 +3809,11 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.reddit.com</t>
+          <t>https://www.netflix.com</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C71" t="n">
         <v>2</v>
@@ -3841,7 +3837,7 @@
         <v>-0</v>
       </c>
       <c r="J71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K71" t="b">
         <v>0</v>
@@ -3850,7 +3846,7 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>7805</v>
+        <v>10532</v>
       </c>
       <c r="N71" t="n">
         <v>0</v>
@@ -3862,7 +3858,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.paypal.com</t>
+          <t>https://www.reddit.com</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -3890,7 +3886,7 @@
         <v>-0</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72" t="b">
         <v>0</v>
@@ -3899,7 +3895,7 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>9921</v>
+        <v>7805</v>
       </c>
       <c r="N72" t="n">
         <v>0</v>
@@ -4009,11 +4005,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.bbc.com</t>
+          <t>https://www.dropbox.com</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C75" t="n">
         <v>2</v>
@@ -4046,7 +4042,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>13573</v>
+        <v>11399</v>
       </c>
       <c r="N75" t="n">
         <v>0</v>
@@ -4058,11 +4054,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.dropbox.com</t>
+          <t>https://www.bbc.com</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C76" t="n">
         <v>2</v>
@@ -4095,7 +4091,7 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>11399</v>
+        <v>13573</v>
       </c>
       <c r="N76" t="n">
         <v>0</v>
@@ -4450,11 +4446,11 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.ebay.com</t>
+          <t>https://www.adobe.com</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C84" t="n">
         <v>2</v>
@@ -4487,7 +4483,7 @@
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>11362</v>
+        <v>14544</v>
       </c>
       <c r="N84" t="n">
         <v>0</v>
@@ -4499,11 +4495,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.adobe.com</t>
+          <t>https://www.ebay.com</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C85" t="n">
         <v>2</v>
@@ -4536,7 +4532,7 @@
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>14544</v>
+        <v>11362</v>
       </c>
       <c r="N85" t="n">
         <v>0</v>
@@ -4597,11 +4593,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.airbnb.com</t>
+          <t>https://www.uber.com</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C87" t="n">
         <v>2</v>
@@ -4625,19 +4621,19 @@
         <v>-0</v>
       </c>
       <c r="J87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K87" t="b">
         <v>0</v>
       </c>
       <c r="L87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>6612</v>
+        <v>11383</v>
       </c>
       <c r="N87" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -4646,11 +4642,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.uber.com</t>
+          <t>https://www.airbnb.com</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C88" t="n">
         <v>2</v>
@@ -4674,19 +4670,19 @@
         <v>-0</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K88" t="b">
         <v>0</v>
       </c>
       <c r="L88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>11383</v>
+        <v>6612</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>

--- a/labeled_dataset.xlsx
+++ b/labeled_dataset.xlsx
@@ -637,23 +637,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.account-verification-method.vercel.app/</t>
+          <t>http://www.your-order-logistics-global-tracking.vercel.app/</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
       <c r="F5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="b">
         <v>0</v>
@@ -662,7 +662,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -675,7 +675,7 @@
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -684,32 +684,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>http://www.your-order-logistics-global-tracking.vercel.app/</t>
+          <t>https://www.roblox.ly/games/920587237/Adopt-Me?privateServerLinkCode=25143865265762886900763909739476</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
       </c>
       <c r="F6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
       </c>
       <c r="H6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>3.88</v>
+        <v>-0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -720,9 +720,11 @@
       <c r="L6" t="b">
         <v>0</v>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>60</v>
+      </c>
       <c r="N6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -731,17 +733,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://navzuri-mpt-qelfavo-c3h8me57.pages.dev/thn-yjm-uio-lkh?welcome=1235735009619786&amp;stt=1235735009619786&amp;name_stt=E-%20Commerce%20With%20Shoaib</t>
+          <t>https://www.account-verification-method.vercel.app/</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>147</v>
+        <v>51</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -756,7 +758,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>4.35</v>
+        <v>3.75</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -778,17 +780,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://roblox.com.bo/communities/488688266/</t>
+          <t>https://navzuri-mpt-qelfavo-c3h8me57.pages.dev/thn-yjm-uio-lkh?welcome=1235735009619786&amp;stt=1235735009619786&amp;name_stt=E-%20Commerce%20With%20Shoaib</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>44</v>
+        <v>147</v>
       </c>
       <c r="C8" t="n">
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -800,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>2.25</v>
+        <v>4.35</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -816,7 +818,7 @@
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -825,11 +827,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.roblox.ly/games/920587237/Adopt-Me?privateServerLinkCode=25143865265762886900763909739476</t>
+          <t>https://hadiah-shopee242.blogspot.com/</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="C9" t="n">
         <v>2</v>
@@ -847,10 +849,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>-0</v>
+        <v>3.33</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -861,11 +863,9 @@
       <c r="L9" t="b">
         <v>0</v>
       </c>
-      <c r="M9" t="n">
-        <v>60</v>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -874,23 +874,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>http://wp.pl-krajowyrejestdlugow.info.vh13647.vh.net.pl/</t>
+          <t>https://roblox.com.bo/communities/488688266/</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
       </c>
       <c r="F10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="b">
         <v>0</v>
@@ -899,7 +899,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -910,11 +910,9 @@
       <c r="L10" t="b">
         <v>0</v>
       </c>
-      <c r="M10" t="n">
-        <v>2661</v>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -923,17 +921,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://vwwv-roblox.co/users/1515798849/profile</t>
+          <t>https://shopeeid077.blogspot.com/</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -945,13 +943,13 @@
         <v>0</v>
       </c>
       <c r="H11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
@@ -959,9 +957,7 @@
       <c r="L11" t="b">
         <v>0</v>
       </c>
-      <c r="M11" t="n">
-        <v>4</v>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
         <v>3</v>
       </c>
@@ -972,14 +968,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://hadiah-shopee242.blogspot.com/</t>
+          <t>http://wp.pl-krajowyrejestdlugow.info.vh13647.vh.net.pl/</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -988,16 +984,16 @@
         <v>0</v>
       </c>
       <c r="F12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="b">
         <v>0</v>
       </c>
       <c r="H12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>3.33</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1008,9 +1004,11 @@
       <c r="L12" t="b">
         <v>0</v>
       </c>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>2661</v>
+      </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -1019,11 +1017,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.shopeeid414.blogspot.com/</t>
+          <t>http://www.shopeeid077.blogspot.com/</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C13" t="n">
         <v>3</v>
@@ -1035,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="b">
         <v>0</v>
@@ -1057,7 +1055,7 @@
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -1066,17 +1064,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://shopeeid077.blogspot.com/</t>
+          <t>https://vwwv-roblox.co/users/1515798849/profile</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
@@ -1088,13 +1086,13 @@
         <v>0</v>
       </c>
       <c r="H14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="b">
         <v>0</v>
@@ -1102,7 +1100,9 @@
       <c r="L14" t="b">
         <v>0</v>
       </c>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>4</v>
+      </c>
       <c r="N14" t="n">
         <v>3</v>
       </c>
@@ -1113,14 +1113,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://irsrefundservice.us/</t>
+          <t>https://shopeeid414.blogspot.com/</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
@@ -1149,9 +1149,7 @@
       <c r="L15" t="b">
         <v>0</v>
       </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
         <v>3</v>
       </c>
@@ -1209,11 +1207,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>http://www.shopeeid077.blogspot.com/</t>
+          <t>https://www.shopeeid414.blogspot.com/</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C17" t="n">
         <v>3</v>
@@ -1225,7 +1223,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="b">
         <v>0</v>
@@ -1247,7 +1245,7 @@
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O17" t="n">
         <v>1</v>
@@ -1256,11 +1254,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://shopeeid414.blogspot.com/</t>
+          <t>https://3x4x43x.pages.dev/</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C18" t="n">
         <v>2</v>
@@ -1281,7 +1279,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>3.1</v>
+        <v>1.56</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1350,14 +1348,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://3x4x43x.pages.dev/</t>
+          <t>https://vmi3567924.contaboserver.net/fix/sen/rena/msg.php</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -1372,10 +1370,10 @@
         <v>0</v>
       </c>
       <c r="H20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1.56</v>
+        <v>3.32</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1386,9 +1384,11 @@
       <c r="L20" t="b">
         <v>0</v>
       </c>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>3478</v>
+      </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>1</v>
@@ -1397,17 +1397,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://highpoint-02.pages.dev/?app_vl=ZYFwlWpnbWKEmLqxy5qmnnx0YsC2wa-TpaiVYsBxj2phmqOgnLFwrYw&amp;dd=USE1NzEhKCczOiAyZSUjKCA&amp;e=tomtom%2540tomorrow.com&amp;sui=%257Bsui%257D&amp;fn=Tom&amp;ln=Wiltshire%252Bbooth&amp;p=&amp;z=CHNAMER...</t>
+          <t>https://irsrefundservice.us/</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>211</v>
+        <v>28</v>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
@@ -1419,13 +1419,13 @@
         <v>0</v>
       </c>
       <c r="H21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="b">
         <v>0</v>
@@ -1433,7 +1433,9 @@
       <c r="L21" t="b">
         <v>0</v>
       </c>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
       <c r="N21" t="n">
         <v>3</v>
       </c>
@@ -1444,47 +1446,45 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://vmi3567924.contaboserver.net/fix/sen/rena/msg.php</t>
+          <t>https://highpoint-02.pages.dev/?app_vl=ZYFwlWpnbWKEmLqxy5qmnnx0YsC2wa-TpaiVYsBxj2phmqOgnLFwrYw&amp;dd=USE1NzEhKCczOiAyZSUjKCA&amp;e=tomtom%2540tomorrow.com&amp;sui=%257Bsui%257D&amp;fn=Tom&amp;ln=Wiltshire%252Bbooth&amp;p=&amp;z=CHNAMER...</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>57</v>
+        <v>211</v>
       </c>
       <c r="C22" t="n">
+        <v>6</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" t="b">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="n">
         <v>3</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="b">
-        <v>0</v>
-      </c>
-      <c r="F22" t="b">
-        <v>1</v>
-      </c>
-      <c r="G22" t="b">
-        <v>0</v>
-      </c>
-      <c r="H22" t="b">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" t="b">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>3478</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>1</v>
@@ -1540,11 +1540,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://site-tjaobqglc.godaddysites.com/</t>
+          <t>https://vht-sk.sk/Benachrichtigung/htm.html</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C24" t="n">
         <v>2</v>
@@ -1562,10 +1562,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>3.66</v>
+        <v>2.58</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -1577,10 +1577,10 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4680</v>
+        <v>1264</v>
       </c>
       <c r="N24" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>1</v>
@@ -1589,17 +1589,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://vht-sk.sk/Benachrichtigung/htm.html</t>
+          <t>https://lnk.ink/HTv47</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
@@ -1614,10 +1614,10 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>2.58</v>
+        <v>1.58</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
@@ -1626,7 +1626,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1264</v>
+        <v>496</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -1685,17 +1685,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.roblox.com.mu/games/139410450104051/Chat-with-AI-Emiko?privateServerLinkCode=79442235214644471569831337955340</t>
+          <t>https://site-tjaobqglc.godaddysites.com/</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>121</v>
+        <v>40</v>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
@@ -1707,13 +1707,13 @@
         <v>0</v>
       </c>
       <c r="H27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>-0</v>
+        <v>3.66</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="b">
         <v>0</v>
@@ -1722,10 +1722,10 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>97</v>
+        <v>4680</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O27" t="n">
         <v>1</v>
@@ -1781,17 +1781,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://lnk.ink/HTv47</t>
+          <t>https://www.roblox.com.mu/games/139410450104051/Chat-with-AI-Emiko?privateServerLinkCode=79442235214644471569831337955340</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>21</v>
+        <v>121</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
@@ -1806,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1.58</v>
+        <v>-0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1818,7 +1818,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>496</v>
+        <v>97</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -1971,32 +1971,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>http://www.drainit.vercel.app/</t>
+          <t>https://psss13.noloco.co/join/?invitationToken=1b31daf4-a815-42f6-9189-ba0ed3f67c6f</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
       </c>
       <c r="F33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="b">
         <v>0</v>
       </c>
       <c r="H33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>2.52</v>
+        <v>1.79</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2007,9 +2007,11 @@
       <c r="L33" t="b">
         <v>0</v>
       </c>
-      <c r="M33" t="inlineStr"/>
+      <c r="M33" t="n">
+        <v>1892</v>
+      </c>
       <c r="N33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>1</v>
@@ -2018,17 +2020,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://verif-mail.cloud/</t>
+          <t>https://cssm.66ghz.com/</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
@@ -2043,7 +2045,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>3.12</v>
+        <v>1.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2055,10 +2057,10 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>2</v>
+        <v>7236</v>
       </c>
       <c r="N34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>1</v>
@@ -2067,17 +2069,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>http://site-yzcbrf6j0.godaddysites.com/</t>
+          <t>http://www.drainit.vercel.app/</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" t="b">
         <v>0</v>
@@ -2092,10 +2094,10 @@
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>3.81</v>
+        <v>2.52</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="b">
         <v>0</v>
@@ -2103,11 +2105,9 @@
       <c r="L35" t="b">
         <v>0</v>
       </c>
-      <c r="M35" t="n">
-        <v>4680</v>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O35" t="n">
         <v>1</v>
@@ -2212,35 +2212,35 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.roblox.com.hr/users/1671344922/profile</t>
+          <t>http://site-yzcbrf6j0.godaddysites.com/</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" t="b">
         <v>0</v>
       </c>
       <c r="F38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="b">
         <v>0</v>
       </c>
       <c r="H38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>-0</v>
+        <v>3.81</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="b">
         <v>0</v>
@@ -2249,10 +2249,10 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>21</v>
+        <v>4680</v>
       </c>
       <c r="N38" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O38" t="n">
         <v>1</v>
@@ -2261,47 +2261,47 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.roblox.com.bi/users/748717893250/profile</t>
+          <t>https://verif-mail.cloud/</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="b">
+        <v>0</v>
+      </c>
+      <c r="F39" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" t="b">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="b">
+        <v>0</v>
+      </c>
+      <c r="L39" t="b">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>2</v>
+      </c>
+      <c r="N39" t="n">
         <v>3</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="b">
-        <v>0</v>
-      </c>
-      <c r="F39" t="b">
-        <v>1</v>
-      </c>
-      <c r="G39" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" t="b">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>-0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="b">
-        <v>0</v>
-      </c>
-      <c r="L39" t="b">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>190</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>1</v>
@@ -2310,14 +2310,14 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://goo.su/UItgh</t>
+          <t>https://www.roblox.com.hr/users/1671344922/profile</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -2335,7 +2335,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0.92</v>
+        <v>-0</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2347,10 +2347,10 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>2646</v>
+        <v>21</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O40" t="n">
         <v>1</v>
@@ -2453,14 +2453,14 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.metamsk_loogii.godaddysites.com/</t>
+          <t>https://goo.su/UItgh</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -2475,10 +2475,10 @@
         <v>0</v>
       </c>
       <c r="H43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>3.38</v>
+        <v>0.92</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2490,10 +2490,10 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>4680</v>
+        <v>2646</v>
       </c>
       <c r="N43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>1</v>
@@ -2502,17 +2502,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.uupholed-logiinus.godaddysites.com/</t>
+          <t>https://www.metamsk_loogii.godaddysites.com/</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C44" t="n">
         <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" t="b">
         <v>0</v>
@@ -2527,7 +2527,7 @@
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2551,14 +2551,14 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://1xbet-c.com/en/block</t>
+          <t>https://www.uupholed-logiinus.godaddysites.com/</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
         <v>1</v>
@@ -2573,10 +2573,10 @@
         <v>0</v>
       </c>
       <c r="H45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>2.81</v>
+        <v>3.45</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2588,10 +2588,10 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>64</v>
+        <v>4680</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O45" t="n">
         <v>1</v>
@@ -2600,11 +2600,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://1xbet-c.com/*</t>
+          <t>https://1xbet-c.com/en/block</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C46" t="n">
         <v>1</v>
@@ -2649,17 +2649,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://cssm.66ghz.com/</t>
+          <t>https://1xbet-c.com/*</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>1.5</v>
+        <v>2.81</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2686,7 +2686,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>7236</v>
+        <v>64</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -2698,17 +2698,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://psss13.noloco.co/join/?invitationToken=1b31daf4-a815-42f6-9189-ba0ed3f67c6f</t>
+          <t>https://www.roblox.com.bi/users/748717893250/profile</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E48" t="b">
         <v>0</v>
@@ -2723,7 +2723,7 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>1.79</v>
+        <v>-0</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>1892</v>
+        <v>190</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -2843,11 +2843,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://servicemaster.sviluppo.host/sclli/?LOG=24f3a45ae6194eee07570f78868ff973f93a228024c00b23a6c603f16f44550d</t>
+          <t>https://vijwiki.github.io/newhope</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>111</v>
+        <v>33</v>
       </c>
       <c r="C51" t="n">
         <v>2</v>
@@ -2865,25 +2865,23 @@
         <v>0</v>
       </c>
       <c r="H51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" t="n">
-        <v>3.03</v>
+        <v>2.13</v>
       </c>
       <c r="J51" t="n">
         <v>1</v>
       </c>
       <c r="K51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" t="b">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>3410</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O51" t="n">
         <v>1</v>
@@ -2892,11 +2890,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://vijwiki.github.io/newhope</t>
+          <t>https://servicemaster.sviluppo.host/sclli/?LOG=24f3a45ae6194eee07570f78868ff973f93a228024c00b23a6c603f16f44550d</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>33</v>
+        <v>111</v>
       </c>
       <c r="C52" t="n">
         <v>2</v>
@@ -2914,23 +2912,25 @@
         <v>0</v>
       </c>
       <c r="H52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>2.13</v>
+        <v>3.03</v>
       </c>
       <c r="J52" t="n">
         <v>1</v>
       </c>
       <c r="K52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" t="b">
-        <v>1</v>
-      </c>
-      <c r="M52" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>3410</v>
+      </c>
       <c r="N52" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>1</v>
@@ -3419,14 +3419,14 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://shpeeaffilator.com/m/register?codeNumber=399158</t>
+          <t>https://www.github.com</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -3444,10 +3444,10 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>3.38</v>
+        <v>-0</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K63" t="b">
         <v>0</v>
@@ -3456,13 +3456,13 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>2</v>
+        <v>6912</v>
       </c>
       <c r="N63" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -3517,11 +3517,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.github.com</t>
+          <t>https://www.apple.com</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C65" t="n">
         <v>2</v>
@@ -3545,7 +3545,7 @@
         <v>-0</v>
       </c>
       <c r="J65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K65" t="b">
         <v>0</v>
@@ -3554,7 +3554,7 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>6912</v>
+        <v>14450</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
@@ -3566,14 +3566,14 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.roblox.com.ml/users/246777368635/profile</t>
+          <t>https://www.amazon.com</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
@@ -3602,22 +3602,24 @@
       <c r="L66" t="b">
         <v>0</v>
       </c>
-      <c r="M66" t="inlineStr"/>
+      <c r="M66" t="n">
+        <v>11638</v>
+      </c>
       <c r="N66" t="n">
         <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.apple.com</t>
+          <t>https://www.paypal.com</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C67" t="n">
         <v>2</v>
@@ -3641,7 +3643,7 @@
         <v>-0</v>
       </c>
       <c r="J67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K67" t="b">
         <v>0</v>
@@ -3650,7 +3652,7 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>14450</v>
+        <v>9921</v>
       </c>
       <c r="N67" t="n">
         <v>0</v>
@@ -3662,11 +3664,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.amazon.com</t>
+          <t>https://www.netflix.com</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C68" t="n">
         <v>2</v>
@@ -3699,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>11638</v>
+        <v>10532</v>
       </c>
       <c r="N68" t="n">
         <v>0</v>
@@ -3711,11 +3713,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.paypal.com</t>
+          <t>https://www.linkedin.com</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C69" t="n">
         <v>2</v>
@@ -3739,7 +3741,7 @@
         <v>-0</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K69" t="b">
         <v>0</v>
@@ -3748,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>9921</v>
+        <v>8714</v>
       </c>
       <c r="N69" t="n">
         <v>0</v>
@@ -3760,11 +3762,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com</t>
+          <t>https://www.reddit.com</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C70" t="n">
         <v>2</v>
@@ -3788,7 +3790,7 @@
         <v>-0</v>
       </c>
       <c r="J70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K70" t="b">
         <v>0</v>
@@ -3797,7 +3799,7 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>8714</v>
+        <v>7805</v>
       </c>
       <c r="N70" t="n">
         <v>0</v>
@@ -3809,7 +3811,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.netflix.com</t>
+          <t>https://www.spotify.com</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3846,7 +3848,7 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>10532</v>
+        <v>7447</v>
       </c>
       <c r="N71" t="n">
         <v>0</v>
@@ -3858,11 +3860,11 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.reddit.com</t>
+          <t>https://www.dropbox.com</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C72" t="n">
         <v>2</v>
@@ -3886,7 +3888,7 @@
         <v>-0</v>
       </c>
       <c r="J72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K72" t="b">
         <v>0</v>
@@ -3895,7 +3897,7 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>7805</v>
+        <v>11399</v>
       </c>
       <c r="N72" t="n">
         <v>0</v>
@@ -3907,7 +3909,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.spotify.com</t>
+          <t>https://www.nytimes.com</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3935,7 +3937,7 @@
         <v>-0</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" t="b">
         <v>0</v>
@@ -3944,7 +3946,7 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>7447</v>
+        <v>11925</v>
       </c>
       <c r="N73" t="n">
         <v>0</v>
@@ -3956,14 +3958,14 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com</t>
+          <t>https://www.roblox.com.ml/users/246777368635/profile</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
@@ -3984,7 +3986,7 @@
         <v>-0</v>
       </c>
       <c r="J74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K74" t="b">
         <v>0</v>
@@ -3992,27 +3994,25 @@
       <c r="L74" t="b">
         <v>0</v>
       </c>
-      <c r="M74" t="n">
-        <v>11925</v>
-      </c>
+      <c r="M74" t="inlineStr"/>
       <c r="N74" t="n">
         <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.dropbox.com</t>
+          <t>https://shpeeaffilator.com/m/register?codeNumber=399158</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
@@ -4030,7 +4030,7 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>-0</v>
+        <v>3.38</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -4042,13 +4042,13 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>11399</v>
+        <v>2</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4152,11 +4152,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org</t>
+          <t>https://www.oracle.com</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C78" t="n">
         <v>2</v>
@@ -4189,7 +4189,7 @@
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>10458</v>
+        <v>13798</v>
       </c>
       <c r="N78" t="n">
         <v>0</v>
@@ -4201,11 +4201,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.oracle.com</t>
+          <t>https://www.mozilla.org</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C79" t="n">
         <v>2</v>
@@ -4238,7 +4238,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>13798</v>
+        <v>10458</v>
       </c>
       <c r="N79" t="n">
         <v>0</v>
@@ -4250,11 +4250,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.salesforce.com</t>
+          <t>https://www.adobe.com</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C80" t="n">
         <v>2</v>
@@ -4287,7 +4287,7 @@
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>10146</v>
+        <v>14544</v>
       </c>
       <c r="N80" t="n">
         <v>0</v>
@@ -4299,11 +4299,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.zoom.us</t>
+          <t>https://www.salesforce.com</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C81" t="n">
         <v>2</v>
@@ -4336,7 +4336,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>8906</v>
+        <v>10146</v>
       </c>
       <c r="N81" t="n">
         <v>0</v>
@@ -4348,11 +4348,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.shopify.com</t>
+          <t>https://www.zoom.us</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C82" t="n">
         <v>2</v>
@@ -4385,7 +4385,7 @@
         <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>7855</v>
+        <v>8906</v>
       </c>
       <c r="N82" t="n">
         <v>0</v>
@@ -4397,11 +4397,11 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.slack.com</t>
+          <t>https://www.shopify.com</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C83" t="n">
         <v>2</v>
@@ -4434,7 +4434,7 @@
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>12379</v>
+        <v>7855</v>
       </c>
       <c r="N83" t="n">
         <v>0</v>
@@ -4446,7 +4446,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.adobe.com</t>
+          <t>https://www.slack.com</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -4483,7 +4483,7 @@
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>14544</v>
+        <v>12379</v>
       </c>
       <c r="N84" t="n">
         <v>0</v>

--- a/labeled_dataset.xlsx
+++ b/labeled_dataset.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,23 +496,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>http://sp32ct-dalrex-biz-vornik-cesla.pages.dev/</t>
+          <t>https://ing-ledger-help.pages.dev/</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C2" t="n">
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
       </c>
       <c r="F2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="b">
         <v>0</v>
@@ -521,7 +521,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>4.17</v>
+        <v>3.19</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -532,9 +532,11 @@
       <c r="L2" t="b">
         <v>0</v>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>2202</v>
+      </c>
       <c r="N2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -543,23 +545,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>http://intrepid-amused-analysts--vdsbwa.replit.app/</t>
+          <t>https://retired-crimson-irxib1ps.edgeone.dev/</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
       </c>
       <c r="F3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="b">
         <v>0</v>
@@ -568,20 +570,22 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>3.85</v>
+        <v>3.67</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="b">
         <v>0</v>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>461</v>
+      </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -590,17 +594,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://xernqavi-mpt-borvexo-r8d2me61.pages.dev/</t>
+          <t>https://www.roblox.com.ml/users/255877383315/profile</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -612,10 +616,10 @@
         <v>0</v>
       </c>
       <c r="H4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>4.09</v>
+        <v>-0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -626,9 +630,11 @@
       <c r="L4" t="b">
         <v>0</v>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>354</v>
+      </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -637,32 +643,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>http://www.your-order-logistics-global-tracking.vercel.app/</t>
+          <t>https://s4w.in/ezxWm</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
       <c r="F5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="b">
         <v>0</v>
       </c>
       <c r="H5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>3.88</v>
+        <v>1.58</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -673,9 +679,11 @@
       <c r="L5" t="b">
         <v>0</v>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>6877</v>
+      </c>
       <c r="N5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -684,23 +692,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.roblox.ly/games/920587237/Adopt-Me?privateServerLinkCode=25143865265762886900763909739476</t>
+          <t>http://express-dhl-production.up.railway.app/</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>101</v>
+        <v>45</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
       </c>
       <c r="F6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
@@ -709,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-0</v>
+        <v>3.82</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -721,10 +729,10 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>60</v>
+        <v>2600</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -733,17 +741,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.account-verification-method.vercel.app/</t>
+          <t>https://www.roblox.com.mu/users/6151511912/profile</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C7" t="n">
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -755,10 +763,10 @@
         <v>0</v>
       </c>
       <c r="H7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>3.75</v>
+        <v>-0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -769,9 +777,11 @@
       <c r="L7" t="b">
         <v>0</v>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>98</v>
+      </c>
       <c r="N7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -780,17 +790,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://navzuri-mpt-qelfavo-c3h8me57.pages.dev/thn-yjm-uio-lkh?welcome=1235735009619786&amp;stt=1235735009619786&amp;name_stt=E-%20Commerce%20With%20Shoaib</t>
+          <t>https://selector1._domainkey.135nb.top/</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>147</v>
+        <v>39</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -802,10 +812,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>4.35</v>
+        <v>2.95</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -816,9 +826,11 @@
       <c r="L8" t="b">
         <v>0</v>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>310</v>
+      </c>
       <c r="N8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -827,17 +839,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://hadiah-shopee242.blogspot.com/</t>
+          <t>https://meta-verified-blueticks-fb12.vercel.app/privacy-centers.html</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -852,7 +864,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>3.33</v>
+        <v>3.97</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -863,9 +875,11 @@
       <c r="L9" t="b">
         <v>0</v>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>2420</v>
+      </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -874,17 +888,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://roblox.com.bo/communities/488688266/</t>
+          <t>https://haseebansaripk4-web.github.io/journex/</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C10" t="n">
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -896,10 +910,10 @@
         <v>0</v>
       </c>
       <c r="H10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>2.25</v>
+        <v>3.54</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -910,9 +924,11 @@
       <c r="L10" t="b">
         <v>0</v>
       </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>4936</v>
+      </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -921,17 +937,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://shopeeid077.blogspot.com/</t>
+          <t>https://device-official-app-live.pages.dev/</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -946,7 +962,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>3.1</v>
+        <v>3.36</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -968,14 +984,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>http://wp.pl-krajowyrejestdlugow.info.vh13647.vh.net.pl/</t>
+          <t>https://aryansinha23.github.io/banking-app1/</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -984,16 +1000,16 @@
         <v>0</v>
       </c>
       <c r="F12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="b">
         <v>0</v>
       </c>
       <c r="H12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>3.02</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1005,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2661</v>
+        <v>4936</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -1017,23 +1033,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>http://www.shopeeid077.blogspot.com/</t>
+          <t>https://leboncoin-4dah.vercel.app/</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
       </c>
       <c r="F13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="b">
         <v>0</v>
@@ -1042,7 +1058,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1055,7 +1071,7 @@
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -1064,17 +1080,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://vwwv-roblox.co/users/1515798849/profile</t>
+          <t>https://malimasak.net/Giris/e-Devlet-Sifresi</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
@@ -1089,10 +1105,10 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2.91</v>
+        <v>2.42</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="b">
         <v>0</v>
@@ -1113,23 +1129,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://shopeeid414.blogspot.com/</t>
+          <t>http://www.uuu-holdlog.godaddysites.com/</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
       </c>
       <c r="F15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="b">
         <v>0</v>
@@ -1138,7 +1154,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>3.1</v>
+        <v>2.66</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1149,9 +1165,11 @@
       <c r="L15" t="b">
         <v>0</v>
       </c>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>4681</v>
+      </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
@@ -1160,32 +1178,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.robiox.com.gr/users/8880414661/profile</t>
+          <t>http://www.leboncoin-4dah.vercel.app/</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
       </c>
       <c r="F16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="b">
         <v>0</v>
       </c>
       <c r="H16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>-0</v>
+        <v>3.52</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1198,7 +1216,7 @@
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O16" t="n">
         <v>1</v>
@@ -1207,14 +1225,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.shopeeid414.blogspot.com/</t>
+          <t>https://www.roblox.et/users/6300126234/profile</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -1229,10 +1247,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>3.1</v>
+        <v>-0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1245,7 +1263,7 @@
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>1</v>
@@ -1254,14 +1272,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://3x4x43x.pages.dev/</t>
+          <t>https://mtoken.space/</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1276,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1.56</v>
+        <v>2.58</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1290,7 +1308,9 @@
       <c r="L18" t="b">
         <v>0</v>
       </c>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
       <c r="N18" t="n">
         <v>3</v>
       </c>
@@ -1301,14 +1321,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>http://www.robloxc.com.es/users/1539346212/profile/</t>
+          <t>https://u.to/uQywIg</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1317,7 +1337,7 @@
         <v>0</v>
       </c>
       <c r="F19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="b">
         <v>0</v>
@@ -1337,9 +1357,11 @@
       <c r="L19" t="b">
         <v>0</v>
       </c>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>1760</v>
+      </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>1</v>
@@ -1348,14 +1370,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://vmi3567924.contaboserver.net/fix/sen/rena/msg.php</t>
+          <t>http://staffadmin.vip/</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -1364,7 +1386,7 @@
         <v>0</v>
       </c>
       <c r="F20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="b">
         <v>0</v>
@@ -1373,7 +1395,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>3.32</v>
+        <v>2.92</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1385,10 +1407,10 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3478</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O20" t="n">
         <v>1</v>
@@ -1397,11 +1419,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://irsrefundservice.us/</t>
+          <t>https://mtoken.space/download</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
@@ -1422,10 +1444,10 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>3.16</v>
+        <v>2.58</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="b">
         <v>0</v>
@@ -1446,17 +1468,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://highpoint-02.pages.dev/?app_vl=ZYFwlWpnbWKEmLqxy5qmnnx0YsC2wa-TpaiVYsBxj2phmqOgnLFwrYw&amp;dd=USE1NzEhKCczOiAyZSUjKCA&amp;e=tomtom%2540tomorrow.com&amp;sui=%257Bsui%257D&amp;fn=Tom&amp;ln=Wiltshire%252Bbooth&amp;p=&amp;z=CHNAMER...</t>
+          <t>https://facilities-information.com/s/63BZGFSVBWSFCDX7Y9/584dd8/90eab167-7429-489f-99f6-ce86e8d0d81a/</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>211</v>
+        <v>100</v>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
@@ -1468,10 +1490,10 @@
         <v>0</v>
       </c>
       <c r="H22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1482,9 +1504,11 @@
       <c r="L22" t="b">
         <v>0</v>
       </c>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>5063</v>
+      </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>1</v>
@@ -1493,45 +1517,45 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://ledger--livedesktop--welcome.pages.dev/</t>
+          <t>http://security-server-landing-page--ninnyjuju.replit.app/</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="C23" t="n">
         <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
       </c>
       <c r="F23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="b">
         <v>0</v>
       </c>
       <c r="H23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>3.66</v>
+        <v>3.86</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
         <v>1</v>
@@ -1540,17 +1564,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://vht-sk.sk/Benachrichtigung/htm.html</t>
+          <t>https://cffandai.ltbjwz.workers.dev/</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
@@ -1565,10 +1589,10 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="b">
         <v>0</v>
@@ -1576,9 +1600,7 @@
       <c r="L24" t="b">
         <v>0</v>
       </c>
-      <c r="M24" t="n">
-        <v>1264</v>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
         <v>0</v>
       </c>
@@ -1589,17 +1611,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://lnk.ink/HTv47</t>
+          <t>https://sumitmandalwebdev-afk.github.io/Amazon-clone/</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
@@ -1611,10 +1633,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>1.58</v>
+        <v>3.88</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1626,10 +1648,10 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>496</v>
+        <v>4936</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O25" t="n">
         <v>1</v>
@@ -1638,7 +1660,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://aiman54321.github.io/netflix-clone</t>
+          <t>https://gabimen1232007-cmd.github.io/news/</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1663,7 +1685,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>3.12</v>
+        <v>3.84</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1674,9 +1696,11 @@
       <c r="L26" t="b">
         <v>0</v>
       </c>
-      <c r="M26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>4936</v>
+      </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O26" t="n">
         <v>1</v>
@@ -1685,17 +1709,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://site-tjaobqglc.godaddysites.com/</t>
+          <t>https://lingering-cherry-263d.fayrepleasantwreu5z002t.workers.dev/help</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
@@ -1707,13 +1731,13 @@
         <v>0</v>
       </c>
       <c r="H27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>3.66</v>
+        <v>3.69</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="b">
         <v>0</v>
@@ -1721,11 +1745,9 @@
       <c r="L27" t="b">
         <v>0</v>
       </c>
-      <c r="M27" t="n">
-        <v>4680</v>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
         <v>1</v>
@@ -1734,32 +1756,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>http://www.mclarencar.ebaymclaren-austin.eventshouse.app/</t>
+          <t>https://www.increasefollowersforinstagram.blogspot.com/</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
       </c>
       <c r="F28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="b">
         <v>0</v>
       </c>
       <c r="H28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>-0</v>
+        <v>3.65</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1770,9 +1792,11 @@
       <c r="L28" t="b">
         <v>0</v>
       </c>
-      <c r="M28" t="inlineStr"/>
+      <c r="M28" t="n">
+        <v>9539</v>
+      </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
@@ -1781,17 +1805,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.roblox.com.mu/games/139410450104051/Chat-with-AI-Emiko?privateServerLinkCode=79442235214644471569831337955340</t>
+          <t>https://ranika2008.github.io/finance_ledger/</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
@@ -1803,10 +1827,10 @@
         <v>0</v>
       </c>
       <c r="H29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>-0</v>
+        <v>2.92</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1818,10 +1842,10 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>97</v>
+        <v>4936</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O29" t="n">
         <v>1</v>
@@ -1830,17 +1854,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://d2cx10dsi4ptcz.cloudfront.net/</t>
+          <t>https://chatbot-activationid120956.vercel.app/live</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C30" t="n">
         <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
@@ -1852,10 +1876,10 @@
         <v>0</v>
       </c>
       <c r="H30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>3.52</v>
+        <v>3.87</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1868,7 +1892,7 @@
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O30" t="n">
         <v>1</v>
@@ -1877,23 +1901,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>http://www.mclarenf1car.ebaymclaren-austin.eventshouse.app/</t>
+          <t>https://fls-a2ba3ea2-2297-46d0-bceb-50440331a6c9.laravel.cloud/dom/DOMAIN.html</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
       </c>
       <c r="F31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="b">
         <v>0</v>
@@ -1902,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>-0</v>
+        <v>3.96</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1913,9 +1937,11 @@
       <c r="L31" t="b">
         <v>0</v>
       </c>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>3362</v>
+      </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O31" t="n">
         <v>1</v>
@@ -1924,45 +1950,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>http://www.hofmemorabilia.ebaymclaren-austin.eventshouse.app/</t>
+          <t>http://allegrolokalnie.72893752.xyz/oferta/iphone-15-pro-max-256-gb-white-titanium/</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>7</v>
+      </c>
+      <c r="E32" t="b">
+        <v>0</v>
+      </c>
+      <c r="F32" t="b">
+        <v>0</v>
+      </c>
+      <c r="G32" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" t="b">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="b">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" t="n">
         <v>4</v>
-      </c>
-      <c r="D32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" t="b">
-        <v>0</v>
-      </c>
-      <c r="F32" t="b">
-        <v>0</v>
-      </c>
-      <c r="G32" t="b">
-        <v>0</v>
-      </c>
-      <c r="H32" t="b">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>-0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="b">
-        <v>0</v>
-      </c>
-      <c r="L32" t="b">
-        <v>0</v>
-      </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="n">
-        <v>1</v>
       </c>
       <c r="O32" t="n">
         <v>1</v>
@@ -1971,17 +1999,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://psss13.noloco.co/join/?invitationToken=1b31daf4-a815-42f6-9189-ba0ed3f67c6f</t>
+          <t>https://rbcode.net/v/b1ac0ecb25f5419af70cb65ce036b2e8</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
@@ -1996,7 +2024,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>1.79</v>
+        <v>2.58</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2008,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1892</v>
+        <v>81</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -2020,14 +2048,14 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://cssm.66ghz.com/</t>
+          <t>https://www.mettamusksign0inx.godaddysites.com/</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -2042,10 +2070,10 @@
         <v>0</v>
       </c>
       <c r="H34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2057,10 +2085,10 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>7236</v>
+        <v>4681</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O34" t="n">
         <v>1</v>
@@ -2069,23 +2097,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>http://www.drainit.vercel.app/</t>
+          <t>https://siamjjk7-star.github.io/Nothing-</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E35" t="b">
         <v>0</v>
       </c>
       <c r="F35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" t="b">
         <v>0</v>
@@ -2094,7 +2122,7 @@
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>2.52</v>
+        <v>3.24</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2105,9 +2133,11 @@
       <c r="L35" t="b">
         <v>0</v>
       </c>
-      <c r="M35" t="inlineStr"/>
+      <c r="M35" t="n">
+        <v>4936</v>
+      </c>
       <c r="N35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O35" t="n">
         <v>1</v>
@@ -2116,11 +2146,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>http://staging.d2vcbrxbzugw3i.amplifyapp.com/</t>
+          <t>https://www.juno65.godaddysites.com/</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C36" t="n">
         <v>3</v>
@@ -2132,7 +2162,7 @@
         <v>0</v>
       </c>
       <c r="F36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" t="b">
         <v>0</v>
@@ -2141,7 +2171,7 @@
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>4.06</v>
+        <v>2.58</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2152,9 +2182,11 @@
       <c r="L36" t="b">
         <v>0</v>
       </c>
-      <c r="M36" t="inlineStr"/>
+      <c r="M36" t="n">
+        <v>4681</v>
+      </c>
       <c r="N36" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O36" t="n">
         <v>1</v>
@@ -2163,14 +2195,14 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.roblox.com.hr/users/3904040857/profile</t>
+          <t>https://juno65.godaddysites.com/</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -2185,10 +2217,10 @@
         <v>0</v>
       </c>
       <c r="H37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>-0</v>
+        <v>2.58</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2200,7 +2232,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>21</v>
+        <v>4681</v>
       </c>
       <c r="N37" t="n">
         <v>3</v>
@@ -2212,14 +2244,14 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>http://site-yzcbrf6j0.godaddysites.com/</t>
+          <t>https://f005.backblazeb2.com/file/Review-document/index1.html</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D38" t="n">
         <v>1</v>
@@ -2228,19 +2260,19 @@
         <v>0</v>
       </c>
       <c r="F38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="b">
         <v>0</v>
       </c>
       <c r="H38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>3.81</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="b">
         <v>0</v>
@@ -2249,10 +2281,10 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>4680</v>
+        <v>3713</v>
       </c>
       <c r="N38" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>1</v>
@@ -2261,17 +2293,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://verif-mail.cloud/</t>
+          <t>https://auedc.pages.dev/</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" t="b">
         <v>0</v>
@@ -2283,10 +2315,10 @@
         <v>0</v>
       </c>
       <c r="H39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>3.12</v>
+        <v>2.32</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2297,9 +2329,7 @@
       <c r="L39" t="b">
         <v>0</v>
       </c>
-      <c r="M39" t="n">
-        <v>2</v>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="n">
         <v>3</v>
       </c>
@@ -2310,17 +2340,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.roblox.com.hr/users/1671344922/profile</t>
+          <t>https://phantom-wollwt-us.wasmer.app/</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E40" t="b">
         <v>0</v>
@@ -2335,7 +2365,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>-0</v>
+        <v>3.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2346,9 +2376,7 @@
       <c r="L40" t="b">
         <v>0</v>
       </c>
-      <c r="M40" t="n">
-        <v>21</v>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="n">
         <v>3</v>
       </c>
@@ -2359,18 +2387,18 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.collectableswall.ebaymclaren-austin.eventshouse.app/</t>
+          <t>https://sp30ct-kumex-biz-zavel-radix.pages.dev/</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="n">
         <v>4</v>
       </c>
-      <c r="D41" t="n">
-        <v>1</v>
-      </c>
       <c r="E41" t="b">
         <v>0</v>
       </c>
@@ -2381,10 +2409,10 @@
         <v>0</v>
       </c>
       <c r="H41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>-0</v>
+        <v>4.16</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2397,7 +2425,7 @@
       </c>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O41" t="n">
         <v>1</v>
@@ -2406,32 +2434,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>http://7t60y-ix3-chlx-vi11r-11-09-2026-hh.pages.dev/</t>
+          <t>https://webmail-oauth.lygrunfeng.com/manager/26/0b3f80fb-3440-4ced-9341-a0aa52c060d1</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="C42" t="n">
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E42" t="b">
         <v>0</v>
       </c>
       <c r="F42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" t="b">
         <v>0</v>
       </c>
       <c r="H42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>3.76</v>
+        <v>3.55</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2442,9 +2470,11 @@
       <c r="L42" t="b">
         <v>0</v>
       </c>
-      <c r="M42" t="inlineStr"/>
+      <c r="M42" t="n">
+        <v>6773</v>
+      </c>
       <c r="N42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O42" t="n">
         <v>1</v>
@@ -2453,17 +2483,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://goo.su/UItgh</t>
+          <t>https://adammuftau-cmd.github.io/susu_app/</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
@@ -2475,10 +2505,10 @@
         <v>0</v>
       </c>
       <c r="H43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>0.92</v>
+        <v>2.84</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2490,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>2646</v>
+        <v>4936</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O43" t="n">
         <v>1</v>
@@ -2502,11 +2532,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.metamsk_loogii.godaddysites.com/</t>
+          <t>https://www.roblox.com.hr/users/1085927564/profile</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C44" t="n">
         <v>3</v>
@@ -2524,10 +2554,10 @@
         <v>0</v>
       </c>
       <c r="H44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>3.38</v>
+        <v>-0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2539,7 +2569,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>4680</v>
+        <v>22</v>
       </c>
       <c r="N44" t="n">
         <v>3</v>
@@ -2551,17 +2581,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.uupholed-logiinus.godaddysites.com/</t>
+          <t>https://meta-verified-blueticks-fb5.vercel.app/privacy-centers.html</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="C45" t="n">
         <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E45" t="b">
         <v>0</v>
@@ -2576,7 +2606,7 @@
         <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>3.45</v>
+        <v>3.88</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2587,11 +2617,9 @@
       <c r="L45" t="b">
         <v>0</v>
       </c>
-      <c r="M45" t="n">
-        <v>4680</v>
-      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O45" t="n">
         <v>1</v>
@@ -2600,17 +2628,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://1xbet-c.com/en/block</t>
+          <t>https://8zerytt9lboomi1eygs.vercel.app/gsnfns43e5rhbwaerdfsvb.html</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
@@ -2622,10 +2650,10 @@
         <v>0</v>
       </c>
       <c r="H46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>2.81</v>
+        <v>3.83</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2636,11 +2664,9 @@
       <c r="L46" t="b">
         <v>0</v>
       </c>
-      <c r="M46" t="n">
-        <v>64</v>
-      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O46" t="n">
         <v>1</v>
@@ -2649,17 +2675,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://1xbet-c.com/*</t>
+          <t>https://8zerytt9lboomi1eygs.vercel.app/gsnfns43e5rhbwaerdfsvb</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
@@ -2671,10 +2697,10 @@
         <v>0</v>
       </c>
       <c r="H47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>2.81</v>
+        <v>3.83</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2685,11 +2711,9 @@
       <c r="L47" t="b">
         <v>0</v>
       </c>
-      <c r="M47" t="n">
-        <v>64</v>
-      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O47" t="n">
         <v>1</v>
@@ -2698,14 +2722,14 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.roblox.com.bi/users/748717893250/profile</t>
+          <t>https://ejtgs7hmgzc00c87y3r.vercel.app/nsvw35re4hbarefsdbvzxcv</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -2720,10 +2744,10 @@
         <v>0</v>
       </c>
       <c r="H48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>-0</v>
+        <v>3.83</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2734,11 +2758,9 @@
       <c r="L48" t="b">
         <v>0</v>
       </c>
-      <c r="M48" t="n">
-        <v>190</v>
-      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O48" t="n">
         <v>1</v>
@@ -2747,17 +2769,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://account-verification-method.vercel.app/</t>
+          <t>https://ejtgs7hmgzc00c87y3r.vercel.app/nsvw35re4hbarefsdbvzxcv.html</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E49" t="b">
         <v>0</v>
@@ -2772,7 +2794,7 @@
         <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>3.75</v>
+        <v>3.83</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2794,17 +2816,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://start-linkedin.com/</t>
+          <t>https://nfyenkryj6v4oeqwluc.vercel.app/bdsfbw35erbasefdbsdfbn354b</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" t="b">
         <v>0</v>
@@ -2816,10 +2838,10 @@
         <v>0</v>
       </c>
       <c r="H50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>3.38</v>
+        <v>3.93</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2830,11 +2852,9 @@
       <c r="L50" t="b">
         <v>0</v>
       </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O50" t="n">
         <v>1</v>
@@ -2843,14 +2863,14 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://vijwiki.github.io/newhope</t>
+          <t>https://nfyenkryj6v4oeqwluc.vercel.app/bdsfbw35erbasefdbsdfbn354b.html</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -2868,16 +2888,16 @@
         <v>1</v>
       </c>
       <c r="I51" t="n">
-        <v>2.13</v>
+        <v>3.93</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" t="b">
         <v>0</v>
       </c>
       <c r="L51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="n">
@@ -2890,17 +2910,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://servicemaster.sviluppo.host/sclli/?LOG=24f3a45ae6194eee07570f78868ff973f93a228024c00b23a6c603f16f44550d</t>
+          <t>https://khcnoydz4bnrl-hbk11.vercel.app/xcvgh5iuxafyu1xcv</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>111</v>
+        <v>56</v>
       </c>
       <c r="C52" t="n">
         <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" t="b">
         <v>0</v>
@@ -2912,25 +2932,23 @@
         <v>0</v>
       </c>
       <c r="H52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>3.03</v>
+        <v>3.72</v>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" t="b">
         <v>0</v>
       </c>
-      <c r="M52" t="n">
-        <v>3410</v>
-      </c>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O52" t="n">
         <v>1</v>
@@ -2939,17 +2957,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://xernqavi-mpt-borvexo-r8d2me61.pages.dev/thn-yjm-uio-lkh?welcome=164156410116085&amp;stt=164156410116085&amp;name_stt=Centro%20Legal</t>
+          <t>https://dev-nasrullah-pk.github.io/spotify-web-player-clone</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="C53" t="n">
         <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E53" t="b">
         <v>0</v>
@@ -2964,7 +2982,7 @@
         <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>4.09</v>
+        <v>3.62</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2975,7 +2993,9 @@
       <c r="L53" t="b">
         <v>0</v>
       </c>
-      <c r="M53" t="inlineStr"/>
+      <c r="M53" t="n">
+        <v>4936</v>
+      </c>
       <c r="N53" t="n">
         <v>6</v>
       </c>
@@ -2986,17 +3006,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://iahnp-g5p-0jym-r1nwm-11-09-2026-hh.pages.dev/</t>
+          <t>https://khcnoydz4bnrl-hbk11.vercel.app/xcvgh5iuxafyu1xcv.html</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E54" t="b">
         <v>0</v>
@@ -3011,7 +3031,7 @@
         <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>3.85</v>
+        <v>3.72</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -3033,17 +3053,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://your-order-logistics-global-tracking.vercel.app/</t>
+          <t>https://v83cia3cumugxocgu10.vercel.app/bdsfbw35erbasefdbsdfbn354b</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C55" t="n">
         <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
@@ -3058,7 +3078,7 @@
         <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>3.88</v>
+        <v>3.54</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -3080,11 +3100,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>http://ligjerccobstartt.webflow.io/</t>
+          <t>https://sanath2700.github.io/NetflixRegionFix/</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C56" t="n">
         <v>2</v>
@@ -3096,16 +3116,16 @@
         <v>0</v>
       </c>
       <c r="F56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" t="b">
         <v>0</v>
       </c>
       <c r="H56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>3.45</v>
+        <v>2.92</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3116,9 +3136,11 @@
       <c r="L56" t="b">
         <v>0</v>
       </c>
-      <c r="M56" t="inlineStr"/>
+      <c r="M56" t="n">
+        <v>4936</v>
+      </c>
       <c r="N56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O56" t="n">
         <v>1</v>
@@ -3127,17 +3149,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://cerexedwardsteamword2136.myclickfunnels.com/kjjjjkjklkkljljkjkkkl</t>
+          <t>https://ahmadalidev01.github.io/netflix-clone</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="C57" t="n">
         <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" t="b">
         <v>0</v>
@@ -3149,22 +3171,22 @@
         <v>0</v>
       </c>
       <c r="H57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" t="n">
-        <v>3.69</v>
+        <v>3.18</v>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" t="b">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3614</v>
+        <v>4936</v>
       </c>
       <c r="N57" t="n">
         <v>3</v>
@@ -3176,17 +3198,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://roblox.com.bo/games/80576062127494/HOT-Catgirl-Obby-Surprise-at-the-end?privateServerLinkCode=72838528769061477230979315901569</t>
+          <t>https://malxfnty.twilightparadox.com/xverify/signin?verify=pagesprocess_64934</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="C58" t="n">
         <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E58" t="b">
         <v>0</v>
@@ -3201,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3212,7 +3234,9 @@
       <c r="L58" t="b">
         <v>0</v>
       </c>
-      <c r="M58" t="inlineStr"/>
+      <c r="M58" t="n">
+        <v>8447</v>
+      </c>
       <c r="N58" t="n">
         <v>0</v>
       </c>
@@ -3223,11 +3247,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.google.com</t>
+          <t>https://malxfnty.twilightparadox.com/?403verify</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="C59" t="n">
         <v>2</v>
@@ -3248,10 +3272,10 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>-0</v>
+        <v>3</v>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K59" t="b">
         <v>0</v>
@@ -3260,23 +3284,23 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>10589</v>
+        <v>8447</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>http://www.officialseller.vip/m/register/</t>
+          <t>https://_domainkey.135nb.top/</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C60" t="n">
         <v>2</v>
@@ -3288,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="F60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60" t="b">
         <v>0</v>
@@ -3297,7 +3321,7 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>-0</v>
+        <v>3.32</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3309,10 +3333,10 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>11</v>
+        <v>310</v>
       </c>
       <c r="N60" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>1</v>
@@ -3321,11 +3345,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.microsoft.com</t>
+          <t>https://tavlok.horse/ll/gree.html</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C61" t="n">
         <v>2</v>
@@ -3346,10 +3370,10 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>-0</v>
+        <v>2.58</v>
       </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K61" t="b">
         <v>0</v>
@@ -3358,29 +3382,29 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>12917</v>
+        <v>207</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.python.org</t>
+          <t>https://join-coin-eng.zapier.app/go</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="C62" t="n">
         <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E62" t="b">
         <v>0</v>
@@ -3395,10 +3419,10 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>-0</v>
+        <v>2.87</v>
       </c>
       <c r="J62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K62" t="b">
         <v>0</v>
@@ -3407,23 +3431,23 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>11492</v>
+        <v>1453</v>
       </c>
       <c r="N62" t="n">
         <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.github.com</t>
+          <t>http://ww547.colnbasee.us/?tkn=19vnMT3S</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="C63" t="n">
         <v>2</v>
@@ -3435,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="F63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G63" t="b">
         <v>0</v>
@@ -3444,10 +3468,10 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>-0</v>
+        <v>1.92</v>
       </c>
       <c r="J63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K63" t="b">
         <v>0</v>
@@ -3456,26 +3480,26 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>6912</v>
+        <v>794</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.wikipedia.org</t>
+          <t>https://minimonsterrrrr.github.io/projet2.github.io/</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -3490,13 +3514,13 @@
         <v>0</v>
       </c>
       <c r="H64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64" t="n">
-        <v>-0</v>
+        <v>2.73</v>
       </c>
       <c r="J64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K64" t="b">
         <v>0</v>
@@ -3505,29 +3529,29 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>9373</v>
+        <v>4936</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.apple.com</t>
+          <t>https://clearpfzone.s3.eu-north-1.amazonaws.com/pdfurl.html</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E65" t="b">
         <v>0</v>
@@ -3542,10 +3566,10 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>-0</v>
+        <v>3.28</v>
       </c>
       <c r="J65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K65" t="b">
         <v>0</v>
@@ -3554,29 +3578,29 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>14450</v>
+        <v>7696</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.amazon.com</t>
+          <t>https://mervoro-mpt-belfavi-a1h9fe57.pages.dev/thn-yjm-uio-lkh?welcome=106348824461361&amp;stt=106348824461361&amp;name_stt=Plastics%20&amp;%20Rubber%20Indonesia</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>22</v>
+        <v>149</v>
       </c>
       <c r="C66" t="n">
         <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E66" t="b">
         <v>0</v>
@@ -3588,10 +3612,10 @@
         <v>0</v>
       </c>
       <c r="H66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" t="n">
-        <v>-0</v>
+        <v>4.04</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -3603,35 +3627,35 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>11638</v>
+        <v>2202</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.paypal.com</t>
+          <t>http://ext-coinbais-us.wasmer.app/</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C67" t="n">
         <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E67" t="b">
         <v>0</v>
       </c>
       <c r="F67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G67" t="b">
         <v>0</v>
@@ -3640,7 +3664,7 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>-0</v>
+        <v>3.51</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -3652,29 +3676,29 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>9921</v>
+        <v>2888</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.netflix.com</t>
+          <t>https://alisafwat2011-source.github.io/Facebook</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="C68" t="n">
         <v>2</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" t="b">
         <v>0</v>
@@ -3686,10 +3710,10 @@
         <v>0</v>
       </c>
       <c r="H68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" t="n">
-        <v>-0</v>
+        <v>3.88</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -3701,35 +3725,35 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>10532</v>
+        <v>4936</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com</t>
+          <t>http://wetransfer-east856-dppejjz76yzz.edgeone.dev/</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="C69" t="n">
         <v>2</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E69" t="b">
         <v>0</v>
       </c>
       <c r="F69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G69" t="b">
         <v>0</v>
@@ -3738,10 +3762,10 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>-0</v>
+        <v>4.03</v>
       </c>
       <c r="J69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K69" t="b">
         <v>0</v>
@@ -3750,29 +3774,29 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>8714</v>
+        <v>461</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.reddit.com</t>
+          <t>https://sana44092241-collab.github.io/Amazon-Clone</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="C70" t="n">
         <v>2</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E70" t="b">
         <v>0</v>
@@ -3784,13 +3808,13 @@
         <v>0</v>
       </c>
       <c r="H70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70" t="n">
-        <v>-0</v>
+        <v>3.54</v>
       </c>
       <c r="J70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K70" t="b">
         <v>0</v>
@@ -3799,29 +3823,29 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>7805</v>
+        <v>4936</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.spotify.com</t>
+          <t>https://io-trust.github.io/en-es</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C71" t="n">
         <v>2</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E71" t="b">
         <v>0</v>
@@ -3833,10 +3857,10 @@
         <v>0</v>
       </c>
       <c r="H71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I71" t="n">
-        <v>-0</v>
+        <v>2.75</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -3848,26 +3872,26 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>7447</v>
+        <v>4936</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.dropbox.com</t>
+          <t>https://www.roblox.com.hr/users/6790651137/profile</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
@@ -3897,29 +3921,29 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>11399</v>
+        <v>22</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com</t>
+          <t>https://m.ahv3ctpms4e.timeforsurveys.com/s/63BZGFSVBWSFCDX7Y9/584dd8/90eab167-7429-489f-99f6-ce86e8d0d81a/</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>23</v>
+        <v>106</v>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E73" t="b">
         <v>0</v>
@@ -3937,7 +3961,7 @@
         <v>-0</v>
       </c>
       <c r="J73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K73" t="b">
         <v>0</v>
@@ -3946,23 +3970,23 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>11925</v>
+        <v>3956</v>
       </c>
       <c r="N73" t="n">
         <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.roblox.com.ml/users/246777368635/profile</t>
+          <t>https://www.roblox.com.hr/users/2180432315/profile</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C74" t="n">
         <v>3</v>
@@ -3994,9 +4018,11 @@
       <c r="L74" t="b">
         <v>0</v>
       </c>
-      <c r="M74" t="inlineStr"/>
+      <c r="M74" t="n">
+        <v>22</v>
+      </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O74" t="n">
         <v>1</v>
@@ -4005,17 +4031,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://shpeeaffilator.com/m/register?codeNumber=399158</t>
+          <t>https://devoted-rose-2zod17zj.edgeone.dev/home</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E75" t="b">
         <v>0</v>
@@ -4030,7 +4056,7 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>3.38</v>
+        <v>3.52</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -4041,9 +4067,7 @@
       <c r="L75" t="b">
         <v>0</v>
       </c>
-      <c r="M75" t="n">
-        <v>2</v>
-      </c>
+      <c r="M75" t="inlineStr"/>
       <c r="N75" t="n">
         <v>3</v>
       </c>
@@ -4054,17 +4078,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.bbc.com</t>
+          <t>https://stuttrup.github.io/Spencers-task-organizer/</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="C76" t="n">
         <v>2</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E76" t="b">
         <v>0</v>
@@ -4076,10 +4100,10 @@
         <v>0</v>
       </c>
       <c r="H76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76" t="n">
-        <v>-0</v>
+        <v>2.16</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -4091,29 +4115,29 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>13573</v>
+        <v>4936</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.cloudflare.com</t>
+          <t>https://s4w.in/roblox-com-users-21804232315-profile</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E77" t="b">
         <v>0</v>
@@ -4128,7 +4152,7 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>-0</v>
+        <v>1.58</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -4140,44 +4164,44 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>6415</v>
+        <v>6877</v>
       </c>
       <c r="N77" t="n">
         <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.oracle.com</t>
+          <t>http://sp30ct-zemik-biz-kavel-nadex.pages.dev/</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="C78" t="n">
         <v>2</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E78" t="b">
         <v>0</v>
       </c>
       <c r="F78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" t="b">
         <v>0</v>
       </c>
       <c r="H78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78" t="n">
-        <v>-0</v>
+        <v>4.07</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -4188,24 +4212,22 @@
       <c r="L78" t="b">
         <v>0</v>
       </c>
-      <c r="M78" t="n">
-        <v>13798</v>
-      </c>
+      <c r="M78" t="inlineStr"/>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org</t>
+          <t>https://www.smswt.in/</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C79" t="n">
         <v>2</v>
@@ -4238,26 +4260,26 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>10458</v>
+        <v>1316</v>
       </c>
       <c r="N79" t="n">
         <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.adobe.com</t>
+          <t>https://goo.su/U5WFdQ</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>21</v>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
@@ -4275,7 +4297,7 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>-0</v>
+        <v>0.92</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -4287,23 +4309,23 @@
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>14544</v>
+        <v>2647</v>
       </c>
       <c r="N80" t="n">
         <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.salesforce.com</t>
+          <t>https://gamiiinlogio.godaddysites.com/</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C81" t="n">
         <v>2</v>
@@ -4321,10 +4343,10 @@
         <v>0</v>
       </c>
       <c r="H81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I81" t="n">
-        <v>-0</v>
+        <v>2.58</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -4336,26 +4358,26 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>10146</v>
+        <v>4681</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.zoom.us</t>
+          <t>https://www.gamiiinlogio.godaddysites.com/</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
@@ -4370,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="H82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I82" t="n">
-        <v>-0</v>
+        <v>2.58</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -4385,26 +4407,26 @@
         <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>8906</v>
+        <v>4681</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.shopify.com</t>
+          <t>https://www.roblox.com.bi/users/984831893291/profile</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
@@ -4434,35 +4456,35 @@
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>7855</v>
+        <v>191</v>
       </c>
       <c r="N83" t="n">
         <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.slack.com</t>
+          <t>http://www.onedrive.secure-connection.us.ci/</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E84" t="b">
         <v>0</v>
       </c>
       <c r="F84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84" t="b">
         <v>0</v>
@@ -4483,44 +4505,44 @@
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>12379</v>
+        <v>304</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.ebay.com</t>
+          <t>http://send-secure-trustwallet-usdt-bip20.vercel.app/</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="C85" t="n">
         <v>2</v>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E85" t="b">
         <v>0</v>
       </c>
       <c r="F85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G85" t="b">
         <v>0</v>
       </c>
       <c r="H85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I85" t="n">
-        <v>-0</v>
+        <v>3.83</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -4531,27 +4553,25 @@
       <c r="L85" t="b">
         <v>0</v>
       </c>
-      <c r="M85" t="n">
-        <v>11362</v>
-      </c>
+      <c r="M85" t="inlineStr"/>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.twitch.tv</t>
+          <t>https://www.roblox.com.hr/users/7308841562/profile</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="C86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
@@ -4581,29 +4601,29 @@
         <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>6304</v>
+        <v>22</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.uber.com</t>
+          <t>https://s4w.in/roblox-com-users-73288415162-profile</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="C87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E87" t="b">
         <v>0</v>
@@ -4618,7 +4638,7 @@
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>-0</v>
+        <v>1.58</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -4630,26 +4650,26 @@
         <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>11383</v>
+        <v>6877</v>
       </c>
       <c r="N87" t="n">
         <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.airbnb.com</t>
+          <t>https://www.roblox.com.hr/users/120114981/profile</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D88" t="n">
         <v>0</v>
@@ -4670,38 +4690,38 @@
         <v>-0</v>
       </c>
       <c r="J88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K88" t="b">
         <v>0</v>
       </c>
       <c r="L88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>6612</v>
+        <v>22</v>
       </c>
       <c r="N88" t="n">
         <v>3</v>
       </c>
       <c r="O88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.chase.com</t>
+          <t>https://s4w.in/roblox-com-users-1202114981-profile</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="C89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E89" t="b">
         <v>0</v>
@@ -4716,59 +4736,59 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>-0</v>
+        <v>1.58</v>
       </c>
       <c r="J89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" t="b">
         <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>11294</v>
+        <v>6877</v>
       </c>
       <c r="N89" t="n">
         <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.stackoverflow.com</t>
+          <t>http://www.mmatmasck-usa.godaddysites.com/</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E90" t="b">
         <v>0</v>
       </c>
       <c r="F90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G90" t="b">
         <v>0</v>
       </c>
       <c r="H90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>-0</v>
+        <v>2.82</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K90" t="b">
         <v>0</v>
@@ -4777,61 +4797,5338 @@
         <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>8295</v>
+        <v>4681</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>https://increasefollowersforinstagram.blogspot.com/</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>51</v>
+      </c>
+      <c r="C91" t="n">
+        <v>2</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="b">
+        <v>0</v>
+      </c>
+      <c r="F91" t="b">
+        <v>1</v>
+      </c>
+      <c r="G91" t="b">
+        <v>0</v>
+      </c>
+      <c r="H91" t="b">
+        <v>1</v>
+      </c>
+      <c r="I91" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="b">
+        <v>0</v>
+      </c>
+      <c r="L91" t="b">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>9539</v>
+      </c>
+      <c r="N91" t="n">
+        <v>6</v>
+      </c>
+      <c r="O91" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>https://accountsecurityhub.vercel.app/privacy-centers.html</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>58</v>
+      </c>
+      <c r="C92" t="n">
+        <v>3</v>
+      </c>
+      <c r="D92" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" t="b">
+        <v>0</v>
+      </c>
+      <c r="F92" t="b">
+        <v>1</v>
+      </c>
+      <c r="G92" t="b">
+        <v>0</v>
+      </c>
+      <c r="H92" t="b">
+        <v>1</v>
+      </c>
+      <c r="I92" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="b">
+        <v>0</v>
+      </c>
+      <c r="L92" t="b">
+        <v>0</v>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="n">
+        <v>6</v>
+      </c>
+      <c r="O92" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>http://homes-usa-trezr.pages.dev/</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>33</v>
+      </c>
+      <c r="C93" t="n">
+        <v>2</v>
+      </c>
+      <c r="D93" t="n">
+        <v>2</v>
+      </c>
+      <c r="E93" t="b">
+        <v>0</v>
+      </c>
+      <c r="F93" t="b">
+        <v>0</v>
+      </c>
+      <c r="G93" t="b">
+        <v>0</v>
+      </c>
+      <c r="H93" t="b">
+        <v>1</v>
+      </c>
+      <c r="I93" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="b">
+        <v>0</v>
+      </c>
+      <c r="L93" t="b">
+        <v>0</v>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="n">
+        <v>4</v>
+      </c>
+      <c r="O93" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>https://www.roblox.com.bi/users/371040669174/profile</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>52</v>
+      </c>
+      <c r="C94" t="n">
+        <v>3</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="b">
+        <v>0</v>
+      </c>
+      <c r="F94" t="b">
+        <v>1</v>
+      </c>
+      <c r="G94" t="b">
+        <v>0</v>
+      </c>
+      <c r="H94" t="b">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="b">
+        <v>0</v>
+      </c>
+      <c r="L94" t="b">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>191</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>https://arifrxm.github.io/</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>26</v>
+      </c>
+      <c r="C95" t="n">
+        <v>2</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="b">
+        <v>0</v>
+      </c>
+      <c r="F95" t="b">
+        <v>1</v>
+      </c>
+      <c r="G95" t="b">
+        <v>0</v>
+      </c>
+      <c r="H95" t="b">
+        <v>1</v>
+      </c>
+      <c r="I95" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="b">
+        <v>0</v>
+      </c>
+      <c r="L95" t="b">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>4936</v>
+      </c>
+      <c r="N95" t="n">
+        <v>3</v>
+      </c>
+      <c r="O95" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>https://www.roblox.com.mu/communities/3330747117/Robux-Giveaway-Group</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>69</v>
+      </c>
+      <c r="C96" t="n">
+        <v>3</v>
+      </c>
+      <c r="D96" t="n">
+        <v>2</v>
+      </c>
+      <c r="E96" t="b">
+        <v>0</v>
+      </c>
+      <c r="F96" t="b">
+        <v>1</v>
+      </c>
+      <c r="G96" t="b">
+        <v>0</v>
+      </c>
+      <c r="H96" t="b">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="b">
+        <v>0</v>
+      </c>
+      <c r="L96" t="b">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>98</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>https://policy-update-production-migykn.laravel.cloud/</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>54</v>
+      </c>
+      <c r="C97" t="n">
+        <v>2</v>
+      </c>
+      <c r="D97" t="n">
+        <v>3</v>
+      </c>
+      <c r="E97" t="b">
+        <v>0</v>
+      </c>
+      <c r="F97" t="b">
+        <v>1</v>
+      </c>
+      <c r="G97" t="b">
+        <v>0</v>
+      </c>
+      <c r="H97" t="b">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="b">
+        <v>0</v>
+      </c>
+      <c r="L97" t="b">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>3362</v>
+      </c>
+      <c r="N97" t="n">
+        <v>3</v>
+      </c>
+      <c r="O97" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>http://ihsyy-cbq-rnp7-1ob3h-11-09-2026-hh.pages.dev/</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>52</v>
+      </c>
+      <c r="C98" t="n">
+        <v>2</v>
+      </c>
+      <c r="D98" t="n">
+        <v>7</v>
+      </c>
+      <c r="E98" t="b">
+        <v>0</v>
+      </c>
+      <c r="F98" t="b">
+        <v>0</v>
+      </c>
+      <c r="G98" t="b">
+        <v>0</v>
+      </c>
+      <c r="H98" t="b">
+        <v>1</v>
+      </c>
+      <c r="I98" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="b">
+        <v>0</v>
+      </c>
+      <c r="L98" t="b">
+        <v>0</v>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="n">
+        <v>7</v>
+      </c>
+      <c r="O98" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>https://atulraj03.github.io/Spotify-clone-ui</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>44</v>
+      </c>
+      <c r="C99" t="n">
+        <v>2</v>
+      </c>
+      <c r="D99" t="n">
+        <v>2</v>
+      </c>
+      <c r="E99" t="b">
+        <v>0</v>
+      </c>
+      <c r="F99" t="b">
+        <v>1</v>
+      </c>
+      <c r="G99" t="b">
+        <v>0</v>
+      </c>
+      <c r="H99" t="b">
+        <v>1</v>
+      </c>
+      <c r="I99" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="b">
+        <v>0</v>
+      </c>
+      <c r="L99" t="b">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>4936</v>
+      </c>
+      <c r="N99" t="n">
+        <v>3</v>
+      </c>
+      <c r="O99" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>https://www.roblox.ly/users/1604972168/profile</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>46</v>
+      </c>
+      <c r="C100" t="n">
+        <v>2</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="b">
+        <v>0</v>
+      </c>
+      <c r="F100" t="b">
+        <v>1</v>
+      </c>
+      <c r="G100" t="b">
+        <v>0</v>
+      </c>
+      <c r="H100" t="b">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="b">
+        <v>0</v>
+      </c>
+      <c r="L100" t="b">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>61</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>https://meta-verified-blueticks-fb12.vercel.app/</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>48</v>
+      </c>
+      <c r="C101" t="n">
+        <v>2</v>
+      </c>
+      <c r="D101" t="n">
+        <v>3</v>
+      </c>
+      <c r="E101" t="b">
+        <v>0</v>
+      </c>
+      <c r="F101" t="b">
+        <v>1</v>
+      </c>
+      <c r="G101" t="b">
+        <v>0</v>
+      </c>
+      <c r="H101" t="b">
+        <v>1</v>
+      </c>
+      <c r="I101" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="b">
+        <v>0</v>
+      </c>
+      <c r="L101" t="b">
+        <v>0</v>
+      </c>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="n">
+        <v>6</v>
+      </c>
+      <c r="O101" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>https://fb-meta-verified-48503.vercel.app/privacy-/</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>51</v>
+      </c>
+      <c r="C102" t="n">
+        <v>2</v>
+      </c>
+      <c r="D102" t="n">
+        <v>4</v>
+      </c>
+      <c r="E102" t="b">
+        <v>0</v>
+      </c>
+      <c r="F102" t="b">
+        <v>1</v>
+      </c>
+      <c r="G102" t="b">
+        <v>0</v>
+      </c>
+      <c r="H102" t="b">
+        <v>1</v>
+      </c>
+      <c r="I102" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="b">
+        <v>0</v>
+      </c>
+      <c r="L102" t="b">
+        <v>0</v>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="n">
+        <v>6</v>
+      </c>
+      <c r="O102" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>https://www.phantomwallet-solana.godaddysites.com/</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>50</v>
+      </c>
+      <c r="C103" t="n">
+        <v>3</v>
+      </c>
+      <c r="D103" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" t="b">
+        <v>0</v>
+      </c>
+      <c r="F103" t="b">
+        <v>1</v>
+      </c>
+      <c r="G103" t="b">
+        <v>0</v>
+      </c>
+      <c r="H103" t="b">
+        <v>1</v>
+      </c>
+      <c r="I103" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="b">
+        <v>0</v>
+      </c>
+      <c r="L103" t="b">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
+        <v>4681</v>
+      </c>
+      <c r="N103" t="n">
+        <v>3</v>
+      </c>
+      <c r="O103" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>https://app-exodusweb.pages.dev/%22%3EExodus</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>44</v>
+      </c>
+      <c r="C104" t="n">
+        <v>2</v>
+      </c>
+      <c r="D104" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" t="b">
+        <v>0</v>
+      </c>
+      <c r="F104" t="b">
+        <v>1</v>
+      </c>
+      <c r="G104" t="b">
+        <v>0</v>
+      </c>
+      <c r="H104" t="b">
+        <v>1</v>
+      </c>
+      <c r="I104" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="b">
+        <v>0</v>
+      </c>
+      <c r="L104" t="b">
+        <v>0</v>
+      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="n">
+        <v>3</v>
+      </c>
+      <c r="O104" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>https://desirable-apricot-ljcm1knm.edgeone.dev/home</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>51</v>
+      </c>
+      <c r="C105" t="n">
+        <v>2</v>
+      </c>
+      <c r="D105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E105" t="b">
+        <v>0</v>
+      </c>
+      <c r="F105" t="b">
+        <v>1</v>
+      </c>
+      <c r="G105" t="b">
+        <v>0</v>
+      </c>
+      <c r="H105" t="b">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="b">
+        <v>0</v>
+      </c>
+      <c r="L105" t="b">
+        <v>0</v>
+      </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="n">
+        <v>3</v>
+      </c>
+      <c r="O105" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>https://logicbox-12.pages.dev/?app_vl=ZoNwlWpnbWKEmLqxy5qmnnx0YsC2wa-TpaiVYsBxj2phmqOgnLFwrYw&amp;dd=SyguNyQsMSUoOixkIiIrIQ&amp;e=cookg%2540universityhospital.org&amp;sui=%257Bsui%257D&amp;fn=Greg&amp;ln=Cook&amp;p=&amp;z=CHNAMECL-120...</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>209</v>
+      </c>
+      <c r="C106" t="n">
+        <v>6</v>
+      </c>
+      <c r="D106" t="n">
+        <v>3</v>
+      </c>
+      <c r="E106" t="b">
+        <v>0</v>
+      </c>
+      <c r="F106" t="b">
+        <v>1</v>
+      </c>
+      <c r="G106" t="b">
+        <v>0</v>
+      </c>
+      <c r="H106" t="b">
+        <v>1</v>
+      </c>
+      <c r="I106" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="b">
+        <v>0</v>
+      </c>
+      <c r="L106" t="b">
+        <v>0</v>
+      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="n">
+        <v>3</v>
+      </c>
+      <c r="O106" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>https://buildkit-12.pages.dev/?app_vl=ZoNwlWpnbWKEmLqxy5qmnnx0YsC2wa-TpaiVYsBxj2phmqOgnLFwrYw&amp;dd=SyguNyQsMSUoOixkIiIrIQ&amp;e=Chan%2540yagmail.com&amp;sui=%257Bsui%257D&amp;fn=Chan&amp;ln=Han&amp;p=&amp;z=CHNAMERAW-120926-CZA1</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>202</v>
+      </c>
+      <c r="C107" t="n">
+        <v>3</v>
+      </c>
+      <c r="D107" t="n">
+        <v>4</v>
+      </c>
+      <c r="E107" t="b">
+        <v>0</v>
+      </c>
+      <c r="F107" t="b">
+        <v>1</v>
+      </c>
+      <c r="G107" t="b">
+        <v>0</v>
+      </c>
+      <c r="H107" t="b">
+        <v>1</v>
+      </c>
+      <c r="I107" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="b">
+        <v>0</v>
+      </c>
+      <c r="L107" t="b">
+        <v>0</v>
+      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="n">
+        <v>3</v>
+      </c>
+      <c r="O107" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>https://www.robiox.com.ps/users/4904839217/profile</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>50</v>
+      </c>
+      <c r="C108" t="n">
+        <v>3</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" t="b">
+        <v>0</v>
+      </c>
+      <c r="F108" t="b">
+        <v>1</v>
+      </c>
+      <c r="G108" t="b">
+        <v>0</v>
+      </c>
+      <c r="H108" t="b">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="b">
+        <v>0</v>
+      </c>
+      <c r="L108" t="b">
+        <v>0</v>
+      </c>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>https://s4w.in/roblox-com-users-5617473240</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>42</v>
+      </c>
+      <c r="C109" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" t="n">
+        <v>3</v>
+      </c>
+      <c r="E109" t="b">
+        <v>0</v>
+      </c>
+      <c r="F109" t="b">
+        <v>1</v>
+      </c>
+      <c r="G109" t="b">
+        <v>0</v>
+      </c>
+      <c r="H109" t="b">
+        <v>0</v>
+      </c>
+      <c r="I109" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="b">
+        <v>0</v>
+      </c>
+      <c r="L109" t="b">
+        <v>0</v>
+      </c>
+      <c r="M109" t="n">
+        <v>6877</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>https://f005.backblazeb2.com/file/viewmei/idverf.html</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>53</v>
+      </c>
+      <c r="C110" t="n">
+        <v>3</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="b">
+        <v>0</v>
+      </c>
+      <c r="F110" t="b">
+        <v>1</v>
+      </c>
+      <c r="G110" t="b">
+        <v>0</v>
+      </c>
+      <c r="H110" t="b">
+        <v>0</v>
+      </c>
+      <c r="I110" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="b">
+        <v>0</v>
+      </c>
+      <c r="L110" t="b">
+        <v>0</v>
+      </c>
+      <c r="M110" t="n">
+        <v>3713</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>https://microezip--dpaships.replit.app/</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>39</v>
+      </c>
+      <c r="C111" t="n">
+        <v>2</v>
+      </c>
+      <c r="D111" t="n">
+        <v>2</v>
+      </c>
+      <c r="E111" t="b">
+        <v>0</v>
+      </c>
+      <c r="F111" t="b">
+        <v>1</v>
+      </c>
+      <c r="G111" t="b">
+        <v>0</v>
+      </c>
+      <c r="H111" t="b">
+        <v>0</v>
+      </c>
+      <c r="I111" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="J111" t="n">
+        <v>1</v>
+      </c>
+      <c r="K111" t="b">
+        <v>1</v>
+      </c>
+      <c r="L111" t="b">
+        <v>0</v>
+      </c>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="n">
+        <v>3</v>
+      </c>
+      <c r="O111" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>http://www.sendusdtupdated.vercel.app/</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>38</v>
+      </c>
+      <c r="C112" t="n">
+        <v>3</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="b">
+        <v>0</v>
+      </c>
+      <c r="F112" t="b">
+        <v>0</v>
+      </c>
+      <c r="G112" t="b">
+        <v>0</v>
+      </c>
+      <c r="H112" t="b">
+        <v>1</v>
+      </c>
+      <c r="I112" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="b">
+        <v>0</v>
+      </c>
+      <c r="L112" t="b">
+        <v>0</v>
+      </c>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="n">
+        <v>4</v>
+      </c>
+      <c r="O112" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>https://shiva52310.github.io/netflix-clone</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>42</v>
+      </c>
+      <c r="C113" t="n">
+        <v>2</v>
+      </c>
+      <c r="D113" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" t="b">
+        <v>0</v>
+      </c>
+      <c r="F113" t="b">
+        <v>1</v>
+      </c>
+      <c r="G113" t="b">
+        <v>0</v>
+      </c>
+      <c r="H113" t="b">
+        <v>1</v>
+      </c>
+      <c r="I113" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="b">
+        <v>0</v>
+      </c>
+      <c r="L113" t="b">
+        <v>0</v>
+      </c>
+      <c r="M113" t="n">
+        <v>4936</v>
+      </c>
+      <c r="N113" t="n">
+        <v>3</v>
+      </c>
+      <c r="O113" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>http://sendusdt00.netlify.app/</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>30</v>
+      </c>
+      <c r="C114" t="n">
+        <v>2</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="b">
+        <v>0</v>
+      </c>
+      <c r="F114" t="b">
+        <v>0</v>
+      </c>
+      <c r="G114" t="b">
+        <v>0</v>
+      </c>
+      <c r="H114" t="b">
+        <v>1</v>
+      </c>
+      <c r="I114" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" t="b">
+        <v>0</v>
+      </c>
+      <c r="L114" t="b">
+        <v>0</v>
+      </c>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="n">
+        <v>4</v>
+      </c>
+      <c r="O114" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>https://conscious-coffee-kxdep1v7.edgeone.dev/home</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>50</v>
+      </c>
+      <c r="C115" t="n">
+        <v>2</v>
+      </c>
+      <c r="D115" t="n">
+        <v>2</v>
+      </c>
+      <c r="E115" t="b">
+        <v>0</v>
+      </c>
+      <c r="F115" t="b">
+        <v>1</v>
+      </c>
+      <c r="G115" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" t="b">
+        <v>0</v>
+      </c>
+      <c r="I115" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="b">
+        <v>0</v>
+      </c>
+      <c r="L115" t="b">
+        <v>0</v>
+      </c>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="n">
+        <v>3</v>
+      </c>
+      <c r="O115" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>https://meta-verified-blueticks-fb8.vercel.app/privacy-centers.html/</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>68</v>
+      </c>
+      <c r="C116" t="n">
+        <v>3</v>
+      </c>
+      <c r="D116" t="n">
+        <v>4</v>
+      </c>
+      <c r="E116" t="b">
+        <v>0</v>
+      </c>
+      <c r="F116" t="b">
+        <v>1</v>
+      </c>
+      <c r="G116" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" t="b">
+        <v>1</v>
+      </c>
+      <c r="I116" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="b">
+        <v>0</v>
+      </c>
+      <c r="L116" t="b">
+        <v>0</v>
+      </c>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="n">
+        <v>6</v>
+      </c>
+      <c r="O116" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>https://s4w.in/roblox-com-games-2753915549-Blox-FruitsprivateServerLinkCode=15587938948810815525436529481999</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>108</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1</v>
+      </c>
+      <c r="D117" t="n">
+        <v>5</v>
+      </c>
+      <c r="E117" t="b">
+        <v>0</v>
+      </c>
+      <c r="F117" t="b">
+        <v>1</v>
+      </c>
+      <c r="G117" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" t="b">
+        <v>0</v>
+      </c>
+      <c r="I117" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="b">
+        <v>0</v>
+      </c>
+      <c r="L117" t="b">
+        <v>0</v>
+      </c>
+      <c r="M117" t="n">
+        <v>6877</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>http://tiny.cc/5qca101</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>22</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" t="b">
+        <v>0</v>
+      </c>
+      <c r="F118" t="b">
+        <v>0</v>
+      </c>
+      <c r="G118" t="b">
+        <v>0</v>
+      </c>
+      <c r="H118" t="b">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
+        <v>2</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="b">
+        <v>0</v>
+      </c>
+      <c r="L118" t="b">
+        <v>0</v>
+      </c>
+      <c r="M118" t="n">
+        <v>7490</v>
+      </c>
+      <c r="N118" t="n">
+        <v>1</v>
+      </c>
+      <c r="O118" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>https://troubleshoots-google.com/login.php</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>42</v>
+      </c>
+      <c r="C119" t="n">
+        <v>2</v>
+      </c>
+      <c r="D119" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" t="b">
+        <v>0</v>
+      </c>
+      <c r="F119" t="b">
+        <v>1</v>
+      </c>
+      <c r="G119" t="b">
+        <v>0</v>
+      </c>
+      <c r="H119" t="b">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="b">
+        <v>0</v>
+      </c>
+      <c r="L119" t="b">
+        <v>0</v>
+      </c>
+      <c r="M119" t="n">
+        <v>3</v>
+      </c>
+      <c r="N119" t="n">
+        <v>3</v>
+      </c>
+      <c r="O119" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>https://hurt-black-ozr1td9x.edgeone.dev/home</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>44</v>
+      </c>
+      <c r="C120" t="n">
+        <v>2</v>
+      </c>
+      <c r="D120" t="n">
+        <v>2</v>
+      </c>
+      <c r="E120" t="b">
+        <v>0</v>
+      </c>
+      <c r="F120" t="b">
+        <v>1</v>
+      </c>
+      <c r="G120" t="b">
+        <v>0</v>
+      </c>
+      <c r="H120" t="b">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="b">
+        <v>0</v>
+      </c>
+      <c r="L120" t="b">
+        <v>0</v>
+      </c>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="n">
+        <v>3</v>
+      </c>
+      <c r="O120" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>https://timeforsurveys.com/2513501.doc/18a80a/fad0f483-81b2-45c6-ad47-7272058d9cb6/</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>83</v>
+      </c>
+      <c r="C121" t="n">
+        <v>2</v>
+      </c>
+      <c r="D121" t="n">
+        <v>4</v>
+      </c>
+      <c r="E121" t="b">
+        <v>0</v>
+      </c>
+      <c r="F121" t="b">
+        <v>1</v>
+      </c>
+      <c r="G121" t="b">
+        <v>0</v>
+      </c>
+      <c r="H121" t="b">
+        <v>0</v>
+      </c>
+      <c r="I121" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="J121" t="n">
+        <v>1</v>
+      </c>
+      <c r="K121" t="b">
+        <v>1</v>
+      </c>
+      <c r="L121" t="b">
+        <v>0</v>
+      </c>
+      <c r="M121" t="n">
+        <v>3956</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>https://troubleshoots-google.com/</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>33</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" t="b">
+        <v>0</v>
+      </c>
+      <c r="F122" t="b">
+        <v>1</v>
+      </c>
+      <c r="G122" t="b">
+        <v>0</v>
+      </c>
+      <c r="H122" t="b">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="b">
+        <v>0</v>
+      </c>
+      <c r="L122" t="b">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
+        <v>3</v>
+      </c>
+      <c r="N122" t="n">
+        <v>3</v>
+      </c>
+      <c r="O122" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>https://historical-salmon-zl03sn9j.edgeone.dev/home</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>51</v>
+      </c>
+      <c r="C123" t="n">
+        <v>2</v>
+      </c>
+      <c r="D123" t="n">
+        <v>2</v>
+      </c>
+      <c r="E123" t="b">
+        <v>0</v>
+      </c>
+      <c r="F123" t="b">
+        <v>1</v>
+      </c>
+      <c r="G123" t="b">
+        <v>0</v>
+      </c>
+      <c r="H123" t="b">
+        <v>0</v>
+      </c>
+      <c r="I123" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="b">
+        <v>0</v>
+      </c>
+      <c r="L123" t="b">
+        <v>0</v>
+      </c>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="n">
+        <v>3</v>
+      </c>
+      <c r="O123" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>http://send-usdt2.netlify.app/</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>30</v>
+      </c>
+      <c r="C124" t="n">
+        <v>2</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" t="b">
+        <v>0</v>
+      </c>
+      <c r="F124" t="b">
+        <v>0</v>
+      </c>
+      <c r="G124" t="b">
+        <v>0</v>
+      </c>
+      <c r="H124" t="b">
+        <v>1</v>
+      </c>
+      <c r="I124" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="b">
+        <v>0</v>
+      </c>
+      <c r="L124" t="b">
+        <v>0</v>
+      </c>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="n">
+        <v>4</v>
+      </c>
+      <c r="O124" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>https://itsupportorganization.com/2513501.doc/18a80a/fad0f483-81b2-45c6-ad47-7272058d9cb6/</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>90</v>
+      </c>
+      <c r="C125" t="n">
+        <v>2</v>
+      </c>
+      <c r="D125" t="n">
+        <v>4</v>
+      </c>
+      <c r="E125" t="b">
+        <v>0</v>
+      </c>
+      <c r="F125" t="b">
+        <v>1</v>
+      </c>
+      <c r="G125" t="b">
+        <v>0</v>
+      </c>
+      <c r="H125" t="b">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="b">
+        <v>0</v>
+      </c>
+      <c r="L125" t="b">
+        <v>0</v>
+      </c>
+      <c r="M125" t="n">
+        <v>1787</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>https://itrustcepital_loigin.godaddysites.com/</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>46</v>
+      </c>
+      <c r="C126" t="n">
+        <v>2</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="b">
+        <v>0</v>
+      </c>
+      <c r="F126" t="b">
+        <v>1</v>
+      </c>
+      <c r="G126" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126" t="b">
+        <v>1</v>
+      </c>
+      <c r="I126" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="b">
+        <v>0</v>
+      </c>
+      <c r="L126" t="b">
+        <v>0</v>
+      </c>
+      <c r="M126" t="n">
+        <v>4681</v>
+      </c>
+      <c r="N126" t="n">
+        <v>6</v>
+      </c>
+      <c r="O126" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>http://tiny.cc/559a101</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>22</v>
+      </c>
+      <c r="C127" t="n">
+        <v>1</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" t="b">
+        <v>0</v>
+      </c>
+      <c r="F127" t="b">
+        <v>0</v>
+      </c>
+      <c r="G127" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" t="b">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>2</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="b">
+        <v>0</v>
+      </c>
+      <c r="L127" t="b">
+        <v>0</v>
+      </c>
+      <c r="M127" t="n">
+        <v>7490</v>
+      </c>
+      <c r="N127" t="n">
+        <v>1</v>
+      </c>
+      <c r="O127" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>https://www.itrustcepital_loigin.godaddysites.com/</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>50</v>
+      </c>
+      <c r="C128" t="n">
+        <v>3</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="b">
+        <v>0</v>
+      </c>
+      <c r="F128" t="b">
+        <v>1</v>
+      </c>
+      <c r="G128" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" t="b">
+        <v>1</v>
+      </c>
+      <c r="I128" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="b">
+        <v>0</v>
+      </c>
+      <c r="L128" t="b">
+        <v>0</v>
+      </c>
+      <c r="M128" t="n">
+        <v>4681</v>
+      </c>
+      <c r="N128" t="n">
+        <v>6</v>
+      </c>
+      <c r="O128" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>http://trustwalletreport.vercel.app/</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>36</v>
+      </c>
+      <c r="C129" t="n">
+        <v>2</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" t="b">
+        <v>0</v>
+      </c>
+      <c r="F129" t="b">
+        <v>0</v>
+      </c>
+      <c r="G129" t="b">
+        <v>0</v>
+      </c>
+      <c r="H129" t="b">
+        <v>1</v>
+      </c>
+      <c r="I129" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="b">
+        <v>0</v>
+      </c>
+      <c r="L129" t="b">
+        <v>0</v>
+      </c>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="n">
+        <v>4</v>
+      </c>
+      <c r="O129" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>http://sendusdtupdated.vercel.app/</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>34</v>
+      </c>
+      <c r="C130" t="n">
+        <v>2</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" t="b">
+        <v>0</v>
+      </c>
+      <c r="F130" t="b">
+        <v>0</v>
+      </c>
+      <c r="G130" t="b">
+        <v>0</v>
+      </c>
+      <c r="H130" t="b">
+        <v>1</v>
+      </c>
+      <c r="I130" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="b">
+        <v>0</v>
+      </c>
+      <c r="L130" t="b">
+        <v>0</v>
+      </c>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="n">
+        <v>4</v>
+      </c>
+      <c r="O130" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>https://unusual-silver-1esxzkwv.edgeone.dev/home</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>48</v>
+      </c>
+      <c r="C131" t="n">
+        <v>2</v>
+      </c>
+      <c r="D131" t="n">
+        <v>2</v>
+      </c>
+      <c r="E131" t="b">
+        <v>0</v>
+      </c>
+      <c r="F131" t="b">
+        <v>1</v>
+      </c>
+      <c r="G131" t="b">
+        <v>0</v>
+      </c>
+      <c r="H131" t="b">
+        <v>0</v>
+      </c>
+      <c r="I131" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="b">
+        <v>0</v>
+      </c>
+      <c r="L131" t="b">
+        <v>0</v>
+      </c>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="n">
+        <v>3</v>
+      </c>
+      <c r="O131" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>http://www.facebook-six-ivory.vercel.app/</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>41</v>
+      </c>
+      <c r="C132" t="n">
+        <v>3</v>
+      </c>
+      <c r="D132" t="n">
+        <v>2</v>
+      </c>
+      <c r="E132" t="b">
+        <v>0</v>
+      </c>
+      <c r="F132" t="b">
+        <v>0</v>
+      </c>
+      <c r="G132" t="b">
+        <v>0</v>
+      </c>
+      <c r="H132" t="b">
+        <v>1</v>
+      </c>
+      <c r="I132" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="b">
+        <v>0</v>
+      </c>
+      <c r="L132" t="b">
+        <v>0</v>
+      </c>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="n">
+        <v>7</v>
+      </c>
+      <c r="O132" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>https://hot-moccasin-v46kgzzn.edgeone.dev/home</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>46</v>
+      </c>
+      <c r="C133" t="n">
+        <v>2</v>
+      </c>
+      <c r="D133" t="n">
+        <v>2</v>
+      </c>
+      <c r="E133" t="b">
+        <v>0</v>
+      </c>
+      <c r="F133" t="b">
+        <v>1</v>
+      </c>
+      <c r="G133" t="b">
+        <v>0</v>
+      </c>
+      <c r="H133" t="b">
+        <v>0</v>
+      </c>
+      <c r="I133" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="b">
+        <v>0</v>
+      </c>
+      <c r="L133" t="b">
+        <v>0</v>
+      </c>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="n">
+        <v>3</v>
+      </c>
+      <c r="O133" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>http://updateserv-owa.vercel.app/</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>33</v>
+      </c>
+      <c r="C134" t="n">
+        <v>2</v>
+      </c>
+      <c r="D134" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" t="b">
+        <v>0</v>
+      </c>
+      <c r="F134" t="b">
+        <v>0</v>
+      </c>
+      <c r="G134" t="b">
+        <v>0</v>
+      </c>
+      <c r="H134" t="b">
+        <v>1</v>
+      </c>
+      <c r="I134" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="b">
+        <v>0</v>
+      </c>
+      <c r="L134" t="b">
+        <v>0</v>
+      </c>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="n">
+        <v>7</v>
+      </c>
+      <c r="O134" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>https://www.roblox.et/users/6128029595/profile</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>46</v>
+      </c>
+      <c r="C135" t="n">
+        <v>2</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" t="b">
+        <v>0</v>
+      </c>
+      <c r="F135" t="b">
+        <v>1</v>
+      </c>
+      <c r="G135" t="b">
+        <v>0</v>
+      </c>
+      <c r="H135" t="b">
+        <v>0</v>
+      </c>
+      <c r="I135" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="b">
+        <v>0</v>
+      </c>
+      <c r="L135" t="b">
+        <v>0</v>
+      </c>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>https://verified-badge-hub-5639.vercel.app/</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>43</v>
+      </c>
+      <c r="C136" t="n">
+        <v>2</v>
+      </c>
+      <c r="D136" t="n">
+        <v>3</v>
+      </c>
+      <c r="E136" t="b">
+        <v>0</v>
+      </c>
+      <c r="F136" t="b">
+        <v>1</v>
+      </c>
+      <c r="G136" t="b">
+        <v>0</v>
+      </c>
+      <c r="H136" t="b">
+        <v>1</v>
+      </c>
+      <c r="I136" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="b">
+        <v>0</v>
+      </c>
+      <c r="L136" t="b">
+        <v>0</v>
+      </c>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="n">
+        <v>6</v>
+      </c>
+      <c r="O136" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>https://secure-page-builder--garybrown9939.replit.app/</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>54</v>
+      </c>
+      <c r="C137" t="n">
+        <v>2</v>
+      </c>
+      <c r="D137" t="n">
+        <v>4</v>
+      </c>
+      <c r="E137" t="b">
+        <v>0</v>
+      </c>
+      <c r="F137" t="b">
+        <v>1</v>
+      </c>
+      <c r="G137" t="b">
+        <v>0</v>
+      </c>
+      <c r="H137" t="b">
+        <v>0</v>
+      </c>
+      <c r="I137" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="J137" t="n">
+        <v>1</v>
+      </c>
+      <c r="K137" t="b">
+        <v>1</v>
+      </c>
+      <c r="L137" t="b">
+        <v>0</v>
+      </c>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="n">
+        <v>3</v>
+      </c>
+      <c r="O137" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>http://www.site-tjaobqglc.godaddysites.com/</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>43</v>
+      </c>
+      <c r="C138" t="n">
+        <v>3</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" t="b">
+        <v>0</v>
+      </c>
+      <c r="F138" t="b">
+        <v>0</v>
+      </c>
+      <c r="G138" t="b">
+        <v>0</v>
+      </c>
+      <c r="H138" t="b">
+        <v>1</v>
+      </c>
+      <c r="I138" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="b">
+        <v>0</v>
+      </c>
+      <c r="L138" t="b">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>4681</v>
+      </c>
+      <c r="N138" t="n">
+        <v>7</v>
+      </c>
+      <c r="O138" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>http://ebaymclaren-austin.eventshouse.app/</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>42</v>
+      </c>
+      <c r="C139" t="n">
+        <v>2</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1</v>
+      </c>
+      <c r="E139" t="b">
+        <v>0</v>
+      </c>
+      <c r="F139" t="b">
+        <v>0</v>
+      </c>
+      <c r="G139" t="b">
+        <v>0</v>
+      </c>
+      <c r="H139" t="b">
+        <v>0</v>
+      </c>
+      <c r="I139" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="b">
+        <v>0</v>
+      </c>
+      <c r="L139" t="b">
+        <v>0</v>
+      </c>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="n">
+        <v>4</v>
+      </c>
+      <c r="O139" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>http://www.bookish-pancake-two.vercel.app/</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>42</v>
+      </c>
+      <c r="C140" t="n">
+        <v>3</v>
+      </c>
+      <c r="D140" t="n">
+        <v>2</v>
+      </c>
+      <c r="E140" t="b">
+        <v>0</v>
+      </c>
+      <c r="F140" t="b">
+        <v>0</v>
+      </c>
+      <c r="G140" t="b">
+        <v>0</v>
+      </c>
+      <c r="H140" t="b">
+        <v>1</v>
+      </c>
+      <c r="I140" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="b">
+        <v>0</v>
+      </c>
+      <c r="L140" t="b">
+        <v>0</v>
+      </c>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="n">
+        <v>7</v>
+      </c>
+      <c r="O140" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>https://www.shopee-indonesia33.blogspot.com/</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>44</v>
+      </c>
+      <c r="C141" t="n">
+        <v>3</v>
+      </c>
+      <c r="D141" t="n">
+        <v>1</v>
+      </c>
+      <c r="E141" t="b">
+        <v>0</v>
+      </c>
+      <c r="F141" t="b">
+        <v>1</v>
+      </c>
+      <c r="G141" t="b">
+        <v>0</v>
+      </c>
+      <c r="H141" t="b">
+        <v>1</v>
+      </c>
+      <c r="I141" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="b">
+        <v>0</v>
+      </c>
+      <c r="L141" t="b">
+        <v>0</v>
+      </c>
+      <c r="M141" t="n">
+        <v>9539</v>
+      </c>
+      <c r="N141" t="n">
+        <v>3</v>
+      </c>
+      <c r="O141" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>http://www.site-yzcbrf6j0.godaddysites.com/</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>43</v>
+      </c>
+      <c r="C142" t="n">
+        <v>3</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1</v>
+      </c>
+      <c r="E142" t="b">
+        <v>0</v>
+      </c>
+      <c r="F142" t="b">
+        <v>0</v>
+      </c>
+      <c r="G142" t="b">
+        <v>0</v>
+      </c>
+      <c r="H142" t="b">
+        <v>1</v>
+      </c>
+      <c r="I142" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="b">
+        <v>0</v>
+      </c>
+      <c r="L142" t="b">
+        <v>0</v>
+      </c>
+      <c r="M142" t="n">
+        <v>4681</v>
+      </c>
+      <c r="N142" t="n">
+        <v>7</v>
+      </c>
+      <c r="O142" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>https://humanresources-team.com/2513501.doc/18a80a/fad0f483-81b2-45c6-ad47-7272058d9cb6/</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>88</v>
+      </c>
+      <c r="C143" t="n">
+        <v>2</v>
+      </c>
+      <c r="D143" t="n">
+        <v>5</v>
+      </c>
+      <c r="E143" t="b">
+        <v>0</v>
+      </c>
+      <c r="F143" t="b">
+        <v>1</v>
+      </c>
+      <c r="G143" t="b">
+        <v>0</v>
+      </c>
+      <c r="H143" t="b">
+        <v>0</v>
+      </c>
+      <c r="I143" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="b">
+        <v>0</v>
+      </c>
+      <c r="L143" t="b">
+        <v>0</v>
+      </c>
+      <c r="M143" t="n">
+        <v>1787</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>http://www.verifiedbadge-signal-two.vercel.app/</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>47</v>
+      </c>
+      <c r="C144" t="n">
+        <v>3</v>
+      </c>
+      <c r="D144" t="n">
+        <v>2</v>
+      </c>
+      <c r="E144" t="b">
+        <v>0</v>
+      </c>
+      <c r="F144" t="b">
+        <v>0</v>
+      </c>
+      <c r="G144" t="b">
+        <v>0</v>
+      </c>
+      <c r="H144" t="b">
+        <v>1</v>
+      </c>
+      <c r="I144" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="b">
+        <v>0</v>
+      </c>
+      <c r="L144" t="b">
+        <v>0</v>
+      </c>
+      <c r="M144" t="n">
+        <v>2420</v>
+      </c>
+      <c r="N144" t="n">
+        <v>7</v>
+      </c>
+      <c r="O144" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>http://lib-0568.website-us-southeast-1.linodeobjects.com/</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>57</v>
+      </c>
+      <c r="C145" t="n">
+        <v>3</v>
+      </c>
+      <c r="D145" t="n">
+        <v>4</v>
+      </c>
+      <c r="E145" t="b">
+        <v>0</v>
+      </c>
+      <c r="F145" t="b">
+        <v>0</v>
+      </c>
+      <c r="G145" t="b">
+        <v>0</v>
+      </c>
+      <c r="H145" t="b">
+        <v>0</v>
+      </c>
+      <c r="I145" t="n">
+        <v>3</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="b">
+        <v>0</v>
+      </c>
+      <c r="L145" t="b">
+        <v>0</v>
+      </c>
+      <c r="M145" t="n">
+        <v>2985</v>
+      </c>
+      <c r="N145" t="n">
+        <v>1</v>
+      </c>
+      <c r="O145" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>https://www.roblox.com.hr/users/1336597261/profile</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>50</v>
+      </c>
+      <c r="C146" t="n">
+        <v>3</v>
+      </c>
+      <c r="D146" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" t="b">
+        <v>0</v>
+      </c>
+      <c r="F146" t="b">
+        <v>1</v>
+      </c>
+      <c r="G146" t="b">
+        <v>0</v>
+      </c>
+      <c r="H146" t="b">
+        <v>0</v>
+      </c>
+      <c r="I146" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="b">
+        <v>0</v>
+      </c>
+      <c r="L146" t="b">
+        <v>0</v>
+      </c>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="n">
+        <v>0</v>
+      </c>
+      <c r="O146" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>https://s4w.in/roblox-com-users-8336597261-profile</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>50</v>
+      </c>
+      <c r="C147" t="n">
+        <v>1</v>
+      </c>
+      <c r="D147" t="n">
+        <v>4</v>
+      </c>
+      <c r="E147" t="b">
+        <v>0</v>
+      </c>
+      <c r="F147" t="b">
+        <v>1</v>
+      </c>
+      <c r="G147" t="b">
+        <v>0</v>
+      </c>
+      <c r="H147" t="b">
+        <v>0</v>
+      </c>
+      <c r="I147" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="b">
+        <v>0</v>
+      </c>
+      <c r="L147" t="b">
+        <v>0</v>
+      </c>
+      <c r="M147" t="n">
+        <v>6877</v>
+      </c>
+      <c r="N147" t="n">
+        <v>0</v>
+      </c>
+      <c r="O147" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>https://146a1.casmex.at/kraken/cabs28ls.php</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>43</v>
+      </c>
+      <c r="C148" t="n">
+        <v>3</v>
+      </c>
+      <c r="D148" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" t="b">
+        <v>0</v>
+      </c>
+      <c r="F148" t="b">
+        <v>1</v>
+      </c>
+      <c r="G148" t="b">
+        <v>0</v>
+      </c>
+      <c r="H148" t="b">
+        <v>0</v>
+      </c>
+      <c r="I148" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="b">
+        <v>0</v>
+      </c>
+      <c r="L148" t="b">
+        <v>0</v>
+      </c>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="n">
+        <v>0</v>
+      </c>
+      <c r="O148" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>https://www.microsoft.com</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>25</v>
+      </c>
+      <c r="C149" t="n">
+        <v>2</v>
+      </c>
+      <c r="D149" t="n">
+        <v>0</v>
+      </c>
+      <c r="E149" t="b">
+        <v>0</v>
+      </c>
+      <c r="F149" t="b">
+        <v>1</v>
+      </c>
+      <c r="G149" t="b">
+        <v>0</v>
+      </c>
+      <c r="H149" t="b">
+        <v>0</v>
+      </c>
+      <c r="I149" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J149" t="n">
+        <v>1</v>
+      </c>
+      <c r="K149" t="b">
+        <v>0</v>
+      </c>
+      <c r="L149" t="b">
+        <v>0</v>
+      </c>
+      <c r="M149" t="n">
+        <v>12918</v>
+      </c>
+      <c r="N149" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>https://recargasjogo.shop/</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>26</v>
+      </c>
+      <c r="C150" t="n">
+        <v>1</v>
+      </c>
+      <c r="D150" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" t="b">
+        <v>0</v>
+      </c>
+      <c r="F150" t="b">
+        <v>1</v>
+      </c>
+      <c r="G150" t="b">
+        <v>0</v>
+      </c>
+      <c r="H150" t="b">
+        <v>0</v>
+      </c>
+      <c r="I150" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" t="b">
+        <v>0</v>
+      </c>
+      <c r="L150" t="b">
+        <v>0</v>
+      </c>
+      <c r="M150" t="n">
+        <v>29</v>
+      </c>
+      <c r="N150" t="n">
+        <v>3</v>
+      </c>
+      <c r="O150" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>http://www--roblox.co/users/1911090649/profile</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>46</v>
+      </c>
+      <c r="C151" t="n">
+        <v>1</v>
+      </c>
+      <c r="D151" t="n">
+        <v>2</v>
+      </c>
+      <c r="E151" t="b">
+        <v>0</v>
+      </c>
+      <c r="F151" t="b">
+        <v>0</v>
+      </c>
+      <c r="G151" t="b">
+        <v>0</v>
+      </c>
+      <c r="H151" t="b">
+        <v>0</v>
+      </c>
+      <c r="I151" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="b">
+        <v>0</v>
+      </c>
+      <c r="L151" t="b">
+        <v>0</v>
+      </c>
+      <c r="M151" t="n">
+        <v>160</v>
+      </c>
+      <c r="N151" t="n">
+        <v>1</v>
+      </c>
+      <c r="O151" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>https://www.google.com</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>22</v>
+      </c>
+      <c r="C152" t="n">
+        <v>2</v>
+      </c>
+      <c r="D152" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" t="b">
+        <v>0</v>
+      </c>
+      <c r="F152" t="b">
+        <v>1</v>
+      </c>
+      <c r="G152" t="b">
+        <v>0</v>
+      </c>
+      <c r="H152" t="b">
+        <v>0</v>
+      </c>
+      <c r="I152" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J152" t="n">
+        <v>1</v>
+      </c>
+      <c r="K152" t="b">
+        <v>0</v>
+      </c>
+      <c r="L152" t="b">
+        <v>0</v>
+      </c>
+      <c r="M152" t="n">
+        <v>10590</v>
+      </c>
+      <c r="N152" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>https://www.python.org</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>22</v>
+      </c>
+      <c r="C153" t="n">
+        <v>2</v>
+      </c>
+      <c r="D153" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" t="b">
+        <v>0</v>
+      </c>
+      <c r="F153" t="b">
+        <v>1</v>
+      </c>
+      <c r="G153" t="b">
+        <v>0</v>
+      </c>
+      <c r="H153" t="b">
+        <v>0</v>
+      </c>
+      <c r="I153" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J153" t="n">
+        <v>1</v>
+      </c>
+      <c r="K153" t="b">
+        <v>0</v>
+      </c>
+      <c r="L153" t="b">
+        <v>0</v>
+      </c>
+      <c r="M153" t="n">
+        <v>11493</v>
+      </c>
+      <c r="N153" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>https://www.apple.com</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>21</v>
+      </c>
+      <c r="C154" t="n">
+        <v>2</v>
+      </c>
+      <c r="D154" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" t="b">
+        <v>0</v>
+      </c>
+      <c r="F154" t="b">
+        <v>1</v>
+      </c>
+      <c r="G154" t="b">
+        <v>0</v>
+      </c>
+      <c r="H154" t="b">
+        <v>0</v>
+      </c>
+      <c r="I154" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J154" t="n">
+        <v>1</v>
+      </c>
+      <c r="K154" t="b">
+        <v>0</v>
+      </c>
+      <c r="L154" t="b">
+        <v>0</v>
+      </c>
+      <c r="M154" t="n">
+        <v>14451</v>
+      </c>
+      <c r="N154" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>https://accountmanagecenter.vercel.app/privacy-centers.html/</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>60</v>
+      </c>
+      <c r="C155" t="n">
+        <v>3</v>
+      </c>
+      <c r="D155" t="n">
+        <v>1</v>
+      </c>
+      <c r="E155" t="b">
+        <v>0</v>
+      </c>
+      <c r="F155" t="b">
+        <v>1</v>
+      </c>
+      <c r="G155" t="b">
+        <v>0</v>
+      </c>
+      <c r="H155" t="b">
+        <v>1</v>
+      </c>
+      <c r="I155" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" t="b">
+        <v>0</v>
+      </c>
+      <c r="L155" t="b">
+        <v>0</v>
+      </c>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="n">
+        <v>3</v>
+      </c>
+      <c r="O155" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>https://www.github.com</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>22</v>
+      </c>
+      <c r="C156" t="n">
+        <v>2</v>
+      </c>
+      <c r="D156" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" t="b">
+        <v>0</v>
+      </c>
+      <c r="F156" t="b">
+        <v>1</v>
+      </c>
+      <c r="G156" t="b">
+        <v>0</v>
+      </c>
+      <c r="H156" t="b">
+        <v>0</v>
+      </c>
+      <c r="I156" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J156" t="n">
+        <v>2</v>
+      </c>
+      <c r="K156" t="b">
+        <v>0</v>
+      </c>
+      <c r="L156" t="b">
+        <v>0</v>
+      </c>
+      <c r="M156" t="n">
+        <v>6913</v>
+      </c>
+      <c r="N156" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>https://www.wikipedia.org</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>25</v>
+      </c>
+      <c r="C157" t="n">
+        <v>2</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" t="b">
+        <v>0</v>
+      </c>
+      <c r="F157" t="b">
+        <v>1</v>
+      </c>
+      <c r="G157" t="b">
+        <v>0</v>
+      </c>
+      <c r="H157" t="b">
+        <v>0</v>
+      </c>
+      <c r="I157" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J157" t="n">
+        <v>1</v>
+      </c>
+      <c r="K157" t="b">
+        <v>0</v>
+      </c>
+      <c r="L157" t="b">
+        <v>0</v>
+      </c>
+      <c r="M157" t="n">
+        <v>9374</v>
+      </c>
+      <c r="N157" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>22</v>
+      </c>
+      <c r="C158" t="n">
+        <v>2</v>
+      </c>
+      <c r="D158" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" t="b">
+        <v>0</v>
+      </c>
+      <c r="F158" t="b">
+        <v>1</v>
+      </c>
+      <c r="G158" t="b">
+        <v>0</v>
+      </c>
+      <c r="H158" t="b">
+        <v>0</v>
+      </c>
+      <c r="I158" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" t="b">
+        <v>0</v>
+      </c>
+      <c r="L158" t="b">
+        <v>0</v>
+      </c>
+      <c r="M158" t="n">
+        <v>11639</v>
+      </c>
+      <c r="N158" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>24</v>
+      </c>
+      <c r="C159" t="n">
+        <v>2</v>
+      </c>
+      <c r="D159" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" t="b">
+        <v>0</v>
+      </c>
+      <c r="F159" t="b">
+        <v>1</v>
+      </c>
+      <c r="G159" t="b">
+        <v>0</v>
+      </c>
+      <c r="H159" t="b">
+        <v>0</v>
+      </c>
+      <c r="I159" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J159" t="n">
+        <v>2</v>
+      </c>
+      <c r="K159" t="b">
+        <v>0</v>
+      </c>
+      <c r="L159" t="b">
+        <v>0</v>
+      </c>
+      <c r="M159" t="n">
+        <v>8715</v>
+      </c>
+      <c r="N159" t="n">
+        <v>0</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>https://www.spotify.com</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>23</v>
+      </c>
+      <c r="C160" t="n">
+        <v>2</v>
+      </c>
+      <c r="D160" t="n">
+        <v>0</v>
+      </c>
+      <c r="E160" t="b">
+        <v>0</v>
+      </c>
+      <c r="F160" t="b">
+        <v>1</v>
+      </c>
+      <c r="G160" t="b">
+        <v>0</v>
+      </c>
+      <c r="H160" t="b">
+        <v>0</v>
+      </c>
+      <c r="I160" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="b">
+        <v>0</v>
+      </c>
+      <c r="L160" t="b">
+        <v>0</v>
+      </c>
+      <c r="M160" t="n">
+        <v>7448</v>
+      </c>
+      <c r="N160" t="n">
+        <v>0</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>22</v>
+      </c>
+      <c r="C161" t="n">
+        <v>2</v>
+      </c>
+      <c r="D161" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" t="b">
+        <v>0</v>
+      </c>
+      <c r="F161" t="b">
+        <v>1</v>
+      </c>
+      <c r="G161" t="b">
+        <v>0</v>
+      </c>
+      <c r="H161" t="b">
+        <v>0</v>
+      </c>
+      <c r="I161" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="b">
+        <v>0</v>
+      </c>
+      <c r="L161" t="b">
+        <v>0</v>
+      </c>
+      <c r="M161" t="n">
+        <v>7806</v>
+      </c>
+      <c r="N161" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>https://www.paypal.com</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>22</v>
+      </c>
+      <c r="C162" t="n">
+        <v>2</v>
+      </c>
+      <c r="D162" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" t="b">
+        <v>0</v>
+      </c>
+      <c r="F162" t="b">
+        <v>1</v>
+      </c>
+      <c r="G162" t="b">
+        <v>0</v>
+      </c>
+      <c r="H162" t="b">
+        <v>0</v>
+      </c>
+      <c r="I162" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" t="b">
+        <v>0</v>
+      </c>
+      <c r="L162" t="b">
+        <v>0</v>
+      </c>
+      <c r="M162" t="n">
+        <v>9922</v>
+      </c>
+      <c r="N162" t="n">
+        <v>0</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>https://www.netflix.com</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>23</v>
+      </c>
+      <c r="C163" t="n">
+        <v>2</v>
+      </c>
+      <c r="D163" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" t="b">
+        <v>0</v>
+      </c>
+      <c r="F163" t="b">
+        <v>1</v>
+      </c>
+      <c r="G163" t="b">
+        <v>0</v>
+      </c>
+      <c r="H163" t="b">
+        <v>0</v>
+      </c>
+      <c r="I163" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" t="b">
+        <v>0</v>
+      </c>
+      <c r="L163" t="b">
+        <v>0</v>
+      </c>
+      <c r="M163" t="n">
+        <v>10533</v>
+      </c>
+      <c r="N163" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>23</v>
+      </c>
+      <c r="C164" t="n">
+        <v>2</v>
+      </c>
+      <c r="D164" t="n">
+        <v>0</v>
+      </c>
+      <c r="E164" t="b">
+        <v>0</v>
+      </c>
+      <c r="F164" t="b">
+        <v>1</v>
+      </c>
+      <c r="G164" t="b">
+        <v>0</v>
+      </c>
+      <c r="H164" t="b">
+        <v>0</v>
+      </c>
+      <c r="I164" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J164" t="n">
+        <v>1</v>
+      </c>
+      <c r="K164" t="b">
+        <v>0</v>
+      </c>
+      <c r="L164" t="b">
+        <v>0</v>
+      </c>
+      <c r="M164" t="n">
+        <v>11926</v>
+      </c>
+      <c r="N164" t="n">
+        <v>0</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>https://www.dropbox.com</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>23</v>
+      </c>
+      <c r="C165" t="n">
+        <v>2</v>
+      </c>
+      <c r="D165" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" t="b">
+        <v>0</v>
+      </c>
+      <c r="F165" t="b">
+        <v>1</v>
+      </c>
+      <c r="G165" t="b">
+        <v>0</v>
+      </c>
+      <c r="H165" t="b">
+        <v>0</v>
+      </c>
+      <c r="I165" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" t="b">
+        <v>0</v>
+      </c>
+      <c r="L165" t="b">
+        <v>0</v>
+      </c>
+      <c r="M165" t="n">
+        <v>11400</v>
+      </c>
+      <c r="N165" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>19</v>
+      </c>
+      <c r="C166" t="n">
+        <v>2</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" t="b">
+        <v>0</v>
+      </c>
+      <c r="F166" t="b">
+        <v>1</v>
+      </c>
+      <c r="G166" t="b">
+        <v>0</v>
+      </c>
+      <c r="H166" t="b">
+        <v>0</v>
+      </c>
+      <c r="I166" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="b">
+        <v>0</v>
+      </c>
+      <c r="L166" t="b">
+        <v>0</v>
+      </c>
+      <c r="M166" t="n">
+        <v>13574</v>
+      </c>
+      <c r="N166" t="n">
+        <v>0</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>https://www.cloudflare.com</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>26</v>
+      </c>
+      <c r="C167" t="n">
+        <v>2</v>
+      </c>
+      <c r="D167" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" t="b">
+        <v>0</v>
+      </c>
+      <c r="F167" t="b">
+        <v>1</v>
+      </c>
+      <c r="G167" t="b">
+        <v>0</v>
+      </c>
+      <c r="H167" t="b">
+        <v>0</v>
+      </c>
+      <c r="I167" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="b">
+        <v>0</v>
+      </c>
+      <c r="L167" t="b">
+        <v>0</v>
+      </c>
+      <c r="M167" t="n">
+        <v>6416</v>
+      </c>
+      <c r="N167" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>https://www.mozilla.org</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>23</v>
+      </c>
+      <c r="C168" t="n">
+        <v>2</v>
+      </c>
+      <c r="D168" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" t="b">
+        <v>0</v>
+      </c>
+      <c r="F168" t="b">
+        <v>1</v>
+      </c>
+      <c r="G168" t="b">
+        <v>0</v>
+      </c>
+      <c r="H168" t="b">
+        <v>0</v>
+      </c>
+      <c r="I168" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="b">
+        <v>0</v>
+      </c>
+      <c r="L168" t="b">
+        <v>0</v>
+      </c>
+      <c r="M168" t="n">
+        <v>10459</v>
+      </c>
+      <c r="N168" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>https://www.oracle.com</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>22</v>
+      </c>
+      <c r="C169" t="n">
+        <v>2</v>
+      </c>
+      <c r="D169" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" t="b">
+        <v>0</v>
+      </c>
+      <c r="F169" t="b">
+        <v>1</v>
+      </c>
+      <c r="G169" t="b">
+        <v>0</v>
+      </c>
+      <c r="H169" t="b">
+        <v>0</v>
+      </c>
+      <c r="I169" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="b">
+        <v>0</v>
+      </c>
+      <c r="L169" t="b">
+        <v>0</v>
+      </c>
+      <c r="M169" t="n">
+        <v>13799</v>
+      </c>
+      <c r="N169" t="n">
+        <v>0</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>https://www.salesforce.com</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>26</v>
+      </c>
+      <c r="C170" t="n">
+        <v>2</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" t="b">
+        <v>0</v>
+      </c>
+      <c r="F170" t="b">
+        <v>1</v>
+      </c>
+      <c r="G170" t="b">
+        <v>0</v>
+      </c>
+      <c r="H170" t="b">
+        <v>0</v>
+      </c>
+      <c r="I170" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" t="b">
+        <v>0</v>
+      </c>
+      <c r="L170" t="b">
+        <v>0</v>
+      </c>
+      <c r="M170" t="n">
+        <v>10147</v>
+      </c>
+      <c r="N170" t="n">
+        <v>0</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>https://www.zoom.us</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>19</v>
+      </c>
+      <c r="C171" t="n">
+        <v>2</v>
+      </c>
+      <c r="D171" t="n">
+        <v>0</v>
+      </c>
+      <c r="E171" t="b">
+        <v>0</v>
+      </c>
+      <c r="F171" t="b">
+        <v>1</v>
+      </c>
+      <c r="G171" t="b">
+        <v>0</v>
+      </c>
+      <c r="H171" t="b">
+        <v>0</v>
+      </c>
+      <c r="I171" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" t="b">
+        <v>0</v>
+      </c>
+      <c r="L171" t="b">
+        <v>0</v>
+      </c>
+      <c r="M171" t="n">
+        <v>8907</v>
+      </c>
+      <c r="N171" t="n">
+        <v>0</v>
+      </c>
+      <c r="O171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>23</v>
+      </c>
+      <c r="C172" t="n">
+        <v>2</v>
+      </c>
+      <c r="D172" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" t="b">
+        <v>0</v>
+      </c>
+      <c r="F172" t="b">
+        <v>1</v>
+      </c>
+      <c r="G172" t="b">
+        <v>0</v>
+      </c>
+      <c r="H172" t="b">
+        <v>0</v>
+      </c>
+      <c r="I172" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" t="b">
+        <v>0</v>
+      </c>
+      <c r="L172" t="b">
+        <v>0</v>
+      </c>
+      <c r="M172" t="n">
+        <v>7856</v>
+      </c>
+      <c r="N172" t="n">
+        <v>0</v>
+      </c>
+      <c r="O172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>https://www.adobe.com</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>21</v>
+      </c>
+      <c r="C173" t="n">
+        <v>2</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" t="b">
+        <v>0</v>
+      </c>
+      <c r="F173" t="b">
+        <v>1</v>
+      </c>
+      <c r="G173" t="b">
+        <v>0</v>
+      </c>
+      <c r="H173" t="b">
+        <v>0</v>
+      </c>
+      <c r="I173" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K173" t="b">
+        <v>0</v>
+      </c>
+      <c r="L173" t="b">
+        <v>0</v>
+      </c>
+      <c r="M173" t="n">
+        <v>14545</v>
+      </c>
+      <c r="N173" t="n">
+        <v>0</v>
+      </c>
+      <c r="O173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>https://www.slack.com</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>21</v>
+      </c>
+      <c r="C174" t="n">
+        <v>2</v>
+      </c>
+      <c r="D174" t="n">
+        <v>0</v>
+      </c>
+      <c r="E174" t="b">
+        <v>0</v>
+      </c>
+      <c r="F174" t="b">
+        <v>1</v>
+      </c>
+      <c r="G174" t="b">
+        <v>0</v>
+      </c>
+      <c r="H174" t="b">
+        <v>0</v>
+      </c>
+      <c r="I174" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J174" t="n">
+        <v>0</v>
+      </c>
+      <c r="K174" t="b">
+        <v>0</v>
+      </c>
+      <c r="L174" t="b">
+        <v>0</v>
+      </c>
+      <c r="M174" t="n">
+        <v>12380</v>
+      </c>
+      <c r="N174" t="n">
+        <v>0</v>
+      </c>
+      <c r="O174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>20</v>
+      </c>
+      <c r="C175" t="n">
+        <v>2</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" t="b">
+        <v>0</v>
+      </c>
+      <c r="F175" t="b">
+        <v>1</v>
+      </c>
+      <c r="G175" t="b">
+        <v>0</v>
+      </c>
+      <c r="H175" t="b">
+        <v>0</v>
+      </c>
+      <c r="I175" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J175" t="n">
+        <v>0</v>
+      </c>
+      <c r="K175" t="b">
+        <v>0</v>
+      </c>
+      <c r="L175" t="b">
+        <v>0</v>
+      </c>
+      <c r="M175" t="n">
+        <v>11363</v>
+      </c>
+      <c r="N175" t="n">
+        <v>0</v>
+      </c>
+      <c r="O175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>https://www.twitch.tv</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>21</v>
+      </c>
+      <c r="C176" t="n">
+        <v>2</v>
+      </c>
+      <c r="D176" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" t="b">
+        <v>0</v>
+      </c>
+      <c r="F176" t="b">
+        <v>1</v>
+      </c>
+      <c r="G176" t="b">
+        <v>0</v>
+      </c>
+      <c r="H176" t="b">
+        <v>0</v>
+      </c>
+      <c r="I176" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J176" t="n">
+        <v>0</v>
+      </c>
+      <c r="K176" t="b">
+        <v>0</v>
+      </c>
+      <c r="L176" t="b">
+        <v>0</v>
+      </c>
+      <c r="M176" t="n">
+        <v>6305</v>
+      </c>
+      <c r="N176" t="n">
+        <v>0</v>
+      </c>
+      <c r="O176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>https://www.uber.com</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>20</v>
+      </c>
+      <c r="C177" t="n">
+        <v>2</v>
+      </c>
+      <c r="D177" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177" t="b">
+        <v>0</v>
+      </c>
+      <c r="F177" t="b">
+        <v>1</v>
+      </c>
+      <c r="G177" t="b">
+        <v>0</v>
+      </c>
+      <c r="H177" t="b">
+        <v>0</v>
+      </c>
+      <c r="I177" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
+      <c r="K177" t="b">
+        <v>0</v>
+      </c>
+      <c r="L177" t="b">
+        <v>0</v>
+      </c>
+      <c r="M177" t="n">
+        <v>11384</v>
+      </c>
+      <c r="N177" t="n">
+        <v>0</v>
+      </c>
+      <c r="O177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>https://www.airbnb.com</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>22</v>
+      </c>
+      <c r="C178" t="n">
+        <v>2</v>
+      </c>
+      <c r="D178" t="n">
+        <v>0</v>
+      </c>
+      <c r="E178" t="b">
+        <v>0</v>
+      </c>
+      <c r="F178" t="b">
+        <v>1</v>
+      </c>
+      <c r="G178" t="b">
+        <v>0</v>
+      </c>
+      <c r="H178" t="b">
+        <v>0</v>
+      </c>
+      <c r="I178" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J178" t="n">
+        <v>1</v>
+      </c>
+      <c r="K178" t="b">
+        <v>0</v>
+      </c>
+      <c r="L178" t="b">
+        <v>1</v>
+      </c>
+      <c r="M178" t="n">
+        <v>6613</v>
+      </c>
+      <c r="N178" t="n">
+        <v>3</v>
+      </c>
+      <c r="O178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>https://www.chase.com</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>21</v>
+      </c>
+      <c r="C179" t="n">
+        <v>2</v>
+      </c>
+      <c r="D179" t="n">
+        <v>0</v>
+      </c>
+      <c r="E179" t="b">
+        <v>0</v>
+      </c>
+      <c r="F179" t="b">
+        <v>1</v>
+      </c>
+      <c r="G179" t="b">
+        <v>0</v>
+      </c>
+      <c r="H179" t="b">
+        <v>0</v>
+      </c>
+      <c r="I179" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J179" t="n">
+        <v>1</v>
+      </c>
+      <c r="K179" t="b">
+        <v>1</v>
+      </c>
+      <c r="L179" t="b">
+        <v>0</v>
+      </c>
+      <c r="M179" t="n">
+        <v>11295</v>
+      </c>
+      <c r="N179" t="n">
+        <v>0</v>
+      </c>
+      <c r="O179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>https://www.bankofamerica.com</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>29</v>
+      </c>
+      <c r="C180" t="n">
+        <v>2</v>
+      </c>
+      <c r="D180" t="n">
+        <v>0</v>
+      </c>
+      <c r="E180" t="b">
+        <v>0</v>
+      </c>
+      <c r="F180" t="b">
+        <v>1</v>
+      </c>
+      <c r="G180" t="b">
+        <v>0</v>
+      </c>
+      <c r="H180" t="b">
+        <v>0</v>
+      </c>
+      <c r="I180" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J180" t="n">
+        <v>4</v>
+      </c>
+      <c r="K180" t="b">
+        <v>0</v>
+      </c>
+      <c r="L180" t="b">
+        <v>0</v>
+      </c>
+      <c r="M180" t="n">
+        <v>10121</v>
+      </c>
+      <c r="N180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>https://www.target.com</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>22</v>
+      </c>
+      <c r="C181" t="n">
+        <v>2</v>
+      </c>
+      <c r="D181" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" t="b">
+        <v>0</v>
+      </c>
+      <c r="F181" t="b">
+        <v>1</v>
+      </c>
+      <c r="G181" t="b">
+        <v>0</v>
+      </c>
+      <c r="H181" t="b">
+        <v>0</v>
+      </c>
+      <c r="I181" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J181" t="n">
+        <v>3</v>
+      </c>
+      <c r="K181" t="b">
+        <v>0</v>
+      </c>
+      <c r="L181" t="b">
+        <v>0</v>
+      </c>
+      <c r="M181" t="n">
+        <v>10846</v>
+      </c>
+      <c r="N181" t="n">
+        <v>0</v>
+      </c>
+      <c r="O181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>25</v>
+      </c>
+      <c r="C182" t="n">
+        <v>2</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" t="b">
+        <v>0</v>
+      </c>
+      <c r="F182" t="b">
+        <v>1</v>
+      </c>
+      <c r="G182" t="b">
+        <v>0</v>
+      </c>
+      <c r="H182" t="b">
+        <v>0</v>
+      </c>
+      <c r="I182" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J182" t="n">
+        <v>0</v>
+      </c>
+      <c r="K182" t="b">
+        <v>0</v>
+      </c>
+      <c r="L182" t="b">
+        <v>0</v>
+      </c>
+      <c r="M182" t="n">
+        <v>8135</v>
+      </c>
+      <c r="N182" t="n">
+        <v>0</v>
+      </c>
+      <c r="O182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>https://www.wellsfargo.com</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>26</v>
+      </c>
+      <c r="C183" t="n">
+        <v>2</v>
+      </c>
+      <c r="D183" t="n">
+        <v>0</v>
+      </c>
+      <c r="E183" t="b">
+        <v>0</v>
+      </c>
+      <c r="F183" t="b">
+        <v>1</v>
+      </c>
+      <c r="G183" t="b">
+        <v>0</v>
+      </c>
+      <c r="H183" t="b">
+        <v>0</v>
+      </c>
+      <c r="I183" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J183" t="n">
+        <v>4</v>
+      </c>
+      <c r="K183" t="b">
+        <v>1</v>
+      </c>
+      <c r="L183" t="b">
+        <v>1</v>
+      </c>
+      <c r="M183" t="n">
+        <v>12191</v>
+      </c>
+      <c r="N183" t="n">
+        <v>5</v>
+      </c>
+      <c r="O183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>24</v>
+      </c>
+      <c r="C184" t="n">
+        <v>2</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0</v>
+      </c>
+      <c r="E184" t="b">
+        <v>0</v>
+      </c>
+      <c r="F184" t="b">
+        <v>1</v>
+      </c>
+      <c r="G184" t="b">
+        <v>0</v>
+      </c>
+      <c r="H184" t="b">
+        <v>0</v>
+      </c>
+      <c r="I184" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J184" t="n">
+        <v>0</v>
+      </c>
+      <c r="K184" t="b">
+        <v>0</v>
+      </c>
+      <c r="L184" t="b">
+        <v>0</v>
+      </c>
+      <c r="M184" t="n">
+        <v>10760</v>
+      </c>
+      <c r="N184" t="n">
+        <v>0</v>
+      </c>
+      <c r="O184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>https://www.stackoverflow.com</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>29</v>
+      </c>
+      <c r="C185" t="n">
+        <v>2</v>
+      </c>
+      <c r="D185" t="n">
+        <v>0</v>
+      </c>
+      <c r="E185" t="b">
+        <v>0</v>
+      </c>
+      <c r="F185" t="b">
+        <v>1</v>
+      </c>
+      <c r="G185" t="b">
+        <v>0</v>
+      </c>
+      <c r="H185" t="b">
+        <v>0</v>
+      </c>
+      <c r="I185" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J185" t="n">
+        <v>0</v>
+      </c>
+      <c r="K185" t="b">
+        <v>0</v>
+      </c>
+      <c r="L185" t="b">
+        <v>0</v>
+      </c>
+      <c r="M185" t="n">
+        <v>8296</v>
+      </c>
+      <c r="N185" t="n">
+        <v>0</v>
+      </c>
+      <c r="O185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>https://www.pinterest.com</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>25</v>
+      </c>
+      <c r="C186" t="n">
+        <v>2</v>
+      </c>
+      <c r="D186" t="n">
+        <v>0</v>
+      </c>
+      <c r="E186" t="b">
+        <v>0</v>
+      </c>
+      <c r="F186" t="b">
+        <v>1</v>
+      </c>
+      <c r="G186" t="b">
+        <v>0</v>
+      </c>
+      <c r="H186" t="b">
+        <v>0</v>
+      </c>
+      <c r="I186" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J186" t="n">
+        <v>0</v>
+      </c>
+      <c r="K186" t="b">
+        <v>0</v>
+      </c>
+      <c r="L186" t="b">
+        <v>0</v>
+      </c>
+      <c r="M186" t="n">
+        <v>6134</v>
+      </c>
+      <c r="N186" t="n">
+        <v>0</v>
+      </c>
+      <c r="O186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
           <t>https://www.ibm.com</t>
         </is>
       </c>
-      <c r="B91" t="n">
+      <c r="B187" t="n">
         <v>19</v>
       </c>
-      <c r="C91" t="n">
-        <v>2</v>
-      </c>
-      <c r="D91" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" t="b">
-        <v>0</v>
-      </c>
-      <c r="F91" t="b">
-        <v>1</v>
-      </c>
-      <c r="G91" t="b">
-        <v>0</v>
-      </c>
-      <c r="H91" t="b">
-        <v>0</v>
-      </c>
-      <c r="I91" t="n">
+      <c r="C187" t="n">
+        <v>2</v>
+      </c>
+      <c r="D187" t="n">
+        <v>0</v>
+      </c>
+      <c r="E187" t="b">
+        <v>0</v>
+      </c>
+      <c r="F187" t="b">
+        <v>1</v>
+      </c>
+      <c r="G187" t="b">
+        <v>0</v>
+      </c>
+      <c r="H187" t="b">
+        <v>0</v>
+      </c>
+      <c r="I187" t="n">
         <v>-0</v>
       </c>
-      <c r="J91" t="n">
-        <v>1</v>
-      </c>
-      <c r="K91" t="b">
-        <v>0</v>
-      </c>
-      <c r="L91" t="b">
-        <v>0</v>
-      </c>
-      <c r="M91" t="n">
-        <v>14787</v>
-      </c>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" t="n">
+      <c r="J187" t="n">
+        <v>1</v>
+      </c>
+      <c r="K187" t="b">
+        <v>0</v>
+      </c>
+      <c r="L187" t="b">
+        <v>0</v>
+      </c>
+      <c r="M187" t="n">
+        <v>14788</v>
+      </c>
+      <c r="N187" t="n">
+        <v>0</v>
+      </c>
+      <c r="O187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>21</v>
+      </c>
+      <c r="C188" t="n">
+        <v>2</v>
+      </c>
+      <c r="D188" t="n">
+        <v>0</v>
+      </c>
+      <c r="E188" t="b">
+        <v>0</v>
+      </c>
+      <c r="F188" t="b">
+        <v>1</v>
+      </c>
+      <c r="G188" t="b">
+        <v>0</v>
+      </c>
+      <c r="H188" t="b">
+        <v>0</v>
+      </c>
+      <c r="I188" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J188" t="n">
+        <v>1</v>
+      </c>
+      <c r="K188" t="b">
+        <v>0</v>
+      </c>
+      <c r="L188" t="b">
+        <v>0</v>
+      </c>
+      <c r="M188" t="n">
+        <v>11561</v>
+      </c>
+      <c r="N188" t="n">
+        <v>0</v>
+      </c>
+      <c r="O188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>https://www.wordpress.com</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>25</v>
+      </c>
+      <c r="C189" t="n">
+        <v>2</v>
+      </c>
+      <c r="D189" t="n">
+        <v>0</v>
+      </c>
+      <c r="E189" t="b">
+        <v>0</v>
+      </c>
+      <c r="F189" t="b">
+        <v>1</v>
+      </c>
+      <c r="G189" t="b">
+        <v>0</v>
+      </c>
+      <c r="H189" t="b">
+        <v>0</v>
+      </c>
+      <c r="I189" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J189" t="n">
+        <v>1</v>
+      </c>
+      <c r="K189" t="b">
+        <v>0</v>
+      </c>
+      <c r="L189" t="b">
+        <v>1</v>
+      </c>
+      <c r="M189" t="n">
+        <v>9689</v>
+      </c>
+      <c r="N189" t="n">
+        <v>3</v>
+      </c>
+      <c r="O189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>https://www.aws.amazon.com</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>26</v>
+      </c>
+      <c r="C190" t="n">
+        <v>3</v>
+      </c>
+      <c r="D190" t="n">
+        <v>0</v>
+      </c>
+      <c r="E190" t="b">
+        <v>0</v>
+      </c>
+      <c r="F190" t="b">
+        <v>1</v>
+      </c>
+      <c r="G190" t="b">
+        <v>0</v>
+      </c>
+      <c r="H190" t="b">
+        <v>0</v>
+      </c>
+      <c r="I190" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J190" t="n">
+        <v>3</v>
+      </c>
+      <c r="K190" t="b">
+        <v>0</v>
+      </c>
+      <c r="L190" t="b">
+        <v>0</v>
+      </c>
+      <c r="M190" t="n">
+        <v>11639</v>
+      </c>
+      <c r="N190" t="n">
+        <v>0</v>
+      </c>
+      <c r="O190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>https://www.digitalocean.com</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>28</v>
+      </c>
+      <c r="C191" t="n">
+        <v>2</v>
+      </c>
+      <c r="D191" t="n">
+        <v>0</v>
+      </c>
+      <c r="E191" t="b">
+        <v>0</v>
+      </c>
+      <c r="F191" t="b">
+        <v>1</v>
+      </c>
+      <c r="G191" t="b">
+        <v>0</v>
+      </c>
+      <c r="H191" t="b">
+        <v>0</v>
+      </c>
+      <c r="I191" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J191" t="n">
+        <v>0</v>
+      </c>
+      <c r="K191" t="b">
+        <v>0</v>
+      </c>
+      <c r="L191" t="b">
+        <v>0</v>
+      </c>
+      <c r="M191" t="n">
+        <v>9650</v>
+      </c>
+      <c r="N191" t="n">
+        <v>0</v>
+      </c>
+      <c r="O191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>https://www.bing.com</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>20</v>
+      </c>
+      <c r="C192" t="n">
+        <v>2</v>
+      </c>
+      <c r="D192" t="n">
+        <v>0</v>
+      </c>
+      <c r="E192" t="b">
+        <v>0</v>
+      </c>
+      <c r="F192" t="b">
+        <v>1</v>
+      </c>
+      <c r="G192" t="b">
+        <v>0</v>
+      </c>
+      <c r="H192" t="b">
+        <v>0</v>
+      </c>
+      <c r="I192" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J192" t="n">
+        <v>0</v>
+      </c>
+      <c r="K192" t="b">
+        <v>0</v>
+      </c>
+      <c r="L192" t="b">
+        <v>0</v>
+      </c>
+      <c r="M192" t="n">
+        <v>11185</v>
+      </c>
+      <c r="N192" t="n">
+        <v>0</v>
+      </c>
+      <c r="O192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>https://www.notion.so</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>21</v>
+      </c>
+      <c r="C193" t="n">
+        <v>2</v>
+      </c>
+      <c r="D193" t="n">
+        <v>0</v>
+      </c>
+      <c r="E193" t="b">
+        <v>0</v>
+      </c>
+      <c r="F193" t="b">
+        <v>1</v>
+      </c>
+      <c r="G193" t="b">
+        <v>0</v>
+      </c>
+      <c r="H193" t="b">
+        <v>0</v>
+      </c>
+      <c r="I193" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" t="b">
+        <v>0</v>
+      </c>
+      <c r="L193" t="b">
+        <v>0</v>
+      </c>
+      <c r="M193" t="n">
+        <v>4184</v>
+      </c>
+      <c r="N193" t="n">
+        <v>0</v>
+      </c>
+      <c r="O193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>25</v>
+      </c>
+      <c r="C194" t="n">
+        <v>2</v>
+      </c>
+      <c r="D194" t="n">
+        <v>0</v>
+      </c>
+      <c r="E194" t="b">
+        <v>0</v>
+      </c>
+      <c r="F194" t="b">
+        <v>1</v>
+      </c>
+      <c r="G194" t="b">
+        <v>0</v>
+      </c>
+      <c r="H194" t="b">
+        <v>0</v>
+      </c>
+      <c r="I194" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J194" t="n">
+        <v>0</v>
+      </c>
+      <c r="K194" t="b">
+        <v>0</v>
+      </c>
+      <c r="L194" t="b">
+        <v>0</v>
+      </c>
+      <c r="M194" t="n">
+        <v>9308</v>
+      </c>
+      <c r="N194" t="n">
+        <v>0</v>
+      </c>
+      <c r="O194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>https://www.figma.com</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>21</v>
+      </c>
+      <c r="C195" t="n">
+        <v>2</v>
+      </c>
+      <c r="D195" t="n">
+        <v>0</v>
+      </c>
+      <c r="E195" t="b">
+        <v>0</v>
+      </c>
+      <c r="F195" t="b">
+        <v>1</v>
+      </c>
+      <c r="G195" t="b">
+        <v>0</v>
+      </c>
+      <c r="H195" t="b">
+        <v>0</v>
+      </c>
+      <c r="I195" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J195" t="n">
+        <v>0</v>
+      </c>
+      <c r="K195" t="b">
+        <v>0</v>
+      </c>
+      <c r="L195" t="b">
+        <v>0</v>
+      </c>
+      <c r="M195" t="n">
+        <v>10018</v>
+      </c>
+      <c r="N195" t="n">
+        <v>0</v>
+      </c>
+      <c r="O195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>https://www.canva.com</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>21</v>
+      </c>
+      <c r="C196" t="n">
+        <v>2</v>
+      </c>
+      <c r="D196" t="n">
+        <v>0</v>
+      </c>
+      <c r="E196" t="b">
+        <v>0</v>
+      </c>
+      <c r="F196" t="b">
+        <v>1</v>
+      </c>
+      <c r="G196" t="b">
+        <v>0</v>
+      </c>
+      <c r="H196" t="b">
+        <v>0</v>
+      </c>
+      <c r="I196" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J196" t="n">
+        <v>0</v>
+      </c>
+      <c r="K196" t="b">
+        <v>0</v>
+      </c>
+      <c r="L196" t="b">
+        <v>0</v>
+      </c>
+      <c r="M196" t="n">
+        <v>9262</v>
+      </c>
+      <c r="N196" t="n">
+        <v>0</v>
+      </c>
+      <c r="O196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>https://www.trello.com</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>22</v>
+      </c>
+      <c r="C197" t="n">
+        <v>2</v>
+      </c>
+      <c r="D197" t="n">
+        <v>0</v>
+      </c>
+      <c r="E197" t="b">
+        <v>0</v>
+      </c>
+      <c r="F197" t="b">
+        <v>1</v>
+      </c>
+      <c r="G197" t="b">
+        <v>0</v>
+      </c>
+      <c r="H197" t="b">
+        <v>0</v>
+      </c>
+      <c r="I197" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J197" t="n">
+        <v>3</v>
+      </c>
+      <c r="K197" t="b">
+        <v>0</v>
+      </c>
+      <c r="L197" t="b">
+        <v>1</v>
+      </c>
+      <c r="M197" t="n">
+        <v>8058</v>
+      </c>
+      <c r="N197" t="n">
+        <v>3</v>
+      </c>
+      <c r="O197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>https://www.asana.com</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>21</v>
+      </c>
+      <c r="C198" t="n">
+        <v>2</v>
+      </c>
+      <c r="D198" t="n">
+        <v>0</v>
+      </c>
+      <c r="E198" t="b">
+        <v>0</v>
+      </c>
+      <c r="F198" t="b">
+        <v>1</v>
+      </c>
+      <c r="G198" t="b">
+        <v>0</v>
+      </c>
+      <c r="H198" t="b">
+        <v>0</v>
+      </c>
+      <c r="I198" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J198" t="n">
+        <v>1</v>
+      </c>
+      <c r="K198" t="b">
+        <v>0</v>
+      </c>
+      <c r="L198" t="b">
+        <v>0</v>
+      </c>
+      <c r="M198" t="n">
+        <v>6443</v>
+      </c>
+      <c r="N198" t="n">
+        <v>0</v>
+      </c>
+      <c r="O198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>https://www.walmart.com</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>23</v>
+      </c>
+      <c r="C199" t="n">
+        <v>2</v>
+      </c>
+      <c r="D199" t="n">
+        <v>0</v>
+      </c>
+      <c r="E199" t="b">
+        <v>0</v>
+      </c>
+      <c r="F199" t="b">
+        <v>1</v>
+      </c>
+      <c r="G199" t="b">
+        <v>0</v>
+      </c>
+      <c r="H199" t="b">
+        <v>0</v>
+      </c>
+      <c r="I199" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J199" t="n">
+        <v>1</v>
+      </c>
+      <c r="K199" t="b">
+        <v>0</v>
+      </c>
+      <c r="L199" t="b">
+        <v>0</v>
+      </c>
+      <c r="M199" t="n">
+        <v>11525</v>
+      </c>
+      <c r="N199" t="n">
+        <v>0</v>
+      </c>
+      <c r="O199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>https://www.twitter.com</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>23</v>
+      </c>
+      <c r="C200" t="n">
+        <v>2</v>
+      </c>
+      <c r="D200" t="n">
+        <v>0</v>
+      </c>
+      <c r="E200" t="b">
+        <v>0</v>
+      </c>
+      <c r="F200" t="b">
+        <v>1</v>
+      </c>
+      <c r="G200" t="b">
+        <v>0</v>
+      </c>
+      <c r="H200" t="b">
+        <v>0</v>
+      </c>
+      <c r="I200" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J200" t="n">
+        <v>0</v>
+      </c>
+      <c r="K200" t="b">
+        <v>0</v>
+      </c>
+      <c r="L200" t="b">
+        <v>0</v>
+      </c>
+      <c r="M200" t="n">
+        <v>9731</v>
+      </c>
+      <c r="N200" t="n">
+        <v>0</v>
+      </c>
+      <c r="O200" t="n">
         <v>0</v>
       </c>
     </row>

--- a/labeled_dataset.xlsx
+++ b/labeled_dataset.xlsx
@@ -643,23 +643,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://s4w.in/ezxWm</t>
+          <t>http://express-dhl-production.up.railway.app/</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
       <c r="F5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="b">
         <v>0</v>
@@ -668,7 +668,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1.58</v>
+        <v>3.82</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -680,10 +680,10 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>6877</v>
+        <v>2600</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -692,23 +692,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>http://express-dhl-production.up.railway.app/</t>
+          <t>https://s4w.in/ezxWm</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
       </c>
       <c r="F6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>3.82</v>
+        <v>1.58</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -729,10 +729,10 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2600</v>
+        <v>6877</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1129,11 +1129,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>http://www.uuu-holdlog.godaddysites.com/</t>
+          <t>http://www.leboncoin-4dah.vercel.app/</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C15" t="n">
         <v>3</v>
@@ -1154,7 +1154,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>2.66</v>
+        <v>3.52</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1165,11 +1165,9 @@
       <c r="L15" t="b">
         <v>0</v>
       </c>
-      <c r="M15" t="n">
-        <v>4681</v>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
@@ -1178,11 +1176,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>http://www.leboncoin-4dah.vercel.app/</t>
+          <t>http://www.uuu-holdlog.godaddysites.com/</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C16" t="n">
         <v>3</v>
@@ -1203,7 +1201,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>3.52</v>
+        <v>2.66</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1214,9 +1212,11 @@
       <c r="L16" t="b">
         <v>0</v>
       </c>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>4681</v>
+      </c>
       <c r="N16" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
         <v>1</v>
@@ -1468,14 +1468,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://facilities-information.com/s/63BZGFSVBWSFCDX7Y9/584dd8/90eab167-7429-489f-99f6-ce86e8d0d81a/</t>
+          <t>http://security-server-landing-page--ninnyjuju.replit.app/</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
         <v>5</v>
@@ -1484,7 +1484,7 @@
         <v>0</v>
       </c>
       <c r="F22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="b">
         <v>0</v>
@@ -1493,22 +1493,20 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>3.48</v>
+        <v>3.86</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="b">
         <v>0</v>
       </c>
-      <c r="M22" t="n">
-        <v>5063</v>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
         <v>1</v>
@@ -1517,14 +1515,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>http://security-server-landing-page--ninnyjuju.replit.app/</t>
+          <t>https://facilities-information.com/s/63BZGFSVBWSFCDX7Y9/584dd8/90eab167-7429-489f-99f6-ce86e8d0d81a/</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
         <v>5</v>
@@ -1533,7 +1531,7 @@
         <v>0</v>
       </c>
       <c r="F23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="b">
         <v>0</v>
@@ -1542,20 +1540,22 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>3.86</v>
+        <v>3.48</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
       </c>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="n">
+        <v>5063</v>
+      </c>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>1</v>
@@ -1901,23 +1901,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://fls-a2ba3ea2-2297-46d0-bceb-50440331a6c9.laravel.cloud/dom/DOMAIN.html</t>
+          <t>http://allegrolokalnie.72893752.xyz/oferta/iphone-15-pro-max-256-gb-white-titanium/</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
       </c>
       <c r="F31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="b">
         <v>0</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>3.96</v>
+        <v>2.97</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1938,10 +1938,10 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3362</v>
+        <v>1</v>
       </c>
       <c r="N31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O31" t="n">
         <v>1</v>
@@ -1950,23 +1950,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>http://allegrolokalnie.72893752.xyz/oferta/iphone-15-pro-max-256-gb-white-titanium/</t>
+          <t>https://fls-a2ba3ea2-2297-46d0-bceb-50440331a6c9.laravel.cloud/dom/DOMAIN.html</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
       </c>
       <c r="F32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" t="b">
         <v>0</v>
@@ -1975,7 +1975,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>2.97</v>
+        <v>3.96</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1987,10 +1987,10 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>3362</v>
       </c>
       <c r="N32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O32" t="n">
         <v>1</v>
@@ -1999,17 +1999,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://rbcode.net/v/b1ac0ecb25f5419af70cb65ce036b2e8</t>
+          <t>https://siamjjk7-star.github.io/Nothing-</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
@@ -2021,10 +2021,10 @@
         <v>0</v>
       </c>
       <c r="H33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>2.58</v>
+        <v>3.24</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>81</v>
+        <v>4936</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O33" t="n">
         <v>1</v>
@@ -2048,14 +2048,14 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.mettamusksign0inx.godaddysites.com/</t>
+          <t>https://rbcode.net/v/b1ac0ecb25f5419af70cb65ce036b2e8</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -2070,10 +2070,10 @@
         <v>0</v>
       </c>
       <c r="H34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>3.5</v>
+        <v>2.58</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2085,10 +2085,10 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>4681</v>
+        <v>81</v>
       </c>
       <c r="N34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>1</v>
@@ -2097,17 +2097,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://siamjjk7-star.github.io/Nothing-</t>
+          <t>https://www.mettamusksign0inx.godaddysites.com/</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E35" t="b">
         <v>0</v>
@@ -2122,7 +2122,7 @@
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2134,10 +2134,10 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>4936</v>
+        <v>4681</v>
       </c>
       <c r="N35" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O35" t="n">
         <v>1</v>
@@ -2434,17 +2434,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://webmail-oauth.lygrunfeng.com/manager/26/0b3f80fb-3440-4ced-9341-a0aa52c060d1</t>
+          <t>https://adammuftau-cmd.github.io/susu_app/</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="C42" t="n">
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E42" t="b">
         <v>0</v>
@@ -2456,10 +2456,10 @@
         <v>0</v>
       </c>
       <c r="H42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>3.55</v>
+        <v>2.84</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2471,7 +2471,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>6773</v>
+        <v>4936</v>
       </c>
       <c r="N42" t="n">
         <v>3</v>
@@ -2483,17 +2483,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://adammuftau-cmd.github.io/susu_app/</t>
+          <t>https://webmail-oauth.lygrunfeng.com/manager/26/0b3f80fb-3440-4ced-9341-a0aa52c060d1</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="C43" t="n">
         <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
@@ -2505,10 +2505,10 @@
         <v>0</v>
       </c>
       <c r="H43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>2.84</v>
+        <v>3.55</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>4936</v>
+        <v>6773</v>
       </c>
       <c r="N43" t="n">
         <v>3</v>
@@ -2628,17 +2628,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://8zerytt9lboomi1eygs.vercel.app/gsnfns43e5rhbwaerdfsvb.html</t>
+          <t>https://devoted-rose-2zod17zj.edgeone.dev/home</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
@@ -2650,10 +2650,10 @@
         <v>0</v>
       </c>
       <c r="H46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>3.83</v>
+        <v>3.52</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O46" t="n">
         <v>1</v>
@@ -2722,14 +2722,14 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://ejtgs7hmgzc00c87y3r.vercel.app/nsvw35re4hbarefsdbvzxcv</t>
+          <t>https://8zerytt9lboomi1eygs.vercel.app/gsnfns43e5rhbwaerdfsvb.html</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -2769,14 +2769,14 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://ejtgs7hmgzc00c87y3r.vercel.app/nsvw35re4hbarefsdbvzxcv.html</t>
+          <t>https://ejtgs7hmgzc00c87y3r.vercel.app/nsvw35re4hbarefsdbvzxcv</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -2816,14 +2816,14 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://nfyenkryj6v4oeqwluc.vercel.app/bdsfbw35erbasefdbsdfbn354b</t>
+          <t>https://ejtgs7hmgzc00c87y3r.vercel.app/nsvw35re4hbarefsdbvzxcv.html</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -2841,7 +2841,7 @@
         <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>3.93</v>
+        <v>3.83</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2910,17 +2910,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://khcnoydz4bnrl-hbk11.vercel.app/xcvgh5iuxafyu1xcv</t>
+          <t>https://nfyenkryj6v4oeqwluc.vercel.app/bdsfbw35erbasefdbsdfbn354b</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C52" t="n">
         <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" t="b">
         <v>0</v>
@@ -2935,7 +2935,7 @@
         <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>3.72</v>
+        <v>3.93</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2957,17 +2957,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://dev-nasrullah-pk.github.io/spotify-web-player-clone</t>
+          <t>https://khcnoydz4bnrl-hbk11.vercel.app/xcvgh5iuxafyu1xcv.html</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E53" t="b">
         <v>0</v>
@@ -2982,7 +2982,7 @@
         <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>3.62</v>
+        <v>3.72</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2993,9 +2993,7 @@
       <c r="L53" t="b">
         <v>0</v>
       </c>
-      <c r="M53" t="n">
-        <v>4936</v>
-      </c>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="n">
         <v>6</v>
       </c>
@@ -3006,14 +3004,14 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://khcnoydz4bnrl-hbk11.vercel.app/xcvgh5iuxafyu1xcv.html</t>
+          <t>https://khcnoydz4bnrl-hbk11.vercel.app/xcvgh5iuxafyu1xcv</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D54" t="n">
         <v>1</v>
@@ -3100,17 +3098,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://sanath2700.github.io/NetflixRegionFix/</t>
+          <t>https://dev-nasrullah-pk.github.io/spotify-web-player-clone</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="C56" t="n">
         <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E56" t="b">
         <v>0</v>
@@ -3125,7 +3123,7 @@
         <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>2.92</v>
+        <v>3.62</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3140,7 +3138,7 @@
         <v>4936</v>
       </c>
       <c r="N56" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O56" t="n">
         <v>1</v>
@@ -3149,17 +3147,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://ahmadalidev01.github.io/netflix-clone</t>
+          <t>https://malxfnty.twilightparadox.com/xverify/signin?verify=pagesprocess_64934</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="C57" t="n">
         <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" t="b">
         <v>0</v>
@@ -3171,10 +3169,10 @@
         <v>0</v>
       </c>
       <c r="H57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3186,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>4936</v>
+        <v>8447</v>
       </c>
       <c r="N57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>1</v>
@@ -3198,11 +3196,11 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://malxfnty.twilightparadox.com/xverify/signin?verify=pagesprocess_64934</t>
+          <t>https://sanath2700.github.io/NetflixRegionFix/</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="C58" t="n">
         <v>2</v>
@@ -3220,10 +3218,10 @@
         <v>0</v>
       </c>
       <c r="H58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3235,10 +3233,10 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>8447</v>
+        <v>4936</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O58" t="n">
         <v>1</v>
@@ -3247,17 +3245,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://malxfnty.twilightparadox.com/?403verify</t>
+          <t>https://ahmadalidev01.github.io/netflix-clone</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C59" t="n">
         <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" t="b">
         <v>0</v>
@@ -3269,10 +3267,10 @@
         <v>0</v>
       </c>
       <c r="H59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -3284,10 +3282,10 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>8447</v>
+        <v>4936</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O59" t="n">
         <v>1</v>
@@ -3296,11 +3294,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://_domainkey.135nb.top/</t>
+          <t>https://malxfnty.twilightparadox.com/?403verify</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="C60" t="n">
         <v>2</v>
@@ -3321,7 +3319,7 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>3.32</v>
+        <v>3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3333,7 +3331,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>310</v>
+        <v>8447</v>
       </c>
       <c r="N60" t="n">
         <v>0</v>
@@ -3345,17 +3343,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://tavlok.horse/ll/gree.html</t>
+          <t>https://join-coin-eng.zapier.app/go</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C61" t="n">
         <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E61" t="b">
         <v>0</v>
@@ -3370,7 +3368,7 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>2.58</v>
+        <v>2.87</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3381,9 +3379,7 @@
       <c r="L61" t="b">
         <v>0</v>
       </c>
-      <c r="M61" t="n">
-        <v>207</v>
-      </c>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="n">
         <v>0</v>
       </c>
@@ -3394,23 +3390,23 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://join-coin-eng.zapier.app/go</t>
+          <t>http://ww547.colnbasee.us/?tkn=19vnMT3S</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C62" t="n">
         <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E62" t="b">
         <v>0</v>
       </c>
       <c r="F62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G62" t="b">
         <v>0</v>
@@ -3419,7 +3415,7 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>2.87</v>
+        <v>1.92</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -3431,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>1453</v>
+        <v>794</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O62" t="n">
         <v>1</v>
@@ -3443,14 +3439,14 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>http://ww547.colnbasee.us/?tkn=19vnMT3S</t>
+          <t>https://minimonsterrrrr.github.io/projet2.github.io/</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -3459,16 +3455,16 @@
         <v>0</v>
       </c>
       <c r="F63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" t="b">
         <v>0</v>
       </c>
       <c r="H63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63" t="n">
-        <v>1.92</v>
+        <v>2.73</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3480,10 +3476,10 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>794</v>
+        <v>4936</v>
       </c>
       <c r="N63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O63" t="n">
         <v>1</v>
@@ -3492,17 +3488,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://minimonsterrrrr.github.io/projet2.github.io/</t>
+          <t>https://mervoro-mpt-belfavi-a1h9fe57.pages.dev/thn-yjm-uio-lkh?welcome=106348824461361&amp;stt=106348824461361&amp;name_stt=Plastics%20&amp;%20Rubber%20Indonesia</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>52</v>
+        <v>149</v>
       </c>
       <c r="C64" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E64" t="b">
         <v>0</v>
@@ -3517,7 +3513,7 @@
         <v>1</v>
       </c>
       <c r="I64" t="n">
-        <v>2.73</v>
+        <v>4.04</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3528,11 +3524,9 @@
       <c r="L64" t="b">
         <v>0</v>
       </c>
-      <c r="M64" t="n">
-        <v>4936</v>
-      </c>
+      <c r="M64" t="inlineStr"/>
       <c r="N64" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O64" t="n">
         <v>1</v>
@@ -3590,32 +3584,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://mervoro-mpt-belfavi-a1h9fe57.pages.dev/thn-yjm-uio-lkh?welcome=106348824461361&amp;stt=106348824461361&amp;name_stt=Plastics%20&amp;%20Rubber%20Indonesia</t>
+          <t>http://ext-coinbais-us.wasmer.app/</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>149</v>
+        <v>34</v>
       </c>
       <c r="C66" t="n">
         <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E66" t="b">
         <v>0</v>
       </c>
       <c r="F66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G66" t="b">
         <v>0</v>
       </c>
       <c r="H66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>4.04</v>
+        <v>3.51</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -3626,11 +3620,9 @@
       <c r="L66" t="b">
         <v>0</v>
       </c>
-      <c r="M66" t="n">
-        <v>2202</v>
-      </c>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O66" t="n">
         <v>1</v>
@@ -3639,32 +3631,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>http://ext-coinbais-us.wasmer.app/</t>
+          <t>https://alisafwat2011-source.github.io/Facebook</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C67" t="n">
         <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67" t="b">
         <v>0</v>
       </c>
       <c r="F67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" t="b">
         <v>0</v>
       </c>
       <c r="H67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>3.51</v>
+        <v>3.88</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -3676,10 +3668,10 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>2888</v>
+        <v>4936</v>
       </c>
       <c r="N67" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O67" t="n">
         <v>1</v>
@@ -3688,17 +3680,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://alisafwat2011-source.github.io/Facebook</t>
+          <t>https://tavlok.horse/ll/gree.html</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C68" t="n">
         <v>2</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68" t="b">
         <v>0</v>
@@ -3710,10 +3702,10 @@
         <v>0</v>
       </c>
       <c r="H68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>3.88</v>
+        <v>2.58</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -3725,10 +3717,10 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>4936</v>
+        <v>207</v>
       </c>
       <c r="N68" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>1</v>
@@ -3773,9 +3765,7 @@
       <c r="L69" t="b">
         <v>0</v>
       </c>
-      <c r="M69" t="n">
-        <v>461</v>
-      </c>
+      <c r="M69" t="inlineStr"/>
       <c r="N69" t="n">
         <v>4</v>
       </c>
@@ -3786,17 +3776,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://sana44092241-collab.github.io/Amazon-Clone</t>
+          <t>https://_domainkey.135nb.top/</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="C70" t="n">
         <v>2</v>
       </c>
       <c r="D70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E70" t="b">
         <v>0</v>
@@ -3808,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="H70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>3.54</v>
+        <v>3.32</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -3823,10 +3813,10 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>4936</v>
+        <v>310</v>
       </c>
       <c r="N70" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>1</v>
@@ -3835,17 +3825,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://io-trust.github.io/en-es</t>
+          <t>https://shiva52310.github.io/netflix-clone</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C71" t="n">
         <v>2</v>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E71" t="b">
         <v>0</v>
@@ -3860,7 +3850,7 @@
         <v>1</v>
       </c>
       <c r="I71" t="n">
-        <v>2.75</v>
+        <v>3.32</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -3884,17 +3874,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.roblox.com.hr/users/6790651137/profile</t>
+          <t>https://sana44092241-collab.github.io/Amazon-Clone</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>50</v>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E72" t="b">
         <v>0</v>
@@ -3906,10 +3896,10 @@
         <v>0</v>
       </c>
       <c r="H72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" t="n">
-        <v>-0</v>
+        <v>3.54</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -3921,10 +3911,10 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>22</v>
+        <v>4936</v>
       </c>
       <c r="N72" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O72" t="n">
         <v>1</v>
@@ -3933,17 +3923,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://m.ahv3ctpms4e.timeforsurveys.com/s/63BZGFSVBWSFCDX7Y9/584dd8/90eab167-7429-489f-99f6-ce86e8d0d81a/</t>
+          <t>https://io-trust.github.io/en-es</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>106</v>
+        <v>32</v>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E73" t="b">
         <v>0</v>
@@ -3955,10 +3945,10 @@
         <v>0</v>
       </c>
       <c r="H73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" t="n">
-        <v>-0</v>
+        <v>2.75</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -3970,10 +3960,10 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3956</v>
+        <v>4936</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O73" t="n">
         <v>1</v>
@@ -3982,17 +3972,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.roblox.com.hr/users/2180432315/profile</t>
+          <t>https://m.ahv3ctpms4e.timeforsurveys.com/s/63BZGFSVBWSFCDX7Y9/584dd8/90eab167-7429-489f-99f6-ce86e8d0d81a/</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>50</v>
+        <v>106</v>
       </c>
       <c r="C74" t="n">
         <v>3</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E74" t="b">
         <v>0</v>
@@ -4019,10 +4009,10 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>22</v>
+        <v>3956</v>
       </c>
       <c r="N74" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>1</v>
@@ -4031,17 +4021,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://devoted-rose-2zod17zj.edgeone.dev/home</t>
+          <t>https://www.roblox.com.hr/users/6790651137/profile</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E75" t="b">
         <v>0</v>
@@ -4056,7 +4046,7 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>3.52</v>
+        <v>-0</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -4067,7 +4057,9 @@
       <c r="L75" t="b">
         <v>0</v>
       </c>
-      <c r="M75" t="inlineStr"/>
+      <c r="M75" t="n">
+        <v>22</v>
+      </c>
       <c r="N75" t="n">
         <v>3</v>
       </c>
@@ -4078,17 +4070,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://stuttrup.github.io/Spencers-task-organizer/</t>
+          <t>https://www.roblox.com.hr/users/2180432315/profile</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E76" t="b">
         <v>0</v>
@@ -4100,10 +4092,10 @@
         <v>0</v>
       </c>
       <c r="H76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>2.16</v>
+        <v>-0</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -4115,7 +4107,7 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>4936</v>
+        <v>22</v>
       </c>
       <c r="N76" t="n">
         <v>3</v>
@@ -4127,17 +4119,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://s4w.in/roblox-com-users-21804232315-profile</t>
+          <t>https://stuttrup.github.io/Spencers-task-organizer/</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>51</v>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D77" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E77" t="b">
         <v>0</v>
@@ -4149,10 +4141,10 @@
         <v>0</v>
       </c>
       <c r="H77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77" t="n">
-        <v>1.58</v>
+        <v>2.16</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -4164,10 +4156,10 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>6877</v>
+        <v>4936</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O77" t="n">
         <v>1</v>
@@ -4223,14 +4215,14 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.smswt.in/</t>
+          <t>https://goo.su/U5WFdQ</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>21</v>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
@@ -4248,7 +4240,7 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>-0</v>
+        <v>0.92</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -4260,7 +4252,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>1316</v>
+        <v>2647</v>
       </c>
       <c r="N79" t="n">
         <v>0</v>
@@ -4272,17 +4264,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://goo.su/U5WFdQ</t>
+          <t>https://s4w.in/roblox-com-users-21804232315-profile</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="C80" t="n">
         <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E80" t="b">
         <v>0</v>
@@ -4297,7 +4289,7 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>0.92</v>
+        <v>1.58</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -4309,7 +4301,7 @@
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>2647</v>
+        <v>6877</v>
       </c>
       <c r="N80" t="n">
         <v>0</v>
@@ -4321,11 +4313,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://gamiiinlogio.godaddysites.com/</t>
+          <t>https://www.smswt.in/</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C81" t="n">
         <v>2</v>
@@ -4343,10 +4335,10 @@
         <v>0</v>
       </c>
       <c r="H81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>2.58</v>
+        <v>-0</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -4358,10 +4350,10 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>4681</v>
+        <v>1316</v>
       </c>
       <c r="N81" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>1</v>
@@ -4370,14 +4362,14 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.gamiiinlogio.godaddysites.com/</t>
+          <t>https://gamiiinlogio.godaddysites.com/</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
@@ -4419,11 +4411,11 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.roblox.com.bi/users/984831893291/profile</t>
+          <t>https://www.gamiiinlogio.godaddysites.com/</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C83" t="n">
         <v>3</v>
@@ -4441,10 +4433,10 @@
         <v>0</v>
       </c>
       <c r="H83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I83" t="n">
-        <v>-0</v>
+        <v>2.58</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -4456,10 +4448,10 @@
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>191</v>
+        <v>4681</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O83" t="n">
         <v>1</v>
@@ -4468,18 +4460,18 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>http://www.onedrive.secure-connection.us.ci/</t>
+          <t>http://send-secure-trustwallet-usdt-bip20.vercel.app/</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C84" t="n">
+        <v>2</v>
+      </c>
+      <c r="D84" t="n">
         <v>4</v>
       </c>
-      <c r="D84" t="n">
-        <v>1</v>
-      </c>
       <c r="E84" t="b">
         <v>0</v>
       </c>
@@ -4490,10 +4482,10 @@
         <v>0</v>
       </c>
       <c r="H84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I84" t="n">
-        <v>-0</v>
+        <v>3.83</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -4504,11 +4496,9 @@
       <c r="L84" t="b">
         <v>0</v>
       </c>
-      <c r="M84" t="n">
-        <v>304</v>
-      </c>
+      <c r="M84" t="inlineStr"/>
       <c r="N84" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O84" t="n">
         <v>1</v>
@@ -4517,32 +4507,32 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>http://send-secure-trustwallet-usdt-bip20.vercel.app/</t>
+          <t>https://www.roblox.com.bi/users/984831893291/profile</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D85" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E85" t="b">
         <v>0</v>
       </c>
       <c r="F85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G85" t="b">
         <v>0</v>
       </c>
       <c r="H85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>3.83</v>
+        <v>-0</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -4553,9 +4543,11 @@
       <c r="L85" t="b">
         <v>0</v>
       </c>
-      <c r="M85" t="inlineStr"/>
+      <c r="M85" t="n">
+        <v>191</v>
+      </c>
       <c r="N85" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>1</v>
@@ -4662,23 +4654,23 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.roblox.com.hr/users/120114981/profile</t>
+          <t>http://www.onedrive.secure-connection.us.ci/</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E88" t="b">
         <v>0</v>
       </c>
       <c r="F88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88" t="b">
         <v>0</v>
@@ -4699,10 +4691,10 @@
         <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>22</v>
+        <v>304</v>
       </c>
       <c r="N88" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O88" t="n">
         <v>1</v>
@@ -4711,17 +4703,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://s4w.in/roblox-com-users-1202114981-profile</t>
+          <t>https://www.roblox.com.hr/users/120114981/profile</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D89" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E89" t="b">
         <v>0</v>
@@ -4736,7 +4728,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>1.58</v>
+        <v>-0</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -4748,10 +4740,10 @@
         <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>6877</v>
+        <v>22</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O89" t="n">
         <v>1</v>
@@ -4760,35 +4752,35 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>http://www.mmatmasck-usa.godaddysites.com/</t>
+          <t>https://s4w.in/roblox-com-users-1202114981-profile</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E90" t="b">
         <v>0</v>
       </c>
       <c r="F90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G90" t="b">
         <v>0</v>
       </c>
       <c r="H90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>2.82</v>
+        <v>1.58</v>
       </c>
       <c r="J90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K90" t="b">
         <v>0</v>
@@ -4797,10 +4789,10 @@
         <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>4681</v>
+        <v>6877</v>
       </c>
       <c r="N90" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>1</v>
@@ -4809,23 +4801,23 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://increasefollowersforinstagram.blogspot.com/</t>
+          <t>http://www.mmatmasck-usa.godaddysites.com/</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E91" t="b">
         <v>0</v>
       </c>
       <c r="F91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G91" t="b">
         <v>0</v>
@@ -4834,10 +4826,10 @@
         <v>1</v>
       </c>
       <c r="I91" t="n">
-        <v>3.65</v>
+        <v>2.82</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K91" t="b">
         <v>0</v>
@@ -4846,10 +4838,10 @@
         <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>9539</v>
+        <v>4681</v>
       </c>
       <c r="N91" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O91" t="n">
         <v>1</v>
@@ -4905,23 +4897,23 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>http://homes-usa-trezr.pages.dev/</t>
+          <t>https://increasefollowersforinstagram.blogspot.com/</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C93" t="n">
         <v>2</v>
       </c>
       <c r="D93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E93" t="b">
         <v>0</v>
       </c>
       <c r="F93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" t="b">
         <v>0</v>
@@ -4930,7 +4922,7 @@
         <v>1</v>
       </c>
       <c r="I93" t="n">
-        <v>3.37</v>
+        <v>3.65</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -4941,9 +4933,11 @@
       <c r="L93" t="b">
         <v>0</v>
       </c>
-      <c r="M93" t="inlineStr"/>
+      <c r="M93" t="n">
+        <v>9539</v>
+      </c>
       <c r="N93" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O93" t="n">
         <v>1</v>
@@ -4952,32 +4946,32 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.roblox.com.bi/users/371040669174/profile</t>
+          <t>http://homes-usa-trezr.pages.dev/</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="C94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E94" t="b">
         <v>0</v>
       </c>
       <c r="F94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" t="b">
         <v>0</v>
       </c>
       <c r="H94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I94" t="n">
-        <v>-0</v>
+        <v>3.37</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -4988,11 +4982,9 @@
       <c r="L94" t="b">
         <v>0</v>
       </c>
-      <c r="M94" t="n">
-        <v>191</v>
-      </c>
+      <c r="M94" t="inlineStr"/>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O94" t="n">
         <v>1</v>
@@ -5001,14 +4993,14 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://arifrxm.github.io/</t>
+          <t>https://www.roblox.com.bi/users/371040669174/profile</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
@@ -5023,10 +5015,10 @@
         <v>0</v>
       </c>
       <c r="H95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>2.52</v>
+        <v>-0</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -5038,10 +5030,10 @@
         <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>4936</v>
+        <v>191</v>
       </c>
       <c r="N95" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>1</v>
@@ -5050,17 +5042,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.roblox.com.mu/communities/3330747117/Robux-Giveaway-Group</t>
+          <t>https://arifrxm.github.io/</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="C96" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E96" t="b">
         <v>0</v>
@@ -5072,10 +5064,10 @@
         <v>0</v>
       </c>
       <c r="H96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>-0</v>
+        <v>2.52</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -5087,10 +5079,10 @@
         <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>98</v>
+        <v>4936</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O96" t="n">
         <v>1</v>
@@ -5099,17 +5091,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://policy-update-production-migykn.laravel.cloud/</t>
+          <t>https://www.roblox.ly/users/1604972168/profile</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C97" t="n">
         <v>2</v>
       </c>
       <c r="D97" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E97" t="b">
         <v>0</v>
@@ -5124,7 +5116,7 @@
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>3.95</v>
+        <v>-0</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -5136,10 +5128,10 @@
         <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3362</v>
+        <v>61</v>
       </c>
       <c r="N97" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>1</v>
@@ -5148,32 +5140,32 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>http://ihsyy-cbq-rnp7-1ob3h-11-09-2026-hh.pages.dev/</t>
+          <t>https://policy-update-production-migykn.laravel.cloud/</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C98" t="n">
         <v>2</v>
       </c>
       <c r="D98" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E98" t="b">
         <v>0</v>
       </c>
       <c r="F98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G98" t="b">
         <v>0</v>
       </c>
       <c r="H98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -5184,9 +5176,11 @@
       <c r="L98" t="b">
         <v>0</v>
       </c>
-      <c r="M98" t="inlineStr"/>
+      <c r="M98" t="n">
+        <v>3362</v>
+      </c>
       <c r="N98" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O98" t="n">
         <v>1</v>
@@ -5195,17 +5189,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://atulraj03.github.io/Spotify-clone-ui</t>
+          <t>https://www.phantomwallet-solana.godaddysites.com/</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E99" t="b">
         <v>0</v>
@@ -5220,7 +5214,7 @@
         <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>2.95</v>
+        <v>3.38</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -5232,7 +5226,7 @@
         <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>4936</v>
+        <v>4681</v>
       </c>
       <c r="N99" t="n">
         <v>3</v>
@@ -5244,32 +5238,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.roblox.ly/users/1604972168/profile</t>
+          <t>http://ihsyy-cbq-rnp7-1ob3h-11-09-2026-hh.pages.dev/</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C100" t="n">
         <v>2</v>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E100" t="b">
         <v>0</v>
       </c>
       <c r="F100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G100" t="b">
         <v>0</v>
       </c>
       <c r="H100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I100" t="n">
-        <v>-0</v>
+        <v>3.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -5280,11 +5274,9 @@
       <c r="L100" t="b">
         <v>0</v>
       </c>
-      <c r="M100" t="n">
-        <v>61</v>
-      </c>
+      <c r="M100" t="inlineStr"/>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O100" t="n">
         <v>1</v>
@@ -5293,17 +5285,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://meta-verified-blueticks-fb12.vercel.app/</t>
+          <t>https://fb-meta-verified-48503.vercel.app/privacy-/</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C101" t="n">
         <v>2</v>
       </c>
       <c r="D101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E101" t="b">
         <v>0</v>
@@ -5318,7 +5310,7 @@
         <v>1</v>
       </c>
       <c r="I101" t="n">
-        <v>3.97</v>
+        <v>3.85</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -5340,17 +5332,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://fb-meta-verified-48503.vercel.app/privacy-/</t>
+          <t>https://meta-verified-blueticks-fb12.vercel.app/</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C102" t="n">
         <v>2</v>
       </c>
       <c r="D102" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E102" t="b">
         <v>0</v>
@@ -5365,7 +5357,7 @@
         <v>1</v>
       </c>
       <c r="I102" t="n">
-        <v>3.85</v>
+        <v>3.97</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -5387,17 +5379,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.phantomwallet-solana.godaddysites.com/</t>
+          <t>https://www.roblox.com.mu/communities/3330747117/Robux-Giveaway-Group</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="C103" t="n">
         <v>3</v>
       </c>
       <c r="D103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E103" t="b">
         <v>0</v>
@@ -5409,10 +5401,10 @@
         <v>0</v>
       </c>
       <c r="H103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>3.38</v>
+        <v>-0</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -5424,10 +5416,10 @@
         <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>4681</v>
+        <v>98</v>
       </c>
       <c r="N103" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>1</v>
@@ -5436,7 +5428,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://app-exodusweb.pages.dev/%22%3EExodus</t>
+          <t>https://atulraj03.github.io/Spotify-clone-ui</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -5446,7 +5438,7 @@
         <v>2</v>
       </c>
       <c r="D104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E104" t="b">
         <v>0</v>
@@ -5461,7 +5453,7 @@
         <v>1</v>
       </c>
       <c r="I104" t="n">
-        <v>3.39</v>
+        <v>2.95</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -5472,7 +5464,9 @@
       <c r="L104" t="b">
         <v>0</v>
       </c>
-      <c r="M104" t="inlineStr"/>
+      <c r="M104" t="n">
+        <v>4936</v>
+      </c>
       <c r="N104" t="n">
         <v>3</v>
       </c>
@@ -5483,17 +5477,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://desirable-apricot-ljcm1knm.edgeone.dev/home</t>
+          <t>https://app-exodusweb.pages.dev/%22%3EExodus</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C105" t="n">
         <v>2</v>
       </c>
       <c r="D105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E105" t="b">
         <v>0</v>
@@ -5505,10 +5499,10 @@
         <v>0</v>
       </c>
       <c r="H105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I105" t="n">
-        <v>4.09</v>
+        <v>3.39</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -5530,17 +5524,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://logicbox-12.pages.dev/?app_vl=ZoNwlWpnbWKEmLqxy5qmnnx0YsC2wa-TpaiVYsBxj2phmqOgnLFwrYw&amp;dd=SyguNyQsMSUoOixkIiIrIQ&amp;e=cookg%2540universityhospital.org&amp;sui=%257Bsui%257D&amp;fn=Greg&amp;ln=Cook&amp;p=&amp;z=CHNAMECL-120...</t>
+          <t>https://desirable-apricot-ljcm1knm.edgeone.dev/home</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>209</v>
+        <v>51</v>
       </c>
       <c r="C106" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E106" t="b">
         <v>0</v>
@@ -5552,10 +5546,10 @@
         <v>0</v>
       </c>
       <c r="H106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>3.28</v>
+        <v>4.09</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -5577,17 +5571,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://buildkit-12.pages.dev/?app_vl=ZoNwlWpnbWKEmLqxy5qmnnx0YsC2wa-TpaiVYsBxj2phmqOgnLFwrYw&amp;dd=SyguNyQsMSUoOixkIiIrIQ&amp;e=Chan%2540yagmail.com&amp;sui=%257Bsui%257D&amp;fn=Chan&amp;ln=Han&amp;p=&amp;z=CHNAMERAW-120926-CZA1</t>
+          <t>https://logicbox-12.pages.dev/?app_vl=ZoNwlWpnbWKEmLqxy5qmnnx0YsC2wa-TpaiVYsBxj2phmqOgnLFwrYw&amp;dd=SyguNyQsMSUoOixkIiIrIQ&amp;e=cookg%2540universityhospital.org&amp;sui=%257Bsui%257D&amp;fn=Greg&amp;ln=Cook&amp;p=&amp;z=CHNAMECL-120...</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="C107" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D107" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E107" t="b">
         <v>0</v>
@@ -5624,17 +5618,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.robiox.com.ps/users/4904839217/profile</t>
+          <t>https://buildkit-12.pages.dev/?app_vl=ZoNwlWpnbWKEmLqxy5qmnnx0YsC2wa-TpaiVYsBxj2phmqOgnLFwrYw&amp;dd=SyguNyQsMSUoOixkIiIrIQ&amp;e=Chan%2540yagmail.com&amp;sui=%257Bsui%257D&amp;fn=Chan&amp;ln=Han&amp;p=&amp;z=CHNAMERAW-120926-CZA1</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>50</v>
+        <v>202</v>
       </c>
       <c r="C108" t="n">
         <v>3</v>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E108" t="b">
         <v>0</v>
@@ -5646,10 +5640,10 @@
         <v>0</v>
       </c>
       <c r="H108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I108" t="n">
-        <v>-0</v>
+        <v>3.28</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -5662,7 +5656,7 @@
       </c>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O108" t="n">
         <v>1</v>
@@ -5671,17 +5665,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://s4w.in/roblox-com-users-5617473240</t>
+          <t>https://accountmanagecenter.vercel.app/privacy-centers.html/</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E109" t="b">
         <v>0</v>
@@ -5693,10 +5687,10 @@
         <v>0</v>
       </c>
       <c r="H109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I109" t="n">
-        <v>1.58</v>
+        <v>3.14</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -5707,11 +5701,9 @@
       <c r="L109" t="b">
         <v>0</v>
       </c>
-      <c r="M109" t="n">
-        <v>6877</v>
-      </c>
+      <c r="M109" t="inlineStr"/>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O109" t="n">
         <v>1</v>
@@ -5720,11 +5712,11 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://f005.backblazeb2.com/file/viewmei/idverf.html</t>
+          <t>https://www.robiox.com.ps/users/4904839217/profile</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C110" t="n">
         <v>3</v>
@@ -5745,7 +5737,7 @@
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>1.5</v>
+        <v>-0</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -5756,9 +5748,7 @@
       <c r="L110" t="b">
         <v>0</v>
       </c>
-      <c r="M110" t="n">
-        <v>3713</v>
-      </c>
+      <c r="M110" t="inlineStr"/>
       <c r="N110" t="n">
         <v>0</v>
       </c>
@@ -5863,17 +5853,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://shiva52310.github.io/netflix-clone</t>
+          <t>https://s4w.in/roblox-com-users-5617473240</t>
         </is>
       </c>
       <c r="B113" t="n">
         <v>42</v>
       </c>
       <c r="C113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E113" t="b">
         <v>0</v>
@@ -5885,10 +5875,10 @@
         <v>0</v>
       </c>
       <c r="H113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>3.32</v>
+        <v>1.58</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -5900,10 +5890,10 @@
         <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>4936</v>
+        <v>6877</v>
       </c>
       <c r="N113" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>1</v>
@@ -6053,17 +6043,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://s4w.in/roblox-com-games-2753915549-Blox-FruitsprivateServerLinkCode=15587938948810815525436529481999</t>
+          <t>https://troubleshoots-google.com/login.php</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>108</v>
+        <v>42</v>
       </c>
       <c r="C117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D117" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E117" t="b">
         <v>0</v>
@@ -6078,7 +6068,7 @@
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>1.58</v>
+        <v>3.24</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -6090,10 +6080,10 @@
         <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>6877</v>
+        <v>3</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O117" t="n">
         <v>1</v>
@@ -6151,17 +6141,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://troubleshoots-google.com/login.php</t>
+          <t>https://timeforsurveys.com/2513501.doc/18a80a/fad0f483-81b2-45c6-ad47-7272058d9cb6/</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="C119" t="n">
         <v>2</v>
       </c>
       <c r="D119" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E119" t="b">
         <v>0</v>
@@ -6176,22 +6166,22 @@
         <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>3.24</v>
+        <v>3.38</v>
       </c>
       <c r="J119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K119" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" t="b">
         <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3</v>
+        <v>3956</v>
       </c>
       <c r="N119" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>1</v>
@@ -6247,17 +6237,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://timeforsurveys.com/2513501.doc/18a80a/fad0f483-81b2-45c6-ad47-7272058d9cb6/</t>
+          <t>https://troubleshoots-google.com/</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="C121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D121" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E121" t="b">
         <v>0</v>
@@ -6272,22 +6262,22 @@
         <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>3.38</v>
+        <v>3.24</v>
       </c>
       <c r="J121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L121" t="b">
         <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3956</v>
+        <v>3</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O121" t="n">
         <v>1</v>
@@ -6296,17 +6286,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://troubleshoots-google.com/</t>
+          <t>https://historical-salmon-zl03sn9j.edgeone.dev/home</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E122" t="b">
         <v>0</v>
@@ -6321,7 +6311,7 @@
         <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>3.24</v>
+        <v>3.95</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -6332,9 +6322,7 @@
       <c r="L122" t="b">
         <v>0</v>
       </c>
-      <c r="M122" t="n">
-        <v>3</v>
-      </c>
+      <c r="M122" t="inlineStr"/>
       <c r="N122" t="n">
         <v>3</v>
       </c>
@@ -6345,17 +6333,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://historical-salmon-zl03sn9j.edgeone.dev/home</t>
+          <t>https://itsupportorganization.com/2513501.doc/18a80a/fad0f483-81b2-45c6-ad47-7272058d9cb6/</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="C123" t="n">
         <v>2</v>
       </c>
       <c r="D123" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E123" t="b">
         <v>0</v>
@@ -6370,7 +6358,7 @@
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>3.95</v>
+        <v>3.33</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -6381,9 +6369,11 @@
       <c r="L123" t="b">
         <v>0</v>
       </c>
-      <c r="M123" t="inlineStr"/>
+      <c r="M123" t="n">
+        <v>1787</v>
+      </c>
       <c r="N123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>1</v>
@@ -6439,23 +6429,23 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://itsupportorganization.com/2513501.doc/18a80a/fad0f483-81b2-45c6-ad47-7272058d9cb6/</t>
+          <t>http://tiny.cc/559a101</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="C125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D125" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E125" t="b">
         <v>0</v>
       </c>
       <c r="F125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G125" t="b">
         <v>0</v>
@@ -6464,7 +6454,7 @@
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>3.33</v>
+        <v>2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -6476,10 +6466,10 @@
         <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>1787</v>
+        <v>7490</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O125" t="n">
         <v>1</v>
@@ -6537,14 +6527,14 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>http://tiny.cc/559a101</t>
+          <t>https://www.itrustcepital_loigin.godaddysites.com/</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="C127" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -6553,16 +6543,16 @@
         <v>0</v>
       </c>
       <c r="F127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G127" t="b">
         <v>0</v>
       </c>
       <c r="H127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I127" t="n">
-        <v>2</v>
+        <v>3.58</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -6574,10 +6564,10 @@
         <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>7490</v>
+        <v>4681</v>
       </c>
       <c r="N127" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O127" t="n">
         <v>1</v>
@@ -6586,14 +6576,14 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://www.itrustcepital_loigin.godaddysites.com/</t>
+          <t>http://trustwalletreport.vercel.app/</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
@@ -6602,7 +6592,7 @@
         <v>0</v>
       </c>
       <c r="F128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G128" t="b">
         <v>0</v>
@@ -6611,7 +6601,7 @@
         <v>1</v>
       </c>
       <c r="I128" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -6622,11 +6612,9 @@
       <c r="L128" t="b">
         <v>0</v>
       </c>
-      <c r="M128" t="n">
-        <v>4681</v>
-      </c>
+      <c r="M128" t="inlineStr"/>
       <c r="N128" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O128" t="n">
         <v>1</v>
@@ -6635,11 +6623,11 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>http://trustwalletreport.vercel.app/</t>
+          <t>http://sendusdtupdated.vercel.app/</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C129" t="n">
         <v>2</v>
@@ -6660,7 +6648,7 @@
         <v>1</v>
       </c>
       <c r="I129" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -6682,17 +6670,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>http://sendusdtupdated.vercel.app/</t>
+          <t>http://www.facebook-six-ivory.vercel.app/</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E130" t="b">
         <v>0</v>
@@ -6707,7 +6695,7 @@
         <v>1</v>
       </c>
       <c r="I130" t="n">
-        <v>2.84</v>
+        <v>3.68</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -6720,7 +6708,7 @@
       </c>
       <c r="M130" t="inlineStr"/>
       <c r="N130" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O130" t="n">
         <v>1</v>
@@ -6776,14 +6764,14 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>http://www.facebook-six-ivory.vercel.app/</t>
+          <t>https://hot-moccasin-v46kgzzn.edgeone.dev/home</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D132" t="n">
         <v>2</v>
@@ -6792,16 +6780,16 @@
         <v>0</v>
       </c>
       <c r="F132" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G132" t="b">
         <v>0</v>
       </c>
       <c r="H132" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>3.68</v>
+        <v>3.92</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -6814,7 +6802,7 @@
       </c>
       <c r="M132" t="inlineStr"/>
       <c r="N132" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O132" t="n">
         <v>1</v>
@@ -6823,7 +6811,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://hot-moccasin-v46kgzzn.edgeone.dev/home</t>
+          <t>https://www.roblox.et/users/6128029595/profile</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -6833,7 +6821,7 @@
         <v>2</v>
       </c>
       <c r="D133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E133" t="b">
         <v>0</v>
@@ -6848,7 +6836,7 @@
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>3.92</v>
+        <v>-0</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -6861,7 +6849,7 @@
       </c>
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>1</v>
@@ -6870,45 +6858,45 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>http://updateserv-owa.vercel.app/</t>
+          <t>https://secure-page-builder--garybrown9939.replit.app/</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C134" t="n">
         <v>2</v>
       </c>
       <c r="D134" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E134" t="b">
         <v>0</v>
       </c>
       <c r="F134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G134" t="b">
         <v>0</v>
       </c>
       <c r="H134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>3.52</v>
+        <v>4.01</v>
       </c>
       <c r="J134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L134" t="b">
         <v>0</v>
       </c>
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O134" t="n">
         <v>1</v>
@@ -6917,32 +6905,32 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://www.roblox.et/users/6128029595/profile</t>
+          <t>http://www.site-tjaobqglc.godaddysites.com/</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E135" t="b">
         <v>0</v>
       </c>
       <c r="F135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G135" t="b">
         <v>0</v>
       </c>
       <c r="H135" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I135" t="n">
-        <v>-0</v>
+        <v>3.66</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -6953,9 +6941,11 @@
       <c r="L135" t="b">
         <v>0</v>
       </c>
-      <c r="M135" t="inlineStr"/>
+      <c r="M135" t="n">
+        <v>4681</v>
+      </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O135" t="n">
         <v>1</v>
@@ -6964,23 +6954,23 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://verified-badge-hub-5639.vercel.app/</t>
+          <t>http://updateserv-owa.vercel.app/</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C136" t="n">
         <v>2</v>
       </c>
       <c r="D136" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E136" t="b">
         <v>0</v>
       </c>
       <c r="F136" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G136" t="b">
         <v>0</v>
@@ -6989,7 +6979,7 @@
         <v>1</v>
       </c>
       <c r="I136" t="n">
-        <v>3.85</v>
+        <v>3.52</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -7002,7 +6992,7 @@
       </c>
       <c r="M136" t="inlineStr"/>
       <c r="N136" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O136" t="n">
         <v>1</v>
@@ -7011,17 +7001,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://secure-page-builder--garybrown9939.replit.app/</t>
+          <t>https://verified-badge-hub-5639.vercel.app/</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C137" t="n">
         <v>2</v>
       </c>
       <c r="D137" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E137" t="b">
         <v>0</v>
@@ -7033,23 +7023,23 @@
         <v>0</v>
       </c>
       <c r="H137" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I137" t="n">
-        <v>4.01</v>
+        <v>3.85</v>
       </c>
       <c r="J137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L137" t="b">
         <v>0</v>
       </c>
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O137" t="n">
         <v>1</v>
@@ -7058,7 +7048,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>http://www.site-tjaobqglc.godaddysites.com/</t>
+          <t>http://www.site-yzcbrf6j0.godaddysites.com/</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -7083,7 +7073,7 @@
         <v>1</v>
       </c>
       <c r="I138" t="n">
-        <v>3.66</v>
+        <v>3.81</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -7107,14 +7097,14 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>http://ebaymclaren-austin.eventshouse.app/</t>
+          <t>https://www.shopee-indonesia33.blogspot.com/</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C139" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D139" t="n">
         <v>1</v>
@@ -7123,16 +7113,16 @@
         <v>0</v>
       </c>
       <c r="F139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G139" t="b">
         <v>0</v>
       </c>
       <c r="H139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I139" t="n">
-        <v>3.68</v>
+        <v>3.35</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -7143,9 +7133,11 @@
       <c r="L139" t="b">
         <v>0</v>
       </c>
-      <c r="M139" t="inlineStr"/>
+      <c r="M139" t="n">
+        <v>9539</v>
+      </c>
       <c r="N139" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O139" t="n">
         <v>1</v>
@@ -7154,17 +7146,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>http://www.bookish-pancake-two.vercel.app/</t>
+          <t>http://ebaymclaren-austin.eventshouse.app/</t>
         </is>
       </c>
       <c r="B140" t="n">
         <v>42</v>
       </c>
       <c r="C140" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D140" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E140" t="b">
         <v>0</v>
@@ -7176,7 +7168,7 @@
         <v>0</v>
       </c>
       <c r="H140" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I140" t="n">
         <v>3.68</v>
@@ -7192,7 +7184,7 @@
       </c>
       <c r="M140" t="inlineStr"/>
       <c r="N140" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O140" t="n">
         <v>1</v>
@@ -7201,17 +7193,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://www.shopee-indonesia33.blogspot.com/</t>
+          <t>https://humanresources-team.com/2513501.doc/18a80a/fad0f483-81b2-45c6-ad47-7272058d9cb6/</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="C141" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D141" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E141" t="b">
         <v>0</v>
@@ -7223,10 +7215,10 @@
         <v>0</v>
       </c>
       <c r="H141" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>3.35</v>
+        <v>3.47</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -7238,10 +7230,10 @@
         <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>9539</v>
+        <v>1787</v>
       </c>
       <c r="N141" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
         <v>1</v>
@@ -7250,17 +7242,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>http://www.site-yzcbrf6j0.godaddysites.com/</t>
+          <t>http://www.bookish-pancake-two.vercel.app/</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C142" t="n">
         <v>3</v>
       </c>
       <c r="D142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E142" t="b">
         <v>0</v>
@@ -7275,7 +7267,7 @@
         <v>1</v>
       </c>
       <c r="I142" t="n">
-        <v>3.81</v>
+        <v>3.68</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -7287,7 +7279,7 @@
         <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>4681</v>
+        <v>2420</v>
       </c>
       <c r="N142" t="n">
         <v>7</v>
@@ -7299,32 +7291,32 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://humanresources-team.com/2513501.doc/18a80a/fad0f483-81b2-45c6-ad47-7272058d9cb6/</t>
+          <t>http://www.verifiedbadge-signal-two.vercel.app/</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="C143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D143" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E143" t="b">
         <v>0</v>
       </c>
       <c r="F143" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G143" t="b">
         <v>0</v>
       </c>
       <c r="H143" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I143" t="n">
-        <v>3.47</v>
+        <v>3.86</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -7336,10 +7328,10 @@
         <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>1787</v>
+        <v>2420</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O143" t="n">
         <v>1</v>
@@ -7348,17 +7340,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>http://www.verifiedbadge-signal-two.vercel.app/</t>
+          <t>http://lib-0568.website-us-southeast-1.linodeobjects.com/</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C144" t="n">
         <v>3</v>
       </c>
       <c r="D144" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E144" t="b">
         <v>0</v>
@@ -7370,10 +7362,10 @@
         <v>0</v>
       </c>
       <c r="H144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>3.86</v>
+        <v>3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -7385,10 +7377,10 @@
         <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>2420</v>
+        <v>2985</v>
       </c>
       <c r="N144" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O144" t="n">
         <v>1</v>
@@ -7397,23 +7389,23 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>http://lib-0568.website-us-southeast-1.linodeobjects.com/</t>
+          <t>https://www.roblox.com.hr/users/1336597261/profile</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C145" t="n">
         <v>3</v>
       </c>
       <c r="D145" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E145" t="b">
         <v>0</v>
       </c>
       <c r="F145" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G145" t="b">
         <v>0</v>
@@ -7422,7 +7414,7 @@
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>3</v>
+        <v>-0</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -7433,11 +7425,9 @@
       <c r="L145" t="b">
         <v>0</v>
       </c>
-      <c r="M145" t="n">
-        <v>2985</v>
-      </c>
+      <c r="M145" t="inlineStr"/>
       <c r="N145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
         <v>1</v>
@@ -7446,11 +7436,11 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://www.roblox.com.hr/users/1336597261/profile</t>
+          <t>https://146a1.casmex.at/kraken/cabs28ls.php</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C146" t="n">
         <v>3</v>
@@ -7471,7 +7461,7 @@
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>-0</v>
+        <v>1.92</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -7542,14 +7532,14 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://146a1.casmex.at/kraken/cabs28ls.php</t>
+          <t>https://recargasjogo.shop/</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C148" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D148" t="n">
         <v>0</v>
@@ -7567,7 +7557,7 @@
         <v>0</v>
       </c>
       <c r="I148" t="n">
-        <v>1.92</v>
+        <v>2.92</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -7578,9 +7568,11 @@
       <c r="L148" t="b">
         <v>0</v>
       </c>
-      <c r="M148" t="inlineStr"/>
+      <c r="M148" t="n">
+        <v>29</v>
+      </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O148" t="n">
         <v>1</v>
@@ -7589,11 +7581,11 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://www.microsoft.com</t>
+          <t>https://www.google.com</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C149" t="n">
         <v>2</v>
@@ -7626,7 +7618,7 @@
         <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>12918</v>
+        <v>10590</v>
       </c>
       <c r="N149" t="n">
         <v>0</v>
@@ -7638,14 +7630,14 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://recargasjogo.shop/</t>
+          <t>https://f005.backblazeb2.com/file/viewmei/idverf.html</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="C150" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D150" t="n">
         <v>0</v>
@@ -7663,7 +7655,7 @@
         <v>0</v>
       </c>
       <c r="I150" t="n">
-        <v>2.92</v>
+        <v>1.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -7675,10 +7667,10 @@
         <v>0</v>
       </c>
       <c r="M150" t="n">
-        <v>29</v>
+        <v>3713</v>
       </c>
       <c r="N150" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O150" t="n">
         <v>1</v>
@@ -7736,11 +7728,11 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://www.google.com</t>
+          <t>https://www.microsoft.com</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C152" t="n">
         <v>2</v>
@@ -7773,7 +7765,7 @@
         <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>10590</v>
+        <v>12918</v>
       </c>
       <c r="N152" t="n">
         <v>0</v>
@@ -7834,17 +7826,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://www.apple.com</t>
+          <t>https://s4w.in/roblox-com-games-2753915549-Blox-FruitsprivateServerLinkCode=15587938948810815525436529481999</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="C154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D154" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E154" t="b">
         <v>0</v>
@@ -7859,10 +7851,10 @@
         <v>0</v>
       </c>
       <c r="I154" t="n">
-        <v>-0</v>
+        <v>1.58</v>
       </c>
       <c r="J154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K154" t="b">
         <v>0</v>
@@ -7871,29 +7863,29 @@
         <v>0</v>
       </c>
       <c r="M154" t="n">
-        <v>14451</v>
+        <v>6877</v>
       </c>
       <c r="N154" t="n">
         <v>0</v>
       </c>
       <c r="O154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://accountmanagecenter.vercel.app/privacy-centers.html/</t>
+          <t>https://www.github.com</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="C155" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E155" t="b">
         <v>0</v>
@@ -7905,13 +7897,13 @@
         <v>0</v>
       </c>
       <c r="H155" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I155" t="n">
-        <v>3.14</v>
+        <v>-0</v>
       </c>
       <c r="J155" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K155" t="b">
         <v>0</v>
@@ -7919,22 +7911,24 @@
       <c r="L155" t="b">
         <v>0</v>
       </c>
-      <c r="M155" t="inlineStr"/>
+      <c r="M155" t="n">
+        <v>6913</v>
+      </c>
       <c r="N155" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://www.github.com</t>
+          <t>https://www.apple.com</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C156" t="n">
         <v>2</v>
@@ -7958,7 +7952,7 @@
         <v>-0</v>
       </c>
       <c r="J156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K156" t="b">
         <v>0</v>
@@ -7967,7 +7961,7 @@
         <v>0</v>
       </c>
       <c r="M156" t="n">
-        <v>6913</v>
+        <v>14451</v>
       </c>
       <c r="N156" t="n">
         <v>0</v>
@@ -7979,11 +7973,11 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://www.wikipedia.org</t>
+          <t>https://www.amazon.com</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C157" t="n">
         <v>2</v>
@@ -8007,7 +8001,7 @@
         <v>-0</v>
       </c>
       <c r="J157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K157" t="b">
         <v>0</v>
@@ -8016,7 +8010,7 @@
         <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>9374</v>
+        <v>11639</v>
       </c>
       <c r="N157" t="n">
         <v>0</v>
@@ -8028,7 +8022,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://www.amazon.com</t>
+          <t>https://www.paypal.com</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -8065,7 +8059,7 @@
         <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>11639</v>
+        <v>9922</v>
       </c>
       <c r="N158" t="n">
         <v>0</v>
@@ -8126,11 +8120,11 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://www.spotify.com</t>
+          <t>https://www.reddit.com</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C160" t="n">
         <v>2</v>
@@ -8154,7 +8148,7 @@
         <v>-0</v>
       </c>
       <c r="J160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K160" t="b">
         <v>0</v>
@@ -8163,7 +8157,7 @@
         <v>0</v>
       </c>
       <c r="M160" t="n">
-        <v>7448</v>
+        <v>7806</v>
       </c>
       <c r="N160" t="n">
         <v>0</v>
@@ -8175,11 +8169,11 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://www.reddit.com</t>
+          <t>https://www.wikipedia.org</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C161" t="n">
         <v>2</v>
@@ -8203,7 +8197,7 @@
         <v>-0</v>
       </c>
       <c r="J161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K161" t="b">
         <v>0</v>
@@ -8212,7 +8206,7 @@
         <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>7806</v>
+        <v>9374</v>
       </c>
       <c r="N161" t="n">
         <v>0</v>
@@ -8224,11 +8218,11 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://www.paypal.com</t>
+          <t>https://www.netflix.com</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C162" t="n">
         <v>2</v>
@@ -8261,7 +8255,7 @@
         <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>9922</v>
+        <v>10533</v>
       </c>
       <c r="N162" t="n">
         <v>0</v>
@@ -8273,7 +8267,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://www.netflix.com</t>
+          <t>https://www.spotify.com</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -8310,7 +8304,7 @@
         <v>0</v>
       </c>
       <c r="M163" t="n">
-        <v>10533</v>
+        <v>7448</v>
       </c>
       <c r="N163" t="n">
         <v>0</v>
@@ -8371,11 +8365,11 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://www.dropbox.com</t>
+          <t>https://www.bbc.com</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C165" t="n">
         <v>2</v>
@@ -8408,7 +8402,7 @@
         <v>0</v>
       </c>
       <c r="M165" t="n">
-        <v>11400</v>
+        <v>13574</v>
       </c>
       <c r="N165" t="n">
         <v>0</v>
@@ -8420,11 +8414,11 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://www.bbc.com</t>
+          <t>https://www.dropbox.com</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C166" t="n">
         <v>2</v>
@@ -8457,7 +8451,7 @@
         <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>13574</v>
+        <v>11400</v>
       </c>
       <c r="N166" t="n">
         <v>0</v>
@@ -8959,11 +8953,11 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://www.uber.com</t>
+          <t>https://www.airbnb.com</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C177" t="n">
         <v>2</v>
@@ -8987,19 +8981,19 @@
         <v>-0</v>
       </c>
       <c r="J177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K177" t="b">
         <v>0</v>
       </c>
       <c r="L177" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M177" t="n">
-        <v>11384</v>
+        <v>6613</v>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -9008,11 +9002,11 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://www.airbnb.com</t>
+          <t>https://www.walmart.com</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C178" t="n">
         <v>2</v>
@@ -9042,13 +9036,13 @@
         <v>0</v>
       </c>
       <c r="L178" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M178" t="n">
-        <v>6613</v>
+        <v>11525</v>
       </c>
       <c r="N178" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -9106,11 +9100,11 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://www.bankofamerica.com</t>
+          <t>https://www.uber.com</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C180" t="n">
         <v>2</v>
@@ -9134,7 +9128,7 @@
         <v>-0</v>
       </c>
       <c r="J180" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K180" t="b">
         <v>0</v>
@@ -9143,7 +9137,7 @@
         <v>0</v>
       </c>
       <c r="M180" t="n">
-        <v>10121</v>
+        <v>11384</v>
       </c>
       <c r="N180" t="n">
         <v>0</v>
@@ -9204,11 +9198,11 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://www.instagram.com</t>
+          <t>https://www.wellsfargo.com</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C182" t="n">
         <v>2</v>
@@ -9232,16 +9226,16 @@
         <v>-0</v>
       </c>
       <c r="J182" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K182" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L182" t="b">
         <v>0</v>
       </c>
       <c r="M182" t="n">
-        <v>8135</v>
+        <v>12191</v>
       </c>
       <c r="N182" t="n">
         <v>0</v>
@@ -9253,11 +9247,11 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://www.wellsfargo.com</t>
+          <t>https://www.instagram.com</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C183" t="n">
         <v>2</v>
@@ -9281,19 +9275,19 @@
         <v>-0</v>
       </c>
       <c r="J183" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K183" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L183" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>12191</v>
+        <v>8135</v>
       </c>
       <c r="N183" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -9351,11 +9345,11 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://www.stackoverflow.com</t>
+          <t>https://www.twitter.com</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C185" t="n">
         <v>2</v>
@@ -9379,7 +9373,7 @@
         <v>-0</v>
       </c>
       <c r="J185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K185" t="b">
         <v>0</v>
@@ -9388,7 +9382,7 @@
         <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>8296</v>
+        <v>9731</v>
       </c>
       <c r="N185" t="n">
         <v>0</v>
@@ -9449,11 +9443,11 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://www.ibm.com</t>
+          <t>https://www.stackoverflow.com</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C187" t="n">
         <v>2</v>
@@ -9477,7 +9471,7 @@
         <v>-0</v>
       </c>
       <c r="J187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K187" t="b">
         <v>0</v>
@@ -9486,7 +9480,7 @@
         <v>0</v>
       </c>
       <c r="M187" t="n">
-        <v>14788</v>
+        <v>8296</v>
       </c>
       <c r="N187" t="n">
         <v>0</v>
@@ -9498,11 +9492,11 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://www.yahoo.com</t>
+          <t>https://www.bing.com</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C188" t="n">
         <v>2</v>
@@ -9526,7 +9520,7 @@
         <v>-0</v>
       </c>
       <c r="J188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K188" t="b">
         <v>0</v>
@@ -9535,7 +9529,7 @@
         <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>11561</v>
+        <v>11185</v>
       </c>
       <c r="N188" t="n">
         <v>0</v>
@@ -9581,13 +9575,13 @@
         <v>0</v>
       </c>
       <c r="L189" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M189" t="n">
         <v>9689</v>
       </c>
       <c r="N189" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -9596,14 +9590,14 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://www.aws.amazon.com</t>
+          <t>https://www.digitalocean.com</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C190" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D190" t="n">
         <v>0</v>
@@ -9624,7 +9618,7 @@
         <v>-0</v>
       </c>
       <c r="J190" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K190" t="b">
         <v>0</v>
@@ -9633,7 +9627,7 @@
         <v>0</v>
       </c>
       <c r="M190" t="n">
-        <v>11639</v>
+        <v>9650</v>
       </c>
       <c r="N190" t="n">
         <v>0</v>
@@ -9645,11 +9639,11 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://www.digitalocean.com</t>
+          <t>https://www.yahoo.com</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C191" t="n">
         <v>2</v>
@@ -9673,7 +9667,7 @@
         <v>-0</v>
       </c>
       <c r="J191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K191" t="b">
         <v>0</v>
@@ -9682,7 +9676,7 @@
         <v>0</v>
       </c>
       <c r="M191" t="n">
-        <v>9650</v>
+        <v>11561</v>
       </c>
       <c r="N191" t="n">
         <v>0</v>
@@ -9694,14 +9688,14 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://www.bing.com</t>
+          <t>https://www.aws.amazon.com</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C192" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D192" t="n">
         <v>0</v>
@@ -9722,7 +9716,7 @@
         <v>-0</v>
       </c>
       <c r="J192" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K192" t="b">
         <v>0</v>
@@ -9731,7 +9725,7 @@
         <v>0</v>
       </c>
       <c r="M192" t="n">
-        <v>11185</v>
+        <v>11639</v>
       </c>
       <c r="N192" t="n">
         <v>0</v>
@@ -9743,11 +9737,11 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://www.notion.so</t>
+          <t>https://www.ibm.com</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C193" t="n">
         <v>2</v>
@@ -9771,7 +9765,7 @@
         <v>-0</v>
       </c>
       <c r="J193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K193" t="b">
         <v>0</v>
@@ -9780,7 +9774,7 @@
         <v>0</v>
       </c>
       <c r="M193" t="n">
-        <v>4184</v>
+        <v>14788</v>
       </c>
       <c r="N193" t="n">
         <v>0</v>
@@ -9841,7 +9835,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://www.figma.com</t>
+          <t>https://www.canva.com</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -9878,7 +9872,7 @@
         <v>0</v>
       </c>
       <c r="M195" t="n">
-        <v>10018</v>
+        <v>9262</v>
       </c>
       <c r="N195" t="n">
         <v>0</v>
@@ -9890,7 +9884,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://www.canva.com</t>
+          <t>https://www.notion.so</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -9927,7 +9921,7 @@
         <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>9262</v>
+        <v>4184</v>
       </c>
       <c r="N196" t="n">
         <v>0</v>
@@ -9988,7 +9982,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://www.asana.com</t>
+          <t>https://www.figma.com</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -10016,7 +10010,7 @@
         <v>-0</v>
       </c>
       <c r="J198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K198" t="b">
         <v>0</v>
@@ -10025,7 +10019,7 @@
         <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>6443</v>
+        <v>10018</v>
       </c>
       <c r="N198" t="n">
         <v>0</v>
@@ -10037,11 +10031,11 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://www.walmart.com</t>
+          <t>https://www.asana.com</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C199" t="n">
         <v>2</v>
@@ -10074,7 +10068,7 @@
         <v>0</v>
       </c>
       <c r="M199" t="n">
-        <v>11525</v>
+        <v>6443</v>
       </c>
       <c r="N199" t="n">
         <v>0</v>
@@ -10086,11 +10080,11 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://www.twitter.com</t>
+          <t>https://www.bankofamerica.com</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C200" t="n">
         <v>2</v>
@@ -10114,7 +10108,7 @@
         <v>-0</v>
       </c>
       <c r="J200" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K200" t="b">
         <v>0</v>
@@ -10123,7 +10117,7 @@
         <v>0</v>
       </c>
       <c r="M200" t="n">
-        <v>9731</v>
+        <v>10121</v>
       </c>
       <c r="N200" t="n">
         <v>0</v>
